--- a/tests/oracle/ORACULO_banca.xlsx
+++ b/tests/oracle/ORACULO_banca.xlsx
@@ -4442,7 +4442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EZ4"/>
+  <dimension ref="A1:GV4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="184" min="1" max="1"/>
@@ -4604,2484 +4604,3297 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ciclo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>empresa</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>grupoMercado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>molde</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>cuero</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>accesorios</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>hilo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>planeado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>jefes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>publicidad</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>regimen</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>seleccion0</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>seleccion1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>seleccion2</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>seleccion3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>seleccion4</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>seleccion5</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>seleccion6</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>seleccion7</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
         <is>
           <t>seleccion8</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="0" t="inlineStr">
         <is>
           <t>seleccion9</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="0" t="inlineStr">
         <is>
           <t>seleccion10</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="0" t="inlineStr">
         <is>
           <t>seleccion11</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="0" t="inlineStr">
         <is>
           <t>seleccion12</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="0" t="inlineStr">
         <is>
           <t>seleccion13</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="0" t="inlineStr">
         <is>
           <t>seleccion14</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="0" t="inlineStr">
         <is>
           <t>seleccion15</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="0" t="inlineStr">
         <is>
           <t>seleccion16</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="0" t="inlineStr">
         <is>
           <t>seleccion17</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="0" t="inlineStr">
         <is>
           <t>puntajeEficiencia</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="0" t="inlineStr">
         <is>
           <t>reputacionBase</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="0" t="inlineStr">
         <is>
           <t>saludFinanciera</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="0" t="inlineStr">
         <is>
           <t>calidad</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="0" t="inlineStr">
         <is>
           <t>reputacionCambio</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="0" t="inlineStr">
         <is>
           <t>precioFactor</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="0" t="inlineStr">
         <is>
           <t>reputacionMatriz</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="0" t="inlineStr">
         <is>
           <t>ciclosReputacionBaja</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="0" t="inlineStr">
         <is>
           <t>factorDemanda</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="0" t="inlineStr">
         <is>
           <t>tasaAdicionalPP</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="0" t="inlineStr">
         <is>
           <t>montoPrestamo</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="0" t="inlineStr">
         <is>
           <t>teaBase</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="0" t="inlineStr">
         <is>
           <t>tasaTEA</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="0" t="inlineStr">
         <is>
           <t>deudaPrincipal</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="0" t="inlineStr">
         <is>
           <t>penalizacionPendiente</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="0" t="inlineStr">
         <is>
           <t>factorConsecuencias</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="0" t="inlineStr">
         <is>
           <t>corte00</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="0" t="inlineStr">
         <is>
           <t>corte01</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="0" t="inlineStr">
         <is>
           <t>corte02</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="0" t="inlineStr">
         <is>
           <t>corte10</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="0" t="inlineStr">
         <is>
           <t>corte11</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="0" t="inlineStr">
         <is>
           <t>corte12</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="0" t="inlineStr">
         <is>
           <t>corte20</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="0" t="inlineStr">
         <is>
           <t>corte21</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="0" t="inlineStr">
         <is>
           <t>corte22</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="0" t="inlineStr">
         <is>
           <t>capacidad_corte</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="0" t="inlineStr">
         <is>
           <t>ensamble00</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="0" t="inlineStr">
         <is>
           <t>ensamble01</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="0" t="inlineStr">
         <is>
           <t>ensamble02</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="0" t="inlineStr">
         <is>
           <t>ensamble10</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="0" t="inlineStr">
         <is>
           <t>ensamble11</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="0" t="inlineStr">
         <is>
           <t>ensamble12</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="0" t="inlineStr">
         <is>
           <t>ensamble20</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="0" t="inlineStr">
         <is>
           <t>ensamble21</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="0" t="inlineStr">
         <is>
           <t>ensamble22</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="0" t="inlineStr">
         <is>
           <t>capacidad_ensamble</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="0" t="inlineStr">
         <is>
           <t>acabado00</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="0" t="inlineStr">
         <is>
           <t>acabado01</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="0" t="inlineStr">
         <is>
           <t>acabado02</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="0" t="inlineStr">
         <is>
           <t>acabado10</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="0" t="inlineStr">
         <is>
           <t>acabado11</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="0" t="inlineStr">
         <is>
           <t>acabado12</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="0" t="inlineStr">
         <is>
           <t>acabado20</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="0" t="inlineStr">
         <is>
           <t>acabado21</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="0" t="inlineStr">
         <is>
           <t>acabado22</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="0" t="inlineStr">
         <is>
           <t>capacidad_acabado</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="0" t="inlineStr">
         <is>
           <t>trabajadores</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="0" t="inlineStr">
         <is>
           <t>n3</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="0" t="inlineStr">
         <is>
           <t>factorEficiencia</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="0" t="inlineStr">
         <is>
           <t>capacidadDiaria</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="0" t="inlineStr">
         <is>
           <t>capacidadCiclo</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="0" t="inlineStr">
         <is>
           <t>produccionCapacidad</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-01</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-01</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-02</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-02</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-03</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-03</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-04</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-04</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-05</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-05</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-06</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-06</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-07</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-07</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="0" t="inlineStr">
         <is>
           <t>comprado_INS-08</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="0" t="inlineStr">
         <is>
           <t>disponible_INS-08</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="0" t="inlineStr">
         <is>
           <t>limite_cuero</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="0" t="inlineStr">
         <is>
           <t>limite_accesorios</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="0" t="inlineStr">
         <is>
           <t>limite_hilo</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="0" t="inlineStr">
         <is>
           <t>producidoPre</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="0" t="inlineStr">
         <is>
           <t>producido</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="0" t="inlineStr">
         <is>
           <t>consumoCuero</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-01</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-01</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-02</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-02</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-03</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-03</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="0" t="inlineStr">
         <is>
           <t>consumoAccesorios</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-04</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-04</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-05</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-05</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="0" t="inlineStr">
         <is>
           <t>consumoHilo</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-06</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-06</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-07</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-07</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="0" t="inlineStr">
         <is>
           <t>usado_INS-08</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="0" t="inlineStr">
         <is>
           <t>stockMP_INS-08</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="0" t="inlineStr">
         <is>
           <t>costoMO</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="0" t="inlineStr">
         <is>
           <t>costoMP</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="0" t="inlineStr">
         <is>
           <t>mantenimiento</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="0" t="inlineStr">
         <is>
           <t>depreciacion</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="0" t="inlineStr">
         <is>
           <t>reputacionOperativa</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="0" t="inlineStr">
         <is>
           <t>reputacionMercado</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="0" t="inlineStr">
         <is>
           <t>stockProductoAntes</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="0" t="inlineStr">
         <is>
           <t>mercadoReal</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="0" t="inlineStr">
         <is>
           <t>precioIdeal</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="0" t="inlineStr">
         <is>
           <t>inventarioProducto</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="0" t="inlineStr">
         <is>
           <t>puntajePrecio</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="0" t="inlineStr">
         <is>
           <t>calidadMercado</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="0" t="inlineStr">
         <is>
           <t>puntajeTotal</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="0" t="inlineStr">
         <is>
           <t>porcentaje</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="0" t="inlineStr">
         <is>
           <t>asignado</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="0" t="inlineStr">
         <is>
           <t>demandaAjustada</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="0" t="inlineStr">
         <is>
           <t>vendido</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="0" t="inlineStr">
         <is>
           <t>ingresos</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="0" t="inlineStr">
         <is>
           <t>almacenaje</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="0" t="inlineStr">
         <is>
           <t>horasExtra</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="0" t="inlineStr">
         <is>
           <t>costoGarantia</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="0" t="inlineStr">
         <is>
           <t>costoRecurrente</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="0" t="inlineStr">
         <is>
           <t>costoLeadTime</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="0" t="inlineStr">
         <is>
           <t>costosTotales</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="0" t="inlineStr">
         <is>
           <t>utilidad</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="0" t="inlineStr">
         <is>
           <t>CONS-01</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="0" t="inlineStr">
         <is>
           <t>CONS-02</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="0" t="inlineStr">
         <is>
           <t>CONS-03</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="0" t="inlineStr">
         <is>
           <t>CONS-04</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="0" t="inlineStr">
         <is>
           <t>CONS-05</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="0" t="inlineStr">
         <is>
           <t>CONS-06</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="0" t="inlineStr">
         <is>
           <t>CONS-07</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="0" t="inlineStr">
         <is>
           <t>CONS-08</t>
         </is>
       </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>capitalInicial</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>compraActivos</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>adquisicionNeta</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>valorCompradoNeto</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>valorInventarioNeto</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>cajaInicial</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>tasaNuevoPrestamo</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>interesMensual</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>tasaMensual</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>intereses</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>pagosOperacion</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>cajaFinal</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>depreciacionAcumulada</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>activosCosto</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>activosFijos</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.ingresos</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.ventasNetas</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.costos</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.utilidad</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.depreciacion</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.intereses</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>financial.estadoResultados.costosProduccion</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.cajaInicial</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.entradas</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.salidas</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>financial.balanceCaja.cajaFinal</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.cajaInicial</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.cobrosVentas</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.pagosOperacion</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.compraActivos</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.financiamiento</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.operacion</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.inversion</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.flujoNeto</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>financial.flujoCaja.cajaFinal</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.efectivo</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.activosFijos</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.inventarioMP</t>
+        </is>
+      </c>
+      <c r="GM1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.activos</t>
+        </is>
+      </c>
+      <c r="GN1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.deuda</t>
+        </is>
+      </c>
+      <c r="GO1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.patrimonio</t>
+        </is>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t>financial.balanceGeneral.pasivoPatrimonio</t>
+        </is>
+      </c>
+      <c r="GQ1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.montoPrestamo</t>
+        </is>
+      </c>
+      <c r="GR1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.tasaTEA</t>
+        </is>
+      </c>
+      <c r="GS1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.deudaPrincipal</t>
+        </is>
+      </c>
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.tasaAdicionalProximoPrestamo</t>
+        </is>
+      </c>
+      <c r="GU1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.tasaMensual</t>
+        </is>
+      </c>
+      <c r="GV1" t="inlineStr">
+        <is>
+          <t>financial.financiamiento.intereses</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>1|SEG-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>MYPE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>FIN-01B</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t>INS-10A</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>INV-02A</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2">
+      <c r="Q2" s="0" t="inlineStr"/>
+      <c r="R2" s="0" t="inlineStr"/>
+      <c r="S2" s="0" t="inlineStr"/>
+      <c r="T2" s="0" t="inlineStr"/>
+      <c r="U2" s="0" t="inlineStr"/>
+      <c r="V2" s="0" t="inlineStr"/>
+      <c r="W2" s="0" t="inlineStr"/>
+      <c r="X2" s="0" t="inlineStr"/>
+      <c r="Y2" s="0" t="inlineStr"/>
+      <c r="Z2" s="0" t="inlineStr"/>
+      <c r="AA2" s="0" t="inlineStr"/>
+      <c r="AB2" s="0" t="inlineStr"/>
+      <c r="AC2" s="0" t="inlineStr"/>
+      <c r="AD2" s="0" t="inlineStr"/>
+      <c r="AE2" s="0" t="inlineStr"/>
+      <c r="AF2" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(F2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(G2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(H2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(E2,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="0">
         <f>IF(AND(D2="SEG-03",I2&gt;0),IF(AI2&lt;4,-2,IF(AI2&gt;=7,2,0)),0)</f>
         <v/>
       </c>
-      <c r="AK2">
+      <c r="AK2" s="0">
         <f>IF(AND(D2="SEG-03",I2&gt;0),IF(AI2&lt;4,0.65,IF(AI2&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AL2">
+      <c r="AL2" s="0">
         <f>AG2+AJ2</f>
         <v/>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="0">
         <f>IF(AL2&lt;3,0+1,0)</f>
         <v/>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="0">
         <f>IF(AM2&gt;=2,0.8,1)</f>
         <v/>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="0">
         <f>IF(AH2&lt;3,3,0)</f>
         <v/>
       </c>
-      <c r="AP2" t="n">
+      <c r="AP2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AQ2" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="0">
         <f>AQ2+0</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="0">
         <f>0+AP2</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="0">
         <f>IF(AP2&gt;0,AO2,MAX(0,AO2))</f>
         <v/>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="0">
         <f>IF(AF2&lt;4,0.7,1)*IF(AND(K2=0,AF2&lt;5),0.95,1)</f>
         <v/>
       </c>
-      <c r="AV2" t="n">
+      <c r="AV2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AW2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AX2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AY2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AZ2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BA2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BC2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BD2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BE2">
+      <c r="BE2" s="0">
         <f>AV2*5*1+AY2*7*1+BB2*9*1</f>
         <v/>
       </c>
-      <c r="BF2" t="n">
+      <c r="BF2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BG2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BH2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BI2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BJ2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BK2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BL2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BM2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BN2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BO2">
+      <c r="BO2" s="0">
         <f>BF2*6*1+BG2*6*1.2+BH2*6*1.5+BI2*8*1+BJ2*8*1.2+BK2*8*1.5+BL2*12*1+BM2*12*1.2+BN2*12*1.5</f>
         <v/>
       </c>
-      <c r="BP2" t="n">
+      <c r="BP2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BQ2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BR2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="BS2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="BT2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="BU2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="BV2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="BW2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="BX2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BY2">
+      <c r="BY2" s="0">
         <f>BP2*6*1+BQ2*6*1.2+BR2*6*1.5+BS2*7*1+BT2*7*1.2+BU2*7*1.5+BV2*10*1+BW2*10*1.2+BX2*10*1.5</f>
         <v/>
       </c>
-      <c r="BZ2">
+      <c r="BZ2" s="0">
         <f>AV2+AY2+BB2+BF2+BG2+BH2+BI2+BJ2+BK2+BL2+BM2+BN2+BP2+BQ2+BR2+BS2+BT2+BU2+BV2+BW2+BX2</f>
         <v/>
       </c>
-      <c r="CA2">
+      <c r="CA2" s="0">
         <f>BB2+BL2+BM2+BN2+BV2+BW2+BX2</f>
         <v/>
       </c>
-      <c r="CB2">
+      <c r="CB2" s="0">
         <f>0.9+(BB2+BL2+BV2)*0.01+K2*0.04</f>
         <v/>
       </c>
-      <c r="CC2">
+      <c r="CC2" s="0">
         <f>MIN(BE2,BO2,BY2)</f>
         <v/>
       </c>
-      <c r="CD2">
+      <c r="CD2" s="0">
         <f>CC2*24*1</f>
         <v/>
       </c>
-      <c r="CE2">
+      <c r="CE2" s="0">
         <f>ROUND(CD2*CB2,0)</f>
         <v/>
       </c>
-      <c r="CF2" t="n">
+      <c r="CF2" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="CG2">
+      <c r="CG2" s="0">
         <f>0+CF2</f>
         <v/>
       </c>
-      <c r="CH2" t="n">
+      <c r="CH2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CI2">
+      <c r="CI2" s="0">
         <f>0+CH2</f>
         <v/>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CJ2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CK2">
+      <c r="CK2" s="0">
         <f>0+CJ2</f>
         <v/>
       </c>
-      <c r="CL2" t="n">
+      <c r="CL2" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="CM2">
+      <c r="CM2" s="0">
         <f>0+CL2</f>
         <v/>
       </c>
-      <c r="CN2" t="n">
+      <c r="CN2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CO2">
+      <c r="CO2" s="0">
         <f>0+CN2</f>
         <v/>
       </c>
-      <c r="CP2" t="n">
+      <c r="CP2" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="CQ2">
+      <c r="CQ2" s="0">
         <f>0+CP2</f>
         <v/>
       </c>
-      <c r="CR2" t="n">
+      <c r="CR2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CS2">
+      <c r="CS2" s="0">
         <f>0+CR2</f>
         <v/>
       </c>
-      <c r="CT2" t="n">
+      <c r="CT2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CU2">
+      <c r="CU2" s="0">
         <f>0+CT2</f>
         <v/>
       </c>
-      <c r="CV2">
+      <c r="CV2" s="0">
         <f>(CG2)/0.3</f>
         <v/>
       </c>
-      <c r="CW2">
+      <c r="CW2" s="0">
         <f>(CM2)/1</f>
         <v/>
       </c>
-      <c r="CX2">
+      <c r="CX2" s="0">
         <f>(CQ2)/6</f>
         <v/>
       </c>
-      <c r="CY2">
+      <c r="CY2" s="0">
         <f>ROUNDDOWN(MIN(I2,CE2,CV2,CW2,CX2),0)</f>
         <v/>
       </c>
-      <c r="CZ2">
+      <c r="CZ2" s="0">
         <f>ROUNDDOWN(CY2*AU2,0)</f>
         <v/>
       </c>
-      <c r="DA2">
+      <c r="DA2" s="0">
         <f>CZ2*0.3</f>
         <v/>
       </c>
-      <c r="DB2">
+      <c r="DB2" s="0">
         <f>MIN(CG2,MAX(0,DA2))</f>
         <v/>
       </c>
-      <c r="DC2">
+      <c r="DC2" s="0">
         <f>CG2-DB2</f>
         <v/>
       </c>
-      <c r="DD2">
+      <c r="DD2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DE2">
+      <c r="DE2" s="0">
         <f>CI2-DD2</f>
         <v/>
       </c>
-      <c r="DF2">
+      <c r="DF2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DG2">
+      <c r="DG2" s="0">
         <f>CK2-DF2</f>
         <v/>
       </c>
-      <c r="DH2">
+      <c r="DH2" s="0">
         <f>CZ2*1</f>
         <v/>
       </c>
-      <c r="DI2">
+      <c r="DI2" s="0">
         <f>MIN(CM2,MAX(0,DH2))</f>
         <v/>
       </c>
-      <c r="DJ2">
+      <c r="DJ2" s="0">
         <f>CM2-DI2</f>
         <v/>
       </c>
-      <c r="DK2">
+      <c r="DK2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DL2">
+      <c r="DL2" s="0">
         <f>CO2-DK2</f>
         <v/>
       </c>
-      <c r="DM2">
+      <c r="DM2" s="0">
         <f>CZ2*6</f>
         <v/>
       </c>
-      <c r="DN2">
+      <c r="DN2" s="0">
         <f>MIN(CQ2,MAX(0,DM2))</f>
         <v/>
       </c>
-      <c r="DO2">
+      <c r="DO2" s="0">
         <f>CQ2-DN2</f>
         <v/>
       </c>
-      <c r="DP2">
+      <c r="DP2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DQ2">
+      <c r="DQ2" s="0">
         <f>CS2-DP2</f>
         <v/>
       </c>
-      <c r="DR2">
+      <c r="DR2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DS2">
+      <c r="DS2" s="0">
         <f>CU2-DR2</f>
         <v/>
       </c>
-      <c r="DT2">
+      <c r="DT2" s="0">
         <f>((AV2+AW2+AX2)*IF(M2="NO_MYPE",'Costos De Producción'!V11,'Costos De Producción'!U11)+(AY2+AZ2+BA2)*IF(M2="NO_MYPE",'Costos De Producción'!V20,'Costos De Producción'!U20)+(BB2+BC2+BD2)*IF(M2="NO_MYPE",'Costos De Producción'!V29,'Costos De Producción'!U29)+(BF2+BG2+BH2)*IF(M2="NO_MYPE",'Costos De Producción'!Z11,'Costos De Producción'!Y11)+(BI2+BJ2+BK2)*IF(M2="NO_MYPE",'Costos De Producción'!Z20,'Costos De Producción'!Y20)+(BL2+BM2+BN2)*IF(M2="NO_MYPE",'Costos De Producción'!Z29,'Costos De Producción'!Y29)+(BP2+BQ2+BR2)*IF(M2="NO_MYPE",'Costos De Producción'!AD11,'Costos De Producción'!AC11)+(BS2+BT2+BU2)*IF(M2="NO_MYPE",'Costos De Producción'!AD20,'Costos De Producción'!AC20)+(BV2+BW2+BX2)*IF(M2="NO_MYPE",'Costos De Producción'!AD29,'Costos De Producción'!AC29)+K2*IF(M2="NO_MYPE",'Costos De Producción'!V39,'Costos De Producción'!U39)+IF(M2="NO_MYPE",'Costos De Producción'!Z39,'Costos De Producción'!Y39)+'Costos De Producción'!AC33)*1</f>
         <v/>
       </c>
-      <c r="DU2">
+      <c r="DU2" s="0">
         <f>(DB2*25+DD2*45+DF2*80+DI2*4+DK2*9+DN2*2+DP2*4+DR2*7)*0.8924</f>
         <v/>
       </c>
-      <c r="DV2">
+      <c r="DV2" s="0">
         <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1</f>
         <v/>
       </c>
-      <c r="DW2">
+      <c r="DW2" s="0">
         <f>1*(2375.0/10/12*1)+1*(3325.0/10/12*1)+1*(1140.0/8/12*1)+1*(285.0/5/12*1)</f>
         <v/>
       </c>
-      <c r="DX2">
+      <c r="DX2" s="0">
         <f>IF(CZ2&gt;0,0,0)+IFERROR(CA2/BZ2,0)*10+(IFERROR(DF2/(DB2+DD2+DF2),0)+IFERROR(DK2/(DI2+DK2),0)+IFERROR(DR2/(DP2+DR2),0))/3*10+L2/10000*10</f>
         <v/>
       </c>
-      <c r="DY2">
+      <c r="DY2" s="0">
         <f>DX2+AJ2</f>
         <v/>
       </c>
-      <c r="DZ2">
+      <c r="DZ2" s="0">
         <f>0+CZ2</f>
         <v/>
       </c>
-      <c r="EA2" t="n">
+      <c r="EA2" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="EB2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="EC2">
+      <c r="EC2" s="0">
         <f>DZ2-EJ2</f>
         <v/>
       </c>
-      <c r="ED2">
+      <c r="ED2" s="0">
         <f>IF(D2="SEG-01",IFERROR(100*(_xlfn.MAXIFS($J$2:$J$4,$C$2:$C$4,C2)-J2)/(_xlfn.MAXIFS($J$2:$J$4,$C$2:$C$4,C2)-_xlfn.MINIFS($J$2:$J$4,$C$2:$C$4,C2)),100),100-ABS(J2-EB2)/EB2*100)</f>
         <v/>
       </c>
-      <c r="EE2">
+      <c r="EE2" s="0">
         <f>ROUND(MIN(100,AI2*10),0)</f>
         <v/>
       </c>
-      <c r="EF2">
+      <c r="EF2" s="0">
         <f>0.7*ED2+0.2*DY2*10+0.1*EE2</f>
         <v/>
       </c>
-      <c r="EG2">
+      <c r="EG2" s="0">
         <f>IFERROR(EF2/SUMIF($C$2:$C$4,C2,$EF$2:$EF$4),0)</f>
         <v/>
       </c>
-      <c r="EH2">
+      <c r="EH2" s="0">
         <f>ROUND(EG2*EA2,0)</f>
         <v/>
       </c>
-      <c r="EI2">
+      <c r="EI2" s="0">
         <f>MAX(0,ROUNDDOWN(EH2*AN2*1,0))</f>
         <v/>
       </c>
-      <c r="EJ2">
+      <c r="EJ2" s="0">
         <f>MIN(DZ2,EI2)</f>
         <v/>
       </c>
-      <c r="EK2">
+      <c r="EK2" s="0">
         <f>EJ2*J2*AK2</f>
         <v/>
       </c>
-      <c r="EL2">
+      <c r="EL2" s="0">
         <f>EC2*2</f>
         <v/>
       </c>
-      <c r="EM2">
+      <c r="EM2" s="0">
         <f>IF(I2&gt;CE2,0.25*DT2*IFERROR(MIN(1,(I2-CE2)/CE2),1),0)</f>
         <v/>
       </c>
-      <c r="EN2">
+      <c r="EN2" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)*EJ2</f>
         <v/>
       </c>
-      <c r="EO2">
+      <c r="EO2" s="0">
         <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("INV-02A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
-      <c r="EP2">
+      <c r="EP2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ2">
+      <c r="EQ2" s="0">
         <f>DT2+DU2+DV2+DW2+L2+EL2+EM2+EN2+EO2+EP2</f>
         <v/>
       </c>
-      <c r="ER2">
+      <c r="ER2" s="0">
         <f>EK2-EQ2</f>
         <v/>
       </c>
-      <c r="ES2">
+      <c r="ES2" s="0">
         <f>AND(D2="SEG-03",AI2&lt;4,I2&gt;0)</f>
         <v/>
       </c>
-      <c r="ET2">
+      <c r="ET2" s="0">
         <f>AND(D2="SEG-03",AI2&gt;=7,I2&gt;0)</f>
         <v/>
       </c>
-      <c r="EU2">
+      <c r="EU2" s="0">
         <f>AF2&lt;4</f>
         <v/>
       </c>
-      <c r="EV2">
+      <c r="EV2" s="0">
         <f>AM2&gt;=2</f>
         <v/>
       </c>
-      <c r="EW2">
+      <c r="EW2" s="0">
         <f>AH2&lt;3</f>
         <v/>
       </c>
-      <c r="EX2">
+      <c r="EX2" s="0">
         <f>I2&gt;CE2</f>
         <v/>
       </c>
-      <c r="EY2">
+      <c r="EY2" s="0">
         <f>CZ2&gt;EJ2</f>
         <v/>
       </c>
-      <c r="EZ2">
+      <c r="EZ2" s="0">
         <f>AND(K2=0,AF2&lt;5)</f>
         <v/>
       </c>
+      <c r="FA2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB2">
+        <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC2">
+        <f>1*2500+1*3500+1*1200+1*300</f>
+        <v/>
+      </c>
+      <c r="FD2">
+        <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FE2">
+        <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.8924</f>
+        <v/>
+      </c>
+      <c r="FF2">
+        <f>FA2</f>
+        <v/>
+      </c>
+      <c r="FG2">
+        <f>(1+AR2/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH2">
+        <f>0*0+AP2*FG2</f>
+        <v/>
+      </c>
+      <c r="FI2">
+        <f>IFERROR(FH2/(0+AP2),0)</f>
+        <v/>
+      </c>
+      <c r="FJ2">
+        <f>FH2*1</f>
+        <v/>
+      </c>
+      <c r="FK2">
+        <f>EQ2-DW2-DU2+FD2+FJ2</f>
+        <v/>
+      </c>
+      <c r="FL2">
+        <f>FF2+EK2+AP2-FK2-FB2</f>
+        <v/>
+      </c>
+      <c r="FM2">
+        <f>0+DW2</f>
+        <v/>
+      </c>
+      <c r="FN2">
+        <f>0+FC2</f>
+        <v/>
+      </c>
+      <c r="FO2">
+        <f>FN2-FM2</f>
+        <v/>
+      </c>
+      <c r="FP2">
+        <f>EK2</f>
+        <v/>
+      </c>
+      <c r="FQ2">
+        <f>EK2</f>
+        <v/>
+      </c>
+      <c r="FR2">
+        <f>EQ2+FJ2</f>
+        <v/>
+      </c>
+      <c r="FS2">
+        <f>ER2-FJ2</f>
+        <v/>
+      </c>
+      <c r="FT2">
+        <f>DW2</f>
+        <v/>
+      </c>
+      <c r="FU2">
+        <f>FJ2</f>
+        <v/>
+      </c>
+      <c r="FV2">
+        <f>EQ2</f>
+        <v/>
+      </c>
+      <c r="FW2">
+        <f>FF2</f>
+        <v/>
+      </c>
+      <c r="FX2">
+        <f>EK2+AP2</f>
+        <v/>
+      </c>
+      <c r="FY2">
+        <f>FK2+FB2</f>
+        <v/>
+      </c>
+      <c r="FZ2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GA2">
+        <f>FF2</f>
+        <v/>
+      </c>
+      <c r="GB2">
+        <f>EK2</f>
+        <v/>
+      </c>
+      <c r="GC2">
+        <f>FK2</f>
+        <v/>
+      </c>
+      <c r="GD2">
+        <f>FB2</f>
+        <v/>
+      </c>
+      <c r="GE2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GF2">
+        <f>EK2-FK2</f>
+        <v/>
+      </c>
+      <c r="GG2">
+        <f>-FB2</f>
+        <v/>
+      </c>
+      <c r="GH2">
+        <f>FL2-FF2</f>
+        <v/>
+      </c>
+      <c r="GI2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GJ2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GK2">
+        <f>FO2</f>
+        <v/>
+      </c>
+      <c r="GL2">
+        <f>FE2</f>
+        <v/>
+      </c>
+      <c r="GM2">
+        <f>FL2+FO2+FE2</f>
+        <v/>
+      </c>
+      <c r="GN2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GO2">
+        <f>FL2+FO2+FE2-AS2</f>
+        <v/>
+      </c>
+      <c r="GP2">
+        <f>FL2+FO2+FE2</f>
+        <v/>
+      </c>
+      <c r="GQ2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GR2">
+        <f>AR2</f>
+        <v/>
+      </c>
+      <c r="GS2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GT2">
+        <f>AT2</f>
+        <v/>
+      </c>
+      <c r="GU2">
+        <f>FI2</f>
+        <v/>
+      </c>
+      <c r="GV2">
+        <f>FJ2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>2|SEG-01</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>MYPE</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>COM-01A</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>FIN-01B</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>INS-09A</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="0" t="inlineStr">
         <is>
           <t>INS-10B</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="0" t="inlineStr">
         <is>
           <t>INS-11C</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="0" t="inlineStr">
         <is>
           <t>RH-10B</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>FIN-02B</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="0" t="inlineStr">
         <is>
           <t>COM-06A</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="0" t="inlineStr">
         <is>
           <t>INF-11A</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="0" t="inlineStr">
         <is>
           <t>INS-12A</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3">
+      <c r="X3" s="0" t="inlineStr"/>
+      <c r="Y3" s="0" t="inlineStr"/>
+      <c r="Z3" s="0" t="inlineStr"/>
+      <c r="AA3" s="0" t="inlineStr"/>
+      <c r="AB3" s="0" t="inlineStr"/>
+      <c r="AC3" s="0" t="inlineStr"/>
+      <c r="AD3" s="0" t="inlineStr"/>
+      <c r="AE3" s="0" t="inlineStr"/>
+      <c r="AF3" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(R3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(S3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(T3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(U3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(W3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(R3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(S3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(T3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(U3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(W3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(R3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(S3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(T3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(U3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(W3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(F3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(G3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(H3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(E3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AJ3">
+      <c r="AJ3" s="0">
         <f>IF(AND(D3="SEG-03",I3&gt;0),IF(AI3&lt;4,-2,IF(AI3&gt;=7,2,0)),0)</f>
         <v/>
       </c>
-      <c r="AK3">
+      <c r="AK3" s="0">
         <f>IF(AND(D3="SEG-03",I3&gt;0),IF(AI3&lt;4,0.65,IF(AI3&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AL3">
+      <c r="AL3" s="0">
         <f>AG3+AJ3</f>
         <v/>
       </c>
-      <c r="AM3">
+      <c r="AM3" s="0">
         <f>IF(AL3&lt;3,AM2+1,0)</f>
         <v/>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="0">
         <f>IF(AM3&gt;=2,0.8,1)</f>
         <v/>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="0">
         <f>IF(AH3&lt;3,3,0)</f>
         <v/>
       </c>
-      <c r="AP3" t="n">
+      <c r="AP3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ3" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="0">
         <f>AQ3+AT2</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="0">
         <f>AS2+AP3</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="0">
         <f>IF(AP3&gt;0,AO3,MAX(AT2,AO3))</f>
         <v/>
       </c>
-      <c r="AU3">
+      <c r="AU3" s="0">
         <f>IF(AF3&lt;4,0.7,1)*IF(AND(K3=0,AF3&lt;5),0.95,1)</f>
         <v/>
       </c>
-      <c r="AV3" t="n">
+      <c r="AV3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AW3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AX3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AY3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AZ3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BA3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BC3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BD3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BE3">
+      <c r="BE3" s="0">
         <f>AV3*5*1+AY3*7*1+BB3*9*1</f>
         <v/>
       </c>
-      <c r="BF3" t="n">
+      <c r="BF3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BG3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BH3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BI3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BJ3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BK3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BL3" t="n">
+      <c r="BL3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BM3" t="n">
+      <c r="BM3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BN3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BO3">
+      <c r="BO3" s="0">
         <f>BF3*6*1+BG3*6*1.2+BH3*6*1.5+BI3*8*1+BJ3*8*1.2+BK3*8*1.5+BL3*12*1+BM3*12*1.2+BN3*12*1.5</f>
         <v/>
       </c>
-      <c r="BP3" t="n">
+      <c r="BP3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BQ3" t="n">
+      <c r="BQ3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BR3" t="n">
+      <c r="BR3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BS3" t="n">
+      <c r="BS3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BT3" t="n">
+      <c r="BT3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="BU3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="BV3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="BW3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="BX3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BY3">
+      <c r="BY3" s="0">
         <f>BP3*6*1+BQ3*6*1.2+BR3*6*1.5+BS3*7*1+BT3*7*1.2+BU3*7*1.5+BV3*10*1+BW3*10*1.2+BX3*10*1.5</f>
         <v/>
       </c>
-      <c r="BZ3">
+      <c r="BZ3" s="0">
         <f>AV3+AY3+BB3+BF3+BG3+BH3+BI3+BJ3+BK3+BL3+BM3+BN3+BP3+BQ3+BR3+BS3+BT3+BU3+BV3+BW3+BX3</f>
         <v/>
       </c>
-      <c r="CA3">
+      <c r="CA3" s="0">
         <f>BB3+BL3+BM3+BN3+BV3+BW3+BX3</f>
         <v/>
       </c>
-      <c r="CB3">
+      <c r="CB3" s="0">
         <f>0.9+(BB3+BL3+BV3)*0.01+K3*0.04</f>
         <v/>
       </c>
-      <c r="CC3">
+      <c r="CC3" s="0">
         <f>MIN(BE3,BO3,BY3)</f>
         <v/>
       </c>
-      <c r="CD3">
+      <c r="CD3" s="0">
         <f>CC3*24*1</f>
         <v/>
       </c>
-      <c r="CE3">
+      <c r="CE3" s="0">
         <f>ROUND(CD3*CB3,0)</f>
         <v/>
       </c>
-      <c r="CF3" t="n">
+      <c r="CF3" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="CG3">
+      <c r="CG3" s="0">
         <f>DC2+CF3</f>
         <v/>
       </c>
-      <c r="CH3" t="n">
+      <c r="CH3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CI3">
+      <c r="CI3" s="0">
         <f>DE2+CH3</f>
         <v/>
       </c>
-      <c r="CJ3" t="n">
+      <c r="CJ3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CK3">
+      <c r="CK3" s="0">
         <f>DG2+CJ3</f>
         <v/>
       </c>
-      <c r="CL3" t="n">
+      <c r="CL3" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="CM3">
+      <c r="CM3" s="0">
         <f>DJ2+CL3</f>
         <v/>
       </c>
-      <c r="CN3" t="n">
+      <c r="CN3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CO3">
+      <c r="CO3" s="0">
         <f>DL2+CN3</f>
         <v/>
       </c>
-      <c r="CP3" t="n">
+      <c r="CP3" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="CQ3">
+      <c r="CQ3" s="0">
         <f>DO2+CP3</f>
         <v/>
       </c>
-      <c r="CR3" t="n">
+      <c r="CR3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CS3">
+      <c r="CS3" s="0">
         <f>DQ2+CR3</f>
         <v/>
       </c>
-      <c r="CT3" t="n">
+      <c r="CT3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CU3">
+      <c r="CU3" s="0">
         <f>DS2+CT3</f>
         <v/>
       </c>
-      <c r="CV3">
+      <c r="CV3" s="0">
         <f>(CG3)/0.3</f>
         <v/>
       </c>
-      <c r="CW3">
+      <c r="CW3" s="0">
         <f>(CM3)/1</f>
         <v/>
       </c>
-      <c r="CX3">
+      <c r="CX3" s="0">
         <f>(CQ3)/6</f>
         <v/>
       </c>
-      <c r="CY3">
+      <c r="CY3" s="0">
         <f>ROUNDDOWN(MIN(I3,CE3,CV3,CW3,CX3),0)</f>
         <v/>
       </c>
-      <c r="CZ3">
+      <c r="CZ3" s="0">
         <f>ROUNDDOWN(CY3*AU3,0)</f>
         <v/>
       </c>
-      <c r="DA3">
+      <c r="DA3" s="0">
         <f>CZ3*0.3</f>
         <v/>
       </c>
-      <c r="DB3">
+      <c r="DB3" s="0">
         <f>MIN(CG3,MAX(0,DA3))</f>
         <v/>
       </c>
-      <c r="DC3">
+      <c r="DC3" s="0">
         <f>CG3-DB3</f>
         <v/>
       </c>
-      <c r="DD3">
+      <c r="DD3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DE3">
+      <c r="DE3" s="0">
         <f>CI3-DD3</f>
         <v/>
       </c>
-      <c r="DF3">
+      <c r="DF3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DG3">
+      <c r="DG3" s="0">
         <f>CK3-DF3</f>
         <v/>
       </c>
-      <c r="DH3">
+      <c r="DH3" s="0">
         <f>CZ3*1</f>
         <v/>
       </c>
-      <c r="DI3">
+      <c r="DI3" s="0">
         <f>MIN(CM3,MAX(0,DH3))</f>
         <v/>
       </c>
-      <c r="DJ3">
+      <c r="DJ3" s="0">
         <f>CM3-DI3</f>
         <v/>
       </c>
-      <c r="DK3">
+      <c r="DK3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DL3">
+      <c r="DL3" s="0">
         <f>CO3-DK3</f>
         <v/>
       </c>
-      <c r="DM3">
+      <c r="DM3" s="0">
         <f>CZ3*6</f>
         <v/>
       </c>
-      <c r="DN3">
+      <c r="DN3" s="0">
         <f>MIN(CQ3,MAX(0,DM3))</f>
         <v/>
       </c>
-      <c r="DO3">
+      <c r="DO3" s="0">
         <f>CQ3-DN3</f>
         <v/>
       </c>
-      <c r="DP3">
+      <c r="DP3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DQ3">
+      <c r="DQ3" s="0">
         <f>CS3-DP3</f>
         <v/>
       </c>
-      <c r="DR3">
+      <c r="DR3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DS3">
+      <c r="DS3" s="0">
         <f>CU3-DR3</f>
         <v/>
       </c>
-      <c r="DT3">
+      <c r="DT3" s="0">
         <f>((AV3+AW3+AX3)*IF(M3="NO_MYPE",'Costos De Producción'!V11,'Costos De Producción'!U11)+(AY3+AZ3+BA3)*IF(M3="NO_MYPE",'Costos De Producción'!V20,'Costos De Producción'!U20)+(BB3+BC3+BD3)*IF(M3="NO_MYPE",'Costos De Producción'!V29,'Costos De Producción'!U29)+(BF3+BG3+BH3)*IF(M3="NO_MYPE",'Costos De Producción'!Z11,'Costos De Producción'!Y11)+(BI3+BJ3+BK3)*IF(M3="NO_MYPE",'Costos De Producción'!Z20,'Costos De Producción'!Y20)+(BL3+BM3+BN3)*IF(M3="NO_MYPE",'Costos De Producción'!Z29,'Costos De Producción'!Y29)+(BP3+BQ3+BR3)*IF(M3="NO_MYPE",'Costos De Producción'!AD11,'Costos De Producción'!AC11)+(BS3+BT3+BU3)*IF(M3="NO_MYPE",'Costos De Producción'!AD20,'Costos De Producción'!AC20)+(BV3+BW3+BX3)*IF(M3="NO_MYPE",'Costos De Producción'!AD29,'Costos De Producción'!AC29)+K3*IF(M3="NO_MYPE",'Costos De Producción'!V39,'Costos De Producción'!U39)+IF(M3="NO_MYPE",'Costos De Producción'!Z39,'Costos De Producción'!Y39)+'Costos De Producción'!AC33)*1</f>
         <v/>
       </c>
-      <c r="DU3">
+      <c r="DU3" s="0">
         <f>(DB3*25+DD3*45+DF3*80+DI3*4+DK3*9+DN3*2+DP3*4+DR3*7)*0.9016000000000001</f>
         <v/>
       </c>
-      <c r="DV3">
+      <c r="DV3" s="0">
         <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="DW3">
+      <c r="DW3" s="0">
         <f>1*(2375.0*CZ3/100000)+1*(3325.0*CZ3/100000)+1*(1140.0*CZ3/100000)+1*(285.0*CZ3/100000)</f>
         <v/>
       </c>
-      <c r="DX3">
+      <c r="DX3" s="0">
         <f>IF(CZ3&gt;0,0,0)+IFERROR(CA3/BZ3,0)*10+(IFERROR(DF3/(DB3+DD3+DF3),0)+IFERROR(DK3/(DI3+DK3),0)+IFERROR(DR3/(DP3+DR3),0))/3*10+L3/10000*10</f>
         <v/>
       </c>
-      <c r="DY3">
+      <c r="DY3" s="0">
         <f>DX3+AJ3</f>
         <v/>
       </c>
-      <c r="DZ3">
+      <c r="DZ3" s="0">
         <f>EC2+CZ3</f>
         <v/>
       </c>
-      <c r="EA3" t="n">
+      <c r="EA3" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="EB3" t="n">
+      <c r="EB3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="EC3">
+      <c r="EC3" s="0">
         <f>DZ3-EJ3</f>
         <v/>
       </c>
-      <c r="ED3">
+      <c r="ED3" s="0">
         <f>IF(D3="SEG-01",IFERROR(100*(_xlfn.MAXIFS($J$2:$J$4,$C$2:$C$4,C3)-J3)/(_xlfn.MAXIFS($J$2:$J$4,$C$2:$C$4,C3)-_xlfn.MINIFS($J$2:$J$4,$C$2:$C$4,C3)),100),100-ABS(J3-EB3)/EB3*100)</f>
         <v/>
       </c>
-      <c r="EE3">
+      <c r="EE3" s="0">
         <f>ROUND(MIN(100,AI3*10),0)</f>
         <v/>
       </c>
-      <c r="EF3">
+      <c r="EF3" s="0">
         <f>0.7*ED3+0.2*DY3*10+0.1*EE3</f>
         <v/>
       </c>
-      <c r="EG3">
+      <c r="EG3" s="0">
         <f>IFERROR(EF3/SUMIF($C$2:$C$4,C3,$EF$2:$EF$4),0)</f>
         <v/>
       </c>
-      <c r="EH3">
+      <c r="EH3" s="0">
         <f>ROUND(EG3*EA3,0)</f>
         <v/>
       </c>
-      <c r="EI3">
+      <c r="EI3" s="0">
         <f>MAX(0,ROUNDDOWN(EH3*AN3*1,0))</f>
         <v/>
       </c>
-      <c r="EJ3">
+      <c r="EJ3" s="0">
         <f>MIN(DZ3,EI3)</f>
         <v/>
       </c>
-      <c r="EK3">
+      <c r="EK3" s="0">
         <f>EJ3*J3*AK3</f>
         <v/>
       </c>
-      <c r="EL3">
+      <c r="EL3" s="0">
         <f>EC3*2</f>
         <v/>
       </c>
-      <c r="EM3">
+      <c r="EM3" s="0">
         <f>IF(I3&gt;CE3,0.25*DT3*IFERROR(MIN(1,(I3-CE3)/CE3),1),0)</f>
         <v/>
       </c>
-      <c r="EN3">
+      <c r="EN3" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-06A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)*EJ3</f>
         <v/>
       </c>
-      <c r="EO3">
+      <c r="EO3" s="0">
         <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-01A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("INS-12A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
-      <c r="EP3">
+      <c r="EP3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ3">
+      <c r="EQ3" s="0">
         <f>DT3+DU3+DV3+DW3+L3+EL3+EM3+EN3+EO3+EP3</f>
         <v/>
       </c>
-      <c r="ER3">
+      <c r="ER3" s="0">
         <f>EK3-EQ3</f>
         <v/>
       </c>
-      <c r="ES3">
+      <c r="ES3" s="0">
         <f>AND(D3="SEG-03",AI3&lt;4,I3&gt;0)</f>
         <v/>
       </c>
-      <c r="ET3">
+      <c r="ET3" s="0">
         <f>AND(D3="SEG-03",AI3&gt;=7,I3&gt;0)</f>
         <v/>
       </c>
-      <c r="EU3">
+      <c r="EU3" s="0">
         <f>AF3&lt;4</f>
         <v/>
       </c>
-      <c r="EV3">
+      <c r="EV3" s="0">
         <f>AM3&gt;=2</f>
         <v/>
       </c>
-      <c r="EW3">
+      <c r="EW3" s="0">
         <f>AH3&lt;3</f>
         <v/>
       </c>
-      <c r="EX3">
+      <c r="EX3" s="0">
         <f>I3&gt;CE3</f>
         <v/>
       </c>
-      <c r="EY3">
+      <c r="EY3" s="0">
         <f>CZ3&gt;EJ3</f>
         <v/>
       </c>
-      <c r="EZ3">
+      <c r="EZ3" s="0">
         <f>AND(K3=0,AF3&lt;5)</f>
         <v/>
       </c>
+      <c r="FA3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB3">
+        <f>0*2500*(1+0.03+0.02)+0*3500*(1+0.03+0.02)+0*1200*(1+0.03+0.02)+0*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC3">
+        <f>0*2500+0*3500+0*1200+0*300</f>
+        <v/>
+      </c>
+      <c r="FD3">
+        <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.9016000000000001</f>
+        <v/>
+      </c>
+      <c r="FE3">
+        <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.9016000000000001</f>
+        <v/>
+      </c>
+      <c r="FF3">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="FG3">
+        <f>(1+AR3/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH3">
+        <f>AS2*FI2+AP3*FG3</f>
+        <v/>
+      </c>
+      <c r="FI3">
+        <f>IFERROR(FH3/(AS2+AP3),0)</f>
+        <v/>
+      </c>
+      <c r="FJ3">
+        <f>FH3*1</f>
+        <v/>
+      </c>
+      <c r="FK3">
+        <f>EQ3-DW3-DU3+FD3+FJ3</f>
+        <v/>
+      </c>
+      <c r="FL3">
+        <f>FF3+EK3+AP3-FK3-FB3</f>
+        <v/>
+      </c>
+      <c r="FM3">
+        <f>FM2+DW3</f>
+        <v/>
+      </c>
+      <c r="FN3">
+        <f>FN2+FC3</f>
+        <v/>
+      </c>
+      <c r="FO3">
+        <f>FN3-FM3</f>
+        <v/>
+      </c>
+      <c r="FP3">
+        <f>EK3</f>
+        <v/>
+      </c>
+      <c r="FQ3">
+        <f>EK3</f>
+        <v/>
+      </c>
+      <c r="FR3">
+        <f>EQ3+FJ3</f>
+        <v/>
+      </c>
+      <c r="FS3">
+        <f>ER3-FJ3</f>
+        <v/>
+      </c>
+      <c r="FT3">
+        <f>DW3</f>
+        <v/>
+      </c>
+      <c r="FU3">
+        <f>FJ3</f>
+        <v/>
+      </c>
+      <c r="FV3">
+        <f>EQ3</f>
+        <v/>
+      </c>
+      <c r="FW3">
+        <f>FF3</f>
+        <v/>
+      </c>
+      <c r="FX3">
+        <f>EK3+AP3</f>
+        <v/>
+      </c>
+      <c r="FY3">
+        <f>FK3+FB3</f>
+        <v/>
+      </c>
+      <c r="FZ3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GA3">
+        <f>FF3</f>
+        <v/>
+      </c>
+      <c r="GB3">
+        <f>EK3</f>
+        <v/>
+      </c>
+      <c r="GC3">
+        <f>FK3</f>
+        <v/>
+      </c>
+      <c r="GD3">
+        <f>FB3</f>
+        <v/>
+      </c>
+      <c r="GE3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GF3">
+        <f>EK3-FK3</f>
+        <v/>
+      </c>
+      <c r="GG3">
+        <f>-FB3</f>
+        <v/>
+      </c>
+      <c r="GH3">
+        <f>FL3-FF3</f>
+        <v/>
+      </c>
+      <c r="GI3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GJ3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GK3">
+        <f>FO3</f>
+        <v/>
+      </c>
+      <c r="GL3">
+        <f>FE3</f>
+        <v/>
+      </c>
+      <c r="GM3">
+        <f>FL3+FO3+FE3</f>
+        <v/>
+      </c>
+      <c r="GN3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GO3">
+        <f>FL3+FO3+FE3-AS3</f>
+        <v/>
+      </c>
+      <c r="GP3">
+        <f>FL3+FO3+FE3</f>
+        <v/>
+      </c>
+      <c r="GQ3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GR3">
+        <f>AR3</f>
+        <v/>
+      </c>
+      <c r="GS3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GT3">
+        <f>AT3</f>
+        <v/>
+      </c>
+      <c r="GU3">
+        <f>FI3</f>
+        <v/>
+      </c>
+      <c r="GV3">
+        <f>FJ3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>3|SEG-01</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>SEG-01</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>INF-08</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>INS-01</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>INS-04</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>INS-06</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>MYPE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="0" t="inlineStr">
         <is>
           <t>COM-01A</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="0" t="inlineStr">
         <is>
           <t>INS-09A</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="0" t="inlineStr">
         <is>
           <t>INS-10B</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="0" t="inlineStr">
         <is>
           <t>INS-11C</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="0" t="inlineStr">
         <is>
           <t>RH-10B</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="0" t="inlineStr">
         <is>
           <t>FIN-02B</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="0" t="inlineStr">
         <is>
           <t>COM-06A</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="0" t="inlineStr">
         <is>
           <t>INF-11A</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V4" s="0" t="inlineStr">
         <is>
           <t>INS-12A</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W4" s="0" t="inlineStr">
         <is>
           <t>FIN-01A</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4">
+      <c r="X4" s="0" t="inlineStr"/>
+      <c r="Y4" s="0" t="inlineStr"/>
+      <c r="Z4" s="0" t="inlineStr"/>
+      <c r="AA4" s="0" t="inlineStr"/>
+      <c r="AB4" s="0" t="inlineStr"/>
+      <c r="AC4" s="0" t="inlineStr"/>
+      <c r="AD4" s="0" t="inlineStr"/>
+      <c r="AE4" s="0" t="inlineStr"/>
+      <c r="AF4" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(R4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(S4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(T4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(V4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(W4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(R4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(S4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(T4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(V4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(W4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(R4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(S4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(T4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(V4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(W4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AI4">
+      <c r="AI4" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(F4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(G4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(H4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$H$2:$H$69,MATCH(E4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="AJ4">
+      <c r="AJ4" s="0">
         <f>IF(AND(D4="SEG-03",I4&gt;0),IF(AI4&lt;4,-2,IF(AI4&gt;=7,2,0)),0)</f>
         <v/>
       </c>
-      <c r="AK4">
+      <c r="AK4" s="0">
         <f>IF(AND(D4="SEG-03",I4&gt;0),IF(AI4&lt;4,0.65,IF(AI4&gt;=7,1.4,1)),1)</f>
         <v/>
       </c>
-      <c r="AL4">
+      <c r="AL4" s="0">
         <f>AG4+AJ4</f>
         <v/>
       </c>
-      <c r="AM4">
+      <c r="AM4" s="0">
         <f>IF(AL4&lt;3,AM3+1,0)</f>
         <v/>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="0">
         <f>IF(AM4&gt;=2,0.8,1)</f>
         <v/>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="0">
         <f>IF(AH4&lt;3,3,0)</f>
         <v/>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP4" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ4" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="0">
         <f>AQ4+AT3</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="0">
         <f>AS3+AP4</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="0">
         <f>IF(AP4&gt;0,AO4,MAX(AT3,AO4))</f>
         <v/>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="0">
         <f>IF(AF4&lt;4,0.7,1)*IF(AND(K4=0,AF4&lt;5),0.95,1)</f>
         <v/>
       </c>
-      <c r="AV4" t="n">
+      <c r="AV4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AW4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AX4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AY4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AZ4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BA4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BC4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BD4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BE4">
+      <c r="BE4" s="0">
         <f>AV4*5*1+AY4*7*1+BB4*9*1</f>
         <v/>
       </c>
-      <c r="BF4" t="n">
+      <c r="BF4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BG4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BH4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BI4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BJ4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BK4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BL4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BM4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BN4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BO4">
+      <c r="BO4" s="0">
         <f>BF4*6*1+BG4*6*1.2+BH4*6*1.5+BI4*8*1+BJ4*8*1.2+BK4*8*1.5+BL4*12*1+BM4*12*1.2+BN4*12*1.5</f>
         <v/>
       </c>
-      <c r="BP4" t="n">
+      <c r="BP4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BQ4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="BR4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="BS4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="BT4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="BU4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="BV4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="BW4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="BX4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="BY4">
+      <c r="BY4" s="0">
         <f>BP4*6*1+BQ4*6*1.2+BR4*6*1.5+BS4*7*1+BT4*7*1.2+BU4*7*1.5+BV4*10*1+BW4*10*1.2+BX4*10*1.5</f>
         <v/>
       </c>
-      <c r="BZ4">
+      <c r="BZ4" s="0">
         <f>AV4+AY4+BB4+BF4+BG4+BH4+BI4+BJ4+BK4+BL4+BM4+BN4+BP4+BQ4+BR4+BS4+BT4+BU4+BV4+BW4+BX4</f>
         <v/>
       </c>
-      <c r="CA4">
+      <c r="CA4" s="0">
         <f>BB4+BL4+BM4+BN4+BV4+BW4+BX4</f>
         <v/>
       </c>
-      <c r="CB4">
+      <c r="CB4" s="0">
         <f>0.9+(BB4+BL4+BV4)*0.01+K4*0.04</f>
         <v/>
       </c>
-      <c r="CC4">
+      <c r="CC4" s="0">
         <f>MIN(BE4,BO4,BY4)</f>
         <v/>
       </c>
-      <c r="CD4">
+      <c r="CD4" s="0">
         <f>CC4*24*1</f>
         <v/>
       </c>
-      <c r="CE4">
+      <c r="CE4" s="0">
         <f>ROUND(CD4*CB4,0)</f>
         <v/>
       </c>
-      <c r="CF4" t="n">
+      <c r="CF4" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="CG4">
+      <c r="CG4" s="0">
         <f>DC3+CF4</f>
         <v/>
       </c>
-      <c r="CH4" t="n">
+      <c r="CH4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CI4">
+      <c r="CI4" s="0">
         <f>DE3+CH4</f>
         <v/>
       </c>
-      <c r="CJ4" t="n">
+      <c r="CJ4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CK4">
+      <c r="CK4" s="0">
         <f>DG3+CJ4</f>
         <v/>
       </c>
-      <c r="CL4" t="n">
+      <c r="CL4" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="CM4">
+      <c r="CM4" s="0">
         <f>DJ3+CL4</f>
         <v/>
       </c>
-      <c r="CN4" t="n">
+      <c r="CN4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CO4">
+      <c r="CO4" s="0">
         <f>DL3+CN4</f>
         <v/>
       </c>
-      <c r="CP4" t="n">
+      <c r="CP4" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="CQ4">
+      <c r="CQ4" s="0">
         <f>DO3+CP4</f>
         <v/>
       </c>
-      <c r="CR4" t="n">
+      <c r="CR4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CS4">
+      <c r="CS4" s="0">
         <f>DQ3+CR4</f>
         <v/>
       </c>
-      <c r="CT4" t="n">
+      <c r="CT4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="CU4">
+      <c r="CU4" s="0">
         <f>DS3+CT4</f>
         <v/>
       </c>
-      <c r="CV4">
+      <c r="CV4" s="0">
         <f>(CG4)/0.3</f>
         <v/>
       </c>
-      <c r="CW4">
+      <c r="CW4" s="0">
         <f>(CM4)/1</f>
         <v/>
       </c>
-      <c r="CX4">
+      <c r="CX4" s="0">
         <f>(CQ4)/6</f>
         <v/>
       </c>
-      <c r="CY4">
+      <c r="CY4" s="0">
         <f>ROUNDDOWN(MIN(I4,CE4,CV4,CW4,CX4),0)</f>
         <v/>
       </c>
-      <c r="CZ4">
+      <c r="CZ4" s="0">
         <f>ROUNDDOWN(CY4*AU4,0)</f>
         <v/>
       </c>
-      <c r="DA4">
+      <c r="DA4" s="0">
         <f>CZ4*0.3</f>
         <v/>
       </c>
-      <c r="DB4">
+      <c r="DB4" s="0">
         <f>MIN(CG4,MAX(0,DA4))</f>
         <v/>
       </c>
-      <c r="DC4">
+      <c r="DC4" s="0">
         <f>CG4-DB4</f>
         <v/>
       </c>
-      <c r="DD4">
+      <c r="DD4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DE4">
+      <c r="DE4" s="0">
         <f>CI4-DD4</f>
         <v/>
       </c>
-      <c r="DF4">
+      <c r="DF4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DG4">
+      <c r="DG4" s="0">
         <f>CK4-DF4</f>
         <v/>
       </c>
-      <c r="DH4">
+      <c r="DH4" s="0">
         <f>CZ4*1</f>
         <v/>
       </c>
-      <c r="DI4">
+      <c r="DI4" s="0">
         <f>MIN(CM4,MAX(0,DH4))</f>
         <v/>
       </c>
-      <c r="DJ4">
+      <c r="DJ4" s="0">
         <f>CM4-DI4</f>
         <v/>
       </c>
-      <c r="DK4">
+      <c r="DK4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DL4">
+      <c r="DL4" s="0">
         <f>CO4-DK4</f>
         <v/>
       </c>
-      <c r="DM4">
+      <c r="DM4" s="0">
         <f>CZ4*6</f>
         <v/>
       </c>
-      <c r="DN4">
+      <c r="DN4" s="0">
         <f>MIN(CQ4,MAX(0,DM4))</f>
         <v/>
       </c>
-      <c r="DO4">
+      <c r="DO4" s="0">
         <f>CQ4-DN4</f>
         <v/>
       </c>
-      <c r="DP4">
+      <c r="DP4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DQ4">
+      <c r="DQ4" s="0">
         <f>CS4-DP4</f>
         <v/>
       </c>
-      <c r="DR4">
+      <c r="DR4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="DS4">
+      <c r="DS4" s="0">
         <f>CU4-DR4</f>
         <v/>
       </c>
-      <c r="DT4">
+      <c r="DT4" s="0">
         <f>((AV4+AW4+AX4)*IF(M4="NO_MYPE",'Costos De Producción'!V11,'Costos De Producción'!U11)+(AY4+AZ4+BA4)*IF(M4="NO_MYPE",'Costos De Producción'!V20,'Costos De Producción'!U20)+(BB4+BC4+BD4)*IF(M4="NO_MYPE",'Costos De Producción'!V29,'Costos De Producción'!U29)+(BF4+BG4+BH4)*IF(M4="NO_MYPE",'Costos De Producción'!Z11,'Costos De Producción'!Y11)+(BI4+BJ4+BK4)*IF(M4="NO_MYPE",'Costos De Producción'!Z20,'Costos De Producción'!Y20)+(BL4+BM4+BN4)*IF(M4="NO_MYPE",'Costos De Producción'!Z29,'Costos De Producción'!Y29)+(BP4+BQ4+BR4)*IF(M4="NO_MYPE",'Costos De Producción'!AD11,'Costos De Producción'!AC11)+(BS4+BT4+BU4)*IF(M4="NO_MYPE",'Costos De Producción'!AD20,'Costos De Producción'!AC20)+(BV4+BW4+BX4)*IF(M4="NO_MYPE",'Costos De Producción'!AD29,'Costos De Producción'!AC29)+K4*IF(M4="NO_MYPE",'Costos De Producción'!V39,'Costos De Producción'!U39)+IF(M4="NO_MYPE",'Costos De Producción'!Z39,'Costos De Producción'!Y39)+'Costos De Producción'!AC33)*1</f>
         <v/>
       </c>
-      <c r="DU4">
+      <c r="DU4" s="0">
         <f>(DB4*25+DD4*45+DF4*80+DI4*4+DK4*9+DN4*2+DP4*4+DR4*7)*0.9016000000000001</f>
         <v/>
       </c>
-      <c r="DV4">
+      <c r="DV4" s="0">
         <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
-      <c r="DW4">
+      <c r="DW4" s="0">
         <f>1*(2375.0*CZ4/100000)+1*(3325.0*CZ4/100000)+1*(1140.0*CZ4/100000)+1*(285.0*CZ4/100000)</f>
         <v/>
       </c>
-      <c r="DX4">
+      <c r="DX4" s="0">
         <f>IF(CZ4&gt;0,0,0)+IFERROR(CA4/BZ4,0)*10+(IFERROR(DF4/(DB4+DD4+DF4),0)+IFERROR(DK4/(DI4+DK4),0)+IFERROR(DR4/(DP4+DR4),0))/3*10+L4/10000*10</f>
         <v/>
       </c>
-      <c r="DY4">
+      <c r="DY4" s="0">
         <f>DX4+AJ4</f>
         <v/>
       </c>
-      <c r="DZ4">
+      <c r="DZ4" s="0">
         <f>EC3+CZ4</f>
         <v/>
       </c>
-      <c r="EA4" t="n">
+      <c r="EA4" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="EB4" t="n">
+      <c r="EB4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="EC4">
+      <c r="EC4" s="0">
         <f>DZ4-EJ4</f>
         <v/>
       </c>
-      <c r="ED4">
+      <c r="ED4" s="0">
         <f>IF(D4="SEG-01",IFERROR(100*(_xlfn.MAXIFS($J$2:$J$4,$C$2:$C$4,C4)-J4)/(_xlfn.MAXIFS($J$2:$J$4,$C$2:$C$4,C4)-_xlfn.MINIFS($J$2:$J$4,$C$2:$C$4,C4)),100),100-ABS(J4-EB4)/EB4*100)</f>
         <v/>
       </c>
-      <c r="EE4">
+      <c r="EE4" s="0">
         <f>ROUND(MIN(100,AI4*10),0)</f>
         <v/>
       </c>
-      <c r="EF4">
+      <c r="EF4" s="0">
         <f>0.7*ED4+0.2*DY4*10+0.1*EE4</f>
         <v/>
       </c>
-      <c r="EG4">
+      <c r="EG4" s="0">
         <f>IFERROR(EF4/SUMIF($C$2:$C$4,C4,$EF$2:$EF$4),0)</f>
         <v/>
       </c>
-      <c r="EH4">
+      <c r="EH4" s="0">
         <f>ROUND(EG4*EA4,0)</f>
         <v/>
       </c>
-      <c r="EI4">
+      <c r="EI4" s="0">
         <f>MAX(0,ROUNDDOWN(EH4*AN4*1,0))</f>
         <v/>
       </c>
-      <c r="EJ4">
+      <c r="EJ4" s="0">
         <f>MIN(DZ4,EI4)</f>
         <v/>
       </c>
-      <c r="EK4">
+      <c r="EK4" s="0">
         <f>EJ4*J4*AK4</f>
         <v/>
       </c>
-      <c r="EL4">
+      <c r="EL4" s="0">
         <f>EC4*2</f>
         <v/>
       </c>
-      <c r="EM4">
+      <c r="EM4" s="0">
         <f>IF(I4&gt;CE4,0.25*DT4*IFERROR(MIN(1,(I4-CE4)/CE4),1),0)</f>
         <v/>
       </c>
-      <c r="EN4">
+      <c r="EN4" s="0">
         <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-06A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)*EJ4</f>
         <v/>
       </c>
-      <c r="EO4">
+      <c r="EO4" s="0">
         <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-01A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("INS-12A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
-      <c r="EP4">
+      <c r="EP4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ4">
+      <c r="EQ4" s="0">
         <f>DT4+DU4+DV4+DW4+L4+EL4+EM4+EN4+EO4+EP4</f>
         <v/>
       </c>
-      <c r="ER4">
+      <c r="ER4" s="0">
         <f>EK4-EQ4</f>
         <v/>
       </c>
-      <c r="ES4">
+      <c r="ES4" s="0">
         <f>AND(D4="SEG-03",AI4&lt;4,I4&gt;0)</f>
         <v/>
       </c>
-      <c r="ET4">
+      <c r="ET4" s="0">
         <f>AND(D4="SEG-03",AI4&gt;=7,I4&gt;0)</f>
         <v/>
       </c>
-      <c r="EU4">
+      <c r="EU4" s="0">
         <f>AF4&lt;4</f>
         <v/>
       </c>
-      <c r="EV4">
+      <c r="EV4" s="0">
         <f>AM4&gt;=2</f>
         <v/>
       </c>
-      <c r="EW4">
+      <c r="EW4" s="0">
         <f>AH4&lt;3</f>
         <v/>
       </c>
-      <c r="EX4">
+      <c r="EX4" s="0">
         <f>I4&gt;CE4</f>
         <v/>
       </c>
-      <c r="EY4">
+      <c r="EY4" s="0">
         <f>CZ4&gt;EJ4</f>
         <v/>
       </c>
-      <c r="EZ4">
+      <c r="EZ4" s="0">
         <f>AND(K4=0,AF4&lt;5)</f>
+        <v/>
+      </c>
+      <c r="FA4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="FB4">
+        <f>0*2500*(1+0.03+0.02)+0*3500*(1+0.03+0.02)+0*1200*(1+0.03+0.02)+0*300*(1+0+0.01)</f>
+        <v/>
+      </c>
+      <c r="FC4">
+        <f>0*2500+0*3500+0*1200+0*300</f>
+        <v/>
+      </c>
+      <c r="FD4">
+        <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.9016000000000001</f>
+        <v/>
+      </c>
+      <c r="FE4">
+        <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.9016000000000001</f>
+        <v/>
+      </c>
+      <c r="FF4">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="FG4">
+        <f>(1+AR4/100)^(1/12)-1</f>
+        <v/>
+      </c>
+      <c r="FH4">
+        <f>AS3*FI3+AP4*FG4</f>
+        <v/>
+      </c>
+      <c r="FI4">
+        <f>IFERROR(FH4/(AS3+AP4),0)</f>
+        <v/>
+      </c>
+      <c r="FJ4">
+        <f>FH4*1</f>
+        <v/>
+      </c>
+      <c r="FK4">
+        <f>EQ4-DW4-DU4+FD4+FJ4</f>
+        <v/>
+      </c>
+      <c r="FL4">
+        <f>FF4+EK4+AP4-FK4-FB4</f>
+        <v/>
+      </c>
+      <c r="FM4">
+        <f>FM3+DW4</f>
+        <v/>
+      </c>
+      <c r="FN4">
+        <f>FN3+FC4</f>
+        <v/>
+      </c>
+      <c r="FO4">
+        <f>FN4-FM4</f>
+        <v/>
+      </c>
+      <c r="FP4">
+        <f>EK4</f>
+        <v/>
+      </c>
+      <c r="FQ4">
+        <f>EK4</f>
+        <v/>
+      </c>
+      <c r="FR4">
+        <f>EQ4+FJ4</f>
+        <v/>
+      </c>
+      <c r="FS4">
+        <f>ER4-FJ4</f>
+        <v/>
+      </c>
+      <c r="FT4">
+        <f>DW4</f>
+        <v/>
+      </c>
+      <c r="FU4">
+        <f>FJ4</f>
+        <v/>
+      </c>
+      <c r="FV4">
+        <f>EQ4</f>
+        <v/>
+      </c>
+      <c r="FW4">
+        <f>FF4</f>
+        <v/>
+      </c>
+      <c r="FX4">
+        <f>EK4+AP4</f>
+        <v/>
+      </c>
+      <c r="FY4">
+        <f>FK4+FB4</f>
+        <v/>
+      </c>
+      <c r="FZ4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GA4">
+        <f>FF4</f>
+        <v/>
+      </c>
+      <c r="GB4">
+        <f>EK4</f>
+        <v/>
+      </c>
+      <c r="GC4">
+        <f>FK4</f>
+        <v/>
+      </c>
+      <c r="GD4">
+        <f>FB4</f>
+        <v/>
+      </c>
+      <c r="GE4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GF4">
+        <f>EK4-FK4</f>
+        <v/>
+      </c>
+      <c r="GG4">
+        <f>-FB4</f>
+        <v/>
+      </c>
+      <c r="GH4">
+        <f>FL4-FF4</f>
+        <v/>
+      </c>
+      <c r="GI4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GJ4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GK4">
+        <f>FO4</f>
+        <v/>
+      </c>
+      <c r="GL4">
+        <f>FE4</f>
+        <v/>
+      </c>
+      <c r="GM4">
+        <f>FL4+FO4+FE4</f>
+        <v/>
+      </c>
+      <c r="GN4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GO4">
+        <f>FL4+FO4+FE4-AS4</f>
+        <v/>
+      </c>
+      <c r="GP4">
+        <f>FL4+FO4+FE4</f>
+        <v/>
+      </c>
+      <c r="GQ4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GR4">
+        <f>AR4</f>
+        <v/>
+      </c>
+      <c r="GS4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GT4">
+        <f>AT4</f>
+        <v/>
+      </c>
+      <c r="GU4">
+        <f>FI4</f>
+        <v/>
+      </c>
+      <c r="GV4">
+        <f>FJ4</f>
         <v/>
       </c>
     </row>
@@ -7100,3451 +7913,3451 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1">
+      <c r="A1" s="0">
         <f>'Catalogo_Decisiones'!A1</f>
         <v/>
       </c>
-      <c r="B1">
+      <c r="B1" s="0">
         <f>'Catalogo_Decisiones'!B1</f>
         <v/>
       </c>
-      <c r="C1">
+      <c r="C1" s="0">
         <f>'Catalogo_Decisiones'!C1</f>
         <v/>
       </c>
-      <c r="D1">
+      <c r="D1" s="0">
         <f>'Catalogo_Decisiones'!D1</f>
         <v/>
       </c>
-      <c r="E1">
+      <c r="E1" s="0">
         <f>'Catalogo_Decisiones'!E1</f>
         <v/>
       </c>
-      <c r="F1">
+      <c r="F1" s="0">
         <f>'Catalogo_Decisiones'!F1</f>
         <v/>
       </c>
-      <c r="G1">
+      <c r="G1" s="0">
         <f>'Catalogo_Decisiones'!G1</f>
         <v/>
       </c>
-      <c r="H1">
+      <c r="H1" s="0">
         <f>'Catalogo_Decisiones'!H1</f>
         <v/>
       </c>
-      <c r="I1">
+      <c r="I1" s="0">
         <f>'Catalogo_Decisiones'!I1</f>
         <v/>
       </c>
-      <c r="J1">
+      <c r="J1" s="0">
         <f>'Catalogo_Decisiones'!J1</f>
         <v/>
       </c>
-      <c r="K1">
+      <c r="K1" s="0">
         <f>'Catalogo_Decisiones'!K1</f>
         <v/>
       </c>
-      <c r="L1">
+      <c r="L1" s="0">
         <f>'Catalogo_Decisiones'!L1</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" s="0">
         <f>'Catalogo_Decisiones'!A2</f>
         <v/>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <f>'Catalogo_Decisiones'!B2</f>
         <v/>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <f>'Catalogo_Decisiones'!C2</f>
         <v/>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <f>'Catalogo_Decisiones'!D2</f>
         <v/>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <f>'Catalogo_Decisiones'!E2</f>
         <v/>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <f>'Catalogo_Decisiones'!F2</f>
         <v/>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G2,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <f>'Catalogo_Decisiones'!H2</f>
         <v/>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <f>'Catalogo_Decisiones'!I2</f>
         <v/>
       </c>
-      <c r="J2">
+      <c r="J2" s="0">
         <f>'Catalogo_Decisiones'!J2</f>
         <v/>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <f>'Catalogo_Decisiones'!K2</f>
         <v/>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <f>'Catalogo_Decisiones'!L2</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" s="0">
         <f>'Catalogo_Decisiones'!A3</f>
         <v/>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <f>'Catalogo_Decisiones'!B3</f>
         <v/>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <f>'Catalogo_Decisiones'!C3</f>
         <v/>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <f>'Catalogo_Decisiones'!D3</f>
         <v/>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <f>'Catalogo_Decisiones'!E3</f>
         <v/>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <f>'Catalogo_Decisiones'!F3</f>
         <v/>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G3,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <f>'Catalogo_Decisiones'!H3</f>
         <v/>
       </c>
-      <c r="I3">
+      <c r="I3" s="0">
         <f>'Catalogo_Decisiones'!I3</f>
         <v/>
       </c>
-      <c r="J3">
+      <c r="J3" s="0">
         <f>'Catalogo_Decisiones'!J3</f>
         <v/>
       </c>
-      <c r="K3">
+      <c r="K3" s="0">
         <f>'Catalogo_Decisiones'!K3</f>
         <v/>
       </c>
-      <c r="L3">
+      <c r="L3" s="0">
         <f>'Catalogo_Decisiones'!L3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" s="0">
         <f>'Catalogo_Decisiones'!A4</f>
         <v/>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <f>'Catalogo_Decisiones'!B4</f>
         <v/>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <f>'Catalogo_Decisiones'!C4</f>
         <v/>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <f>'Catalogo_Decisiones'!D4</f>
         <v/>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <f>'Catalogo_Decisiones'!E4</f>
         <v/>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <f>'Catalogo_Decisiones'!F4</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G4,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <f>'Catalogo_Decisiones'!H4</f>
         <v/>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <f>'Catalogo_Decisiones'!I4</f>
         <v/>
       </c>
-      <c r="J4">
+      <c r="J4" s="0">
         <f>'Catalogo_Decisiones'!J4</f>
         <v/>
       </c>
-      <c r="K4">
+      <c r="K4" s="0">
         <f>'Catalogo_Decisiones'!K4</f>
         <v/>
       </c>
-      <c r="L4">
+      <c r="L4" s="0">
         <f>'Catalogo_Decisiones'!L4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" s="0">
         <f>'Catalogo_Decisiones'!A5</f>
         <v/>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <f>'Catalogo_Decisiones'!B5</f>
         <v/>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <f>'Catalogo_Decisiones'!C5</f>
         <v/>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <f>'Catalogo_Decisiones'!D5</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <f>'Catalogo_Decisiones'!E5</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <f>'Catalogo_Decisiones'!F5</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G5,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <f>'Catalogo_Decisiones'!H5</f>
         <v/>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <f>'Catalogo_Decisiones'!I5</f>
         <v/>
       </c>
-      <c r="J5">
+      <c r="J5" s="0">
         <f>'Catalogo_Decisiones'!J5</f>
         <v/>
       </c>
-      <c r="K5">
+      <c r="K5" s="0">
         <f>'Catalogo_Decisiones'!K5</f>
         <v/>
       </c>
-      <c r="L5">
+      <c r="L5" s="0">
         <f>'Catalogo_Decisiones'!L5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" s="0">
         <f>'Catalogo_Decisiones'!A6</f>
         <v/>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <f>'Catalogo_Decisiones'!B6</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <f>'Catalogo_Decisiones'!C6</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <f>'Catalogo_Decisiones'!D6</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <f>'Catalogo_Decisiones'!E6</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <f>'Catalogo_Decisiones'!F6</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G6,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <f>'Catalogo_Decisiones'!H6</f>
         <v/>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <f>'Catalogo_Decisiones'!I6</f>
         <v/>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <f>'Catalogo_Decisiones'!J6</f>
         <v/>
       </c>
-      <c r="K6">
+      <c r="K6" s="0">
         <f>'Catalogo_Decisiones'!K6</f>
         <v/>
       </c>
-      <c r="L6">
+      <c r="L6" s="0">
         <f>'Catalogo_Decisiones'!L6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" s="0">
         <f>'Catalogo_Decisiones'!A7</f>
         <v/>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <f>'Catalogo_Decisiones'!B7</f>
         <v/>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <f>'Catalogo_Decisiones'!C7</f>
         <v/>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <f>'Catalogo_Decisiones'!D7</f>
         <v/>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <f>'Catalogo_Decisiones'!E7</f>
         <v/>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <f>'Catalogo_Decisiones'!F7</f>
         <v/>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G7,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <f>'Catalogo_Decisiones'!H7</f>
         <v/>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <f>'Catalogo_Decisiones'!I7</f>
         <v/>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <f>'Catalogo_Decisiones'!J7</f>
         <v/>
       </c>
-      <c r="K7">
+      <c r="K7" s="0">
         <f>'Catalogo_Decisiones'!K7</f>
         <v/>
       </c>
-      <c r="L7">
+      <c r="L7" s="0">
         <f>'Catalogo_Decisiones'!L7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" s="0">
         <f>'Catalogo_Decisiones'!A8</f>
         <v/>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <f>'Catalogo_Decisiones'!B8</f>
         <v/>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <f>'Catalogo_Decisiones'!C8</f>
         <v/>
       </c>
-      <c r="D8">
+      <c r="D8" s="0">
         <f>'Catalogo_Decisiones'!D8</f>
         <v/>
       </c>
-      <c r="E8">
+      <c r="E8" s="0">
         <f>'Catalogo_Decisiones'!E8</f>
         <v/>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <f>'Catalogo_Decisiones'!F8</f>
         <v/>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G8,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="H8" s="0">
         <f>'Catalogo_Decisiones'!H8</f>
         <v/>
       </c>
-      <c r="I8">
+      <c r="I8" s="0">
         <f>'Catalogo_Decisiones'!I8</f>
         <v/>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <f>'Catalogo_Decisiones'!J8</f>
         <v/>
       </c>
-      <c r="K8">
+      <c r="K8" s="0">
         <f>'Catalogo_Decisiones'!K8</f>
         <v/>
       </c>
-      <c r="L8">
+      <c r="L8" s="0">
         <f>'Catalogo_Decisiones'!L8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" s="0">
         <f>'Catalogo_Decisiones'!A9</f>
         <v/>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <f>'Catalogo_Decisiones'!B9</f>
         <v/>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <f>'Catalogo_Decisiones'!C9</f>
         <v/>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <f>'Catalogo_Decisiones'!D9</f>
         <v/>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <f>'Catalogo_Decisiones'!E9</f>
         <v/>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <f>'Catalogo_Decisiones'!F9</f>
         <v/>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G9,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <f>'Catalogo_Decisiones'!H9</f>
         <v/>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <f>'Catalogo_Decisiones'!I9</f>
         <v/>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <f>'Catalogo_Decisiones'!J9</f>
         <v/>
       </c>
-      <c r="K9">
+      <c r="K9" s="0">
         <f>'Catalogo_Decisiones'!K9</f>
         <v/>
       </c>
-      <c r="L9">
+      <c r="L9" s="0">
         <f>'Catalogo_Decisiones'!L9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" s="0">
         <f>'Catalogo_Decisiones'!A10</f>
         <v/>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <f>'Catalogo_Decisiones'!B10</f>
         <v/>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <f>'Catalogo_Decisiones'!C10</f>
         <v/>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <f>'Catalogo_Decisiones'!D10</f>
         <v/>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <f>'Catalogo_Decisiones'!E10</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <f>'Catalogo_Decisiones'!F10</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="G10" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G10,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H10">
+      <c r="H10" s="0">
         <f>'Catalogo_Decisiones'!H10</f>
         <v/>
       </c>
-      <c r="I10">
+      <c r="I10" s="0">
         <f>'Catalogo_Decisiones'!I10</f>
         <v/>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <f>'Catalogo_Decisiones'!J10</f>
         <v/>
       </c>
-      <c r="K10">
+      <c r="K10" s="0">
         <f>'Catalogo_Decisiones'!K10</f>
         <v/>
       </c>
-      <c r="L10">
+      <c r="L10" s="0">
         <f>'Catalogo_Decisiones'!L10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" s="0">
         <f>'Catalogo_Decisiones'!A11</f>
         <v/>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <f>'Catalogo_Decisiones'!B11</f>
         <v/>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <f>'Catalogo_Decisiones'!C11</f>
         <v/>
       </c>
-      <c r="D11">
+      <c r="D11" s="0">
         <f>'Catalogo_Decisiones'!D11</f>
         <v/>
       </c>
-      <c r="E11">
+      <c r="E11" s="0">
         <f>'Catalogo_Decisiones'!E11</f>
         <v/>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <f>'Catalogo_Decisiones'!F11</f>
         <v/>
       </c>
-      <c r="G11">
+      <c r="G11" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G11,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="H11" s="0">
         <f>'Catalogo_Decisiones'!H11</f>
         <v/>
       </c>
-      <c r="I11">
+      <c r="I11" s="0">
         <f>'Catalogo_Decisiones'!I11</f>
         <v/>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <f>'Catalogo_Decisiones'!J11</f>
         <v/>
       </c>
-      <c r="K11">
+      <c r="K11" s="0">
         <f>'Catalogo_Decisiones'!K11</f>
         <v/>
       </c>
-      <c r="L11">
+      <c r="L11" s="0">
         <f>'Catalogo_Decisiones'!L11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" s="0">
         <f>'Catalogo_Decisiones'!A12</f>
         <v/>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <f>'Catalogo_Decisiones'!B12</f>
         <v/>
       </c>
-      <c r="C12">
+      <c r="C12" s="0">
         <f>'Catalogo_Decisiones'!C12</f>
         <v/>
       </c>
-      <c r="D12">
+      <c r="D12" s="0">
         <f>'Catalogo_Decisiones'!D12</f>
         <v/>
       </c>
-      <c r="E12">
+      <c r="E12" s="0">
         <f>'Catalogo_Decisiones'!E12</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="0">
         <f>'Catalogo_Decisiones'!F12</f>
         <v/>
       </c>
-      <c r="G12">
+      <c r="G12" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G12,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="H12" s="0">
         <f>'Catalogo_Decisiones'!H12</f>
         <v/>
       </c>
-      <c r="I12">
+      <c r="I12" s="0">
         <f>'Catalogo_Decisiones'!I12</f>
         <v/>
       </c>
-      <c r="J12">
+      <c r="J12" s="0">
         <f>'Catalogo_Decisiones'!J12</f>
         <v/>
       </c>
-      <c r="K12">
+      <c r="K12" s="0">
         <f>'Catalogo_Decisiones'!K12</f>
         <v/>
       </c>
-      <c r="L12">
+      <c r="L12" s="0">
         <f>'Catalogo_Decisiones'!L12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" s="0">
         <f>'Catalogo_Decisiones'!A13</f>
         <v/>
       </c>
-      <c r="B13">
+      <c r="B13" s="0">
         <f>'Catalogo_Decisiones'!B13</f>
         <v/>
       </c>
-      <c r="C13">
+      <c r="C13" s="0">
         <f>'Catalogo_Decisiones'!C13</f>
         <v/>
       </c>
-      <c r="D13">
+      <c r="D13" s="0">
         <f>'Catalogo_Decisiones'!D13</f>
         <v/>
       </c>
-      <c r="E13">
+      <c r="E13" s="0">
         <f>'Catalogo_Decisiones'!E13</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="F13" s="0">
         <f>'Catalogo_Decisiones'!F13</f>
         <v/>
       </c>
-      <c r="G13">
+      <c r="G13" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G13,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H13">
+      <c r="H13" s="0">
         <f>'Catalogo_Decisiones'!H13</f>
         <v/>
       </c>
-      <c r="I13">
+      <c r="I13" s="0">
         <f>'Catalogo_Decisiones'!I13</f>
         <v/>
       </c>
-      <c r="J13">
+      <c r="J13" s="0">
         <f>'Catalogo_Decisiones'!J13</f>
         <v/>
       </c>
-      <c r="K13">
+      <c r="K13" s="0">
         <f>'Catalogo_Decisiones'!K13</f>
         <v/>
       </c>
-      <c r="L13">
+      <c r="L13" s="0">
         <f>'Catalogo_Decisiones'!L13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" s="0">
         <f>'Catalogo_Decisiones'!A14</f>
         <v/>
       </c>
-      <c r="B14">
+      <c r="B14" s="0">
         <f>'Catalogo_Decisiones'!B14</f>
         <v/>
       </c>
-      <c r="C14">
+      <c r="C14" s="0">
         <f>'Catalogo_Decisiones'!C14</f>
         <v/>
       </c>
-      <c r="D14">
+      <c r="D14" s="0">
         <f>'Catalogo_Decisiones'!D14</f>
         <v/>
       </c>
-      <c r="E14">
+      <c r="E14" s="0">
         <f>'Catalogo_Decisiones'!E14</f>
         <v/>
       </c>
-      <c r="F14">
+      <c r="F14" s="0">
         <f>'Catalogo_Decisiones'!F14</f>
         <v/>
       </c>
-      <c r="G14">
+      <c r="G14" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G14,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H14">
+      <c r="H14" s="0">
         <f>'Catalogo_Decisiones'!H14</f>
         <v/>
       </c>
-      <c r="I14">
+      <c r="I14" s="0">
         <f>'Catalogo_Decisiones'!I14</f>
         <v/>
       </c>
-      <c r="J14">
+      <c r="J14" s="0">
         <f>'Catalogo_Decisiones'!J14</f>
         <v/>
       </c>
-      <c r="K14">
+      <c r="K14" s="0">
         <f>'Catalogo_Decisiones'!K14</f>
         <v/>
       </c>
-      <c r="L14">
+      <c r="L14" s="0">
         <f>'Catalogo_Decisiones'!L14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" s="0">
         <f>'Catalogo_Decisiones'!A15</f>
         <v/>
       </c>
-      <c r="B15">
+      <c r="B15" s="0">
         <f>'Catalogo_Decisiones'!B15</f>
         <v/>
       </c>
-      <c r="C15">
+      <c r="C15" s="0">
         <f>'Catalogo_Decisiones'!C15</f>
         <v/>
       </c>
-      <c r="D15">
+      <c r="D15" s="0">
         <f>'Catalogo_Decisiones'!D15</f>
         <v/>
       </c>
-      <c r="E15">
+      <c r="E15" s="0">
         <f>'Catalogo_Decisiones'!E15</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F15" s="0">
         <f>'Catalogo_Decisiones'!F15</f>
         <v/>
       </c>
-      <c r="G15">
+      <c r="G15" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G15,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H15">
+      <c r="H15" s="0">
         <f>'Catalogo_Decisiones'!H15</f>
         <v/>
       </c>
-      <c r="I15">
+      <c r="I15" s="0">
         <f>'Catalogo_Decisiones'!I15</f>
         <v/>
       </c>
-      <c r="J15">
+      <c r="J15" s="0">
         <f>'Catalogo_Decisiones'!J15</f>
         <v/>
       </c>
-      <c r="K15">
+      <c r="K15" s="0">
         <f>'Catalogo_Decisiones'!K15</f>
         <v/>
       </c>
-      <c r="L15">
+      <c r="L15" s="0">
         <f>'Catalogo_Decisiones'!L15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" s="0">
         <f>'Catalogo_Decisiones'!A16</f>
         <v/>
       </c>
-      <c r="B16">
+      <c r="B16" s="0">
         <f>'Catalogo_Decisiones'!B16</f>
         <v/>
       </c>
-      <c r="C16">
+      <c r="C16" s="0">
         <f>'Catalogo_Decisiones'!C16</f>
         <v/>
       </c>
-      <c r="D16">
+      <c r="D16" s="0">
         <f>'Catalogo_Decisiones'!D16</f>
         <v/>
       </c>
-      <c r="E16">
+      <c r="E16" s="0">
         <f>'Catalogo_Decisiones'!E16</f>
         <v/>
       </c>
-      <c r="F16">
+      <c r="F16" s="0">
         <f>'Catalogo_Decisiones'!F16</f>
         <v/>
       </c>
-      <c r="G16">
+      <c r="G16" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G16,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H16">
+      <c r="H16" s="0">
         <f>'Catalogo_Decisiones'!H16</f>
         <v/>
       </c>
-      <c r="I16">
+      <c r="I16" s="0">
         <f>'Catalogo_Decisiones'!I16</f>
         <v/>
       </c>
-      <c r="J16">
+      <c r="J16" s="0">
         <f>'Catalogo_Decisiones'!J16</f>
         <v/>
       </c>
-      <c r="K16">
+      <c r="K16" s="0">
         <f>'Catalogo_Decisiones'!K16</f>
         <v/>
       </c>
-      <c r="L16">
+      <c r="L16" s="0">
         <f>'Catalogo_Decisiones'!L16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" s="0">
         <f>'Catalogo_Decisiones'!A17</f>
         <v/>
       </c>
-      <c r="B17">
+      <c r="B17" s="0">
         <f>'Catalogo_Decisiones'!B17</f>
         <v/>
       </c>
-      <c r="C17">
+      <c r="C17" s="0">
         <f>'Catalogo_Decisiones'!C17</f>
         <v/>
       </c>
-      <c r="D17">
+      <c r="D17" s="0">
         <f>'Catalogo_Decisiones'!D17</f>
         <v/>
       </c>
-      <c r="E17">
+      <c r="E17" s="0">
         <f>'Catalogo_Decisiones'!E17</f>
         <v/>
       </c>
-      <c r="F17">
+      <c r="F17" s="0">
         <f>'Catalogo_Decisiones'!F17</f>
         <v/>
       </c>
-      <c r="G17">
+      <c r="G17" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G17,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H17">
+      <c r="H17" s="0">
         <f>'Catalogo_Decisiones'!H17</f>
         <v/>
       </c>
-      <c r="I17">
+      <c r="I17" s="0">
         <f>'Catalogo_Decisiones'!I17</f>
         <v/>
       </c>
-      <c r="J17">
+      <c r="J17" s="0">
         <f>'Catalogo_Decisiones'!J17</f>
         <v/>
       </c>
-      <c r="K17">
+      <c r="K17" s="0">
         <f>'Catalogo_Decisiones'!K17</f>
         <v/>
       </c>
-      <c r="L17">
+      <c r="L17" s="0">
         <f>'Catalogo_Decisiones'!L17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
+      <c r="A18" s="0">
         <f>'Catalogo_Decisiones'!A18</f>
         <v/>
       </c>
-      <c r="B18">
+      <c r="B18" s="0">
         <f>'Catalogo_Decisiones'!B18</f>
         <v/>
       </c>
-      <c r="C18">
+      <c r="C18" s="0">
         <f>'Catalogo_Decisiones'!C18</f>
         <v/>
       </c>
-      <c r="D18">
+      <c r="D18" s="0">
         <f>'Catalogo_Decisiones'!D18</f>
         <v/>
       </c>
-      <c r="E18">
+      <c r="E18" s="0">
         <f>'Catalogo_Decisiones'!E18</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="F18" s="0">
         <f>'Catalogo_Decisiones'!F18</f>
         <v/>
       </c>
-      <c r="G18">
+      <c r="G18" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G18,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H18">
+      <c r="H18" s="0">
         <f>'Catalogo_Decisiones'!H18</f>
         <v/>
       </c>
-      <c r="I18">
+      <c r="I18" s="0">
         <f>'Catalogo_Decisiones'!I18</f>
         <v/>
       </c>
-      <c r="J18">
+      <c r="J18" s="0">
         <f>'Catalogo_Decisiones'!J18</f>
         <v/>
       </c>
-      <c r="K18">
+      <c r="K18" s="0">
         <f>'Catalogo_Decisiones'!K18</f>
         <v/>
       </c>
-      <c r="L18">
+      <c r="L18" s="0">
         <f>'Catalogo_Decisiones'!L18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" s="0">
         <f>'Catalogo_Decisiones'!A19</f>
         <v/>
       </c>
-      <c r="B19">
+      <c r="B19" s="0">
         <f>'Catalogo_Decisiones'!B19</f>
         <v/>
       </c>
-      <c r="C19">
+      <c r="C19" s="0">
         <f>'Catalogo_Decisiones'!C19</f>
         <v/>
       </c>
-      <c r="D19">
+      <c r="D19" s="0">
         <f>'Catalogo_Decisiones'!D19</f>
         <v/>
       </c>
-      <c r="E19">
+      <c r="E19" s="0">
         <f>'Catalogo_Decisiones'!E19</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="F19" s="0">
         <f>'Catalogo_Decisiones'!F19</f>
         <v/>
       </c>
-      <c r="G19">
+      <c r="G19" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G19,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H19">
+      <c r="H19" s="0">
         <f>'Catalogo_Decisiones'!H19</f>
         <v/>
       </c>
-      <c r="I19">
+      <c r="I19" s="0">
         <f>'Catalogo_Decisiones'!I19</f>
         <v/>
       </c>
-      <c r="J19">
+      <c r="J19" s="0">
         <f>'Catalogo_Decisiones'!J19</f>
         <v/>
       </c>
-      <c r="K19">
+      <c r="K19" s="0">
         <f>'Catalogo_Decisiones'!K19</f>
         <v/>
       </c>
-      <c r="L19">
+      <c r="L19" s="0">
         <f>'Catalogo_Decisiones'!L19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
+      <c r="A20" s="0">
         <f>'Catalogo_Decisiones'!A20</f>
         <v/>
       </c>
-      <c r="B20">
+      <c r="B20" s="0">
         <f>'Catalogo_Decisiones'!B20</f>
         <v/>
       </c>
-      <c r="C20">
+      <c r="C20" s="0">
         <f>'Catalogo_Decisiones'!C20</f>
         <v/>
       </c>
-      <c r="D20">
+      <c r="D20" s="0">
         <f>'Catalogo_Decisiones'!D20</f>
         <v/>
       </c>
-      <c r="E20">
+      <c r="E20" s="0">
         <f>'Catalogo_Decisiones'!E20</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F20" s="0">
         <f>'Catalogo_Decisiones'!F20</f>
         <v/>
       </c>
-      <c r="G20">
+      <c r="G20" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G20,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H20">
+      <c r="H20" s="0">
         <f>'Catalogo_Decisiones'!H20</f>
         <v/>
       </c>
-      <c r="I20">
+      <c r="I20" s="0">
         <f>'Catalogo_Decisiones'!I20</f>
         <v/>
       </c>
-      <c r="J20">
+      <c r="J20" s="0">
         <f>'Catalogo_Decisiones'!J20</f>
         <v/>
       </c>
-      <c r="K20">
+      <c r="K20" s="0">
         <f>'Catalogo_Decisiones'!K20</f>
         <v/>
       </c>
-      <c r="L20">
+      <c r="L20" s="0">
         <f>'Catalogo_Decisiones'!L20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" s="0">
         <f>'Catalogo_Decisiones'!A21</f>
         <v/>
       </c>
-      <c r="B21">
+      <c r="B21" s="0">
         <f>'Catalogo_Decisiones'!B21</f>
         <v/>
       </c>
-      <c r="C21">
+      <c r="C21" s="0">
         <f>'Catalogo_Decisiones'!C21</f>
         <v/>
       </c>
-      <c r="D21">
+      <c r="D21" s="0">
         <f>'Catalogo_Decisiones'!D21</f>
         <v/>
       </c>
-      <c r="E21">
+      <c r="E21" s="0">
         <f>'Catalogo_Decisiones'!E21</f>
         <v/>
       </c>
-      <c r="F21">
+      <c r="F21" s="0">
         <f>'Catalogo_Decisiones'!F21</f>
         <v/>
       </c>
-      <c r="G21">
+      <c r="G21" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G21,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H21">
+      <c r="H21" s="0">
         <f>'Catalogo_Decisiones'!H21</f>
         <v/>
       </c>
-      <c r="I21">
+      <c r="I21" s="0">
         <f>'Catalogo_Decisiones'!I21</f>
         <v/>
       </c>
-      <c r="J21">
+      <c r="J21" s="0">
         <f>'Catalogo_Decisiones'!J21</f>
         <v/>
       </c>
-      <c r="K21">
+      <c r="K21" s="0">
         <f>'Catalogo_Decisiones'!K21</f>
         <v/>
       </c>
-      <c r="L21">
+      <c r="L21" s="0">
         <f>'Catalogo_Decisiones'!L21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
+      <c r="A22" s="0">
         <f>'Catalogo_Decisiones'!A22</f>
         <v/>
       </c>
-      <c r="B22">
+      <c r="B22" s="0">
         <f>'Catalogo_Decisiones'!B22</f>
         <v/>
       </c>
-      <c r="C22">
+      <c r="C22" s="0">
         <f>'Catalogo_Decisiones'!C22</f>
         <v/>
       </c>
-      <c r="D22">
+      <c r="D22" s="0">
         <f>'Catalogo_Decisiones'!D22</f>
         <v/>
       </c>
-      <c r="E22">
+      <c r="E22" s="0">
         <f>'Catalogo_Decisiones'!E22</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="F22" s="0">
         <f>'Catalogo_Decisiones'!F22</f>
         <v/>
       </c>
-      <c r="G22">
+      <c r="G22" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G22,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H22">
+      <c r="H22" s="0">
         <f>'Catalogo_Decisiones'!H22</f>
         <v/>
       </c>
-      <c r="I22">
+      <c r="I22" s="0">
         <f>'Catalogo_Decisiones'!I22</f>
         <v/>
       </c>
-      <c r="J22">
+      <c r="J22" s="0">
         <f>'Catalogo_Decisiones'!J22</f>
         <v/>
       </c>
-      <c r="K22">
+      <c r="K22" s="0">
         <f>'Catalogo_Decisiones'!K22</f>
         <v/>
       </c>
-      <c r="L22">
+      <c r="L22" s="0">
         <f>'Catalogo_Decisiones'!L22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
+      <c r="A23" s="0">
         <f>'Catalogo_Decisiones'!A23</f>
         <v/>
       </c>
-      <c r="B23">
+      <c r="B23" s="0">
         <f>'Catalogo_Decisiones'!B23</f>
         <v/>
       </c>
-      <c r="C23">
+      <c r="C23" s="0">
         <f>'Catalogo_Decisiones'!C23</f>
         <v/>
       </c>
-      <c r="D23">
+      <c r="D23" s="0">
         <f>'Catalogo_Decisiones'!D23</f>
         <v/>
       </c>
-      <c r="E23">
+      <c r="E23" s="0">
         <f>'Catalogo_Decisiones'!E23</f>
         <v/>
       </c>
-      <c r="F23">
+      <c r="F23" s="0">
         <f>'Catalogo_Decisiones'!F23</f>
         <v/>
       </c>
-      <c r="G23">
+      <c r="G23" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G23,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H23">
+      <c r="H23" s="0">
         <f>'Catalogo_Decisiones'!H23</f>
         <v/>
       </c>
-      <c r="I23">
+      <c r="I23" s="0">
         <f>'Catalogo_Decisiones'!I23</f>
         <v/>
       </c>
-      <c r="J23">
+      <c r="J23" s="0">
         <f>'Catalogo_Decisiones'!J23</f>
         <v/>
       </c>
-      <c r="K23">
+      <c r="K23" s="0">
         <f>'Catalogo_Decisiones'!K23</f>
         <v/>
       </c>
-      <c r="L23">
+      <c r="L23" s="0">
         <f>'Catalogo_Decisiones'!L23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
+      <c r="A24" s="0">
         <f>'Catalogo_Decisiones'!A24</f>
         <v/>
       </c>
-      <c r="B24">
+      <c r="B24" s="0">
         <f>'Catalogo_Decisiones'!B24</f>
         <v/>
       </c>
-      <c r="C24">
+      <c r="C24" s="0">
         <f>'Catalogo_Decisiones'!C24</f>
         <v/>
       </c>
-      <c r="D24">
+      <c r="D24" s="0">
         <f>'Catalogo_Decisiones'!D24</f>
         <v/>
       </c>
-      <c r="E24">
+      <c r="E24" s="0">
         <f>'Catalogo_Decisiones'!E24</f>
         <v/>
       </c>
-      <c r="F24">
+      <c r="F24" s="0">
         <f>'Catalogo_Decisiones'!F24</f>
         <v/>
       </c>
-      <c r="G24">
+      <c r="G24" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G24,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H24">
+      <c r="H24" s="0">
         <f>'Catalogo_Decisiones'!H24</f>
         <v/>
       </c>
-      <c r="I24">
+      <c r="I24" s="0">
         <f>'Catalogo_Decisiones'!I24</f>
         <v/>
       </c>
-      <c r="J24">
+      <c r="J24" s="0">
         <f>'Catalogo_Decisiones'!J24</f>
         <v/>
       </c>
-      <c r="K24">
+      <c r="K24" s="0">
         <f>'Catalogo_Decisiones'!K24</f>
         <v/>
       </c>
-      <c r="L24">
+      <c r="L24" s="0">
         <f>'Catalogo_Decisiones'!L24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
+      <c r="A25" s="0">
         <f>'Catalogo_Decisiones'!A25</f>
         <v/>
       </c>
-      <c r="B25">
+      <c r="B25" s="0">
         <f>'Catalogo_Decisiones'!B25</f>
         <v/>
       </c>
-      <c r="C25">
+      <c r="C25" s="0">
         <f>'Catalogo_Decisiones'!C25</f>
         <v/>
       </c>
-      <c r="D25">
+      <c r="D25" s="0">
         <f>'Catalogo_Decisiones'!D25</f>
         <v/>
       </c>
-      <c r="E25">
+      <c r="E25" s="0">
         <f>'Catalogo_Decisiones'!E25</f>
         <v/>
       </c>
-      <c r="F25">
+      <c r="F25" s="0">
         <f>'Catalogo_Decisiones'!F25</f>
         <v/>
       </c>
-      <c r="G25">
+      <c r="G25" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G25,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H25">
+      <c r="H25" s="0">
         <f>'Catalogo_Decisiones'!H25</f>
         <v/>
       </c>
-      <c r="I25">
+      <c r="I25" s="0">
         <f>'Catalogo_Decisiones'!I25</f>
         <v/>
       </c>
-      <c r="J25">
+      <c r="J25" s="0">
         <f>'Catalogo_Decisiones'!J25</f>
         <v/>
       </c>
-      <c r="K25">
+      <c r="K25" s="0">
         <f>'Catalogo_Decisiones'!K25</f>
         <v/>
       </c>
-      <c r="L25">
+      <c r="L25" s="0">
         <f>'Catalogo_Decisiones'!L25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
+      <c r="A26" s="0">
         <f>'Catalogo_Decisiones'!A26</f>
         <v/>
       </c>
-      <c r="B26">
+      <c r="B26" s="0">
         <f>'Catalogo_Decisiones'!B26</f>
         <v/>
       </c>
-      <c r="C26">
+      <c r="C26" s="0">
         <f>'Catalogo_Decisiones'!C26</f>
         <v/>
       </c>
-      <c r="D26">
+      <c r="D26" s="0">
         <f>'Catalogo_Decisiones'!D26</f>
         <v/>
       </c>
-      <c r="E26">
+      <c r="E26" s="0">
         <f>'Catalogo_Decisiones'!E26</f>
         <v/>
       </c>
-      <c r="F26">
+      <c r="F26" s="0">
         <f>'Catalogo_Decisiones'!F26</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G26" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G26,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H26">
+      <c r="H26" s="0">
         <f>'Catalogo_Decisiones'!H26</f>
         <v/>
       </c>
-      <c r="I26">
+      <c r="I26" s="0">
         <f>'Catalogo_Decisiones'!I26</f>
         <v/>
       </c>
-      <c r="J26">
+      <c r="J26" s="0">
         <f>'Catalogo_Decisiones'!J26</f>
         <v/>
       </c>
-      <c r="K26">
+      <c r="K26" s="0">
         <f>'Catalogo_Decisiones'!K26</f>
         <v/>
       </c>
-      <c r="L26">
+      <c r="L26" s="0">
         <f>'Catalogo_Decisiones'!L26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
+      <c r="A27" s="0">
         <f>'Catalogo_Decisiones'!A27</f>
         <v/>
       </c>
-      <c r="B27">
+      <c r="B27" s="0">
         <f>'Catalogo_Decisiones'!B27</f>
         <v/>
       </c>
-      <c r="C27">
+      <c r="C27" s="0">
         <f>'Catalogo_Decisiones'!C27</f>
         <v/>
       </c>
-      <c r="D27">
+      <c r="D27" s="0">
         <f>'Catalogo_Decisiones'!D27</f>
         <v/>
       </c>
-      <c r="E27">
+      <c r="E27" s="0">
         <f>'Catalogo_Decisiones'!E27</f>
         <v/>
       </c>
-      <c r="F27">
+      <c r="F27" s="0">
         <f>'Catalogo_Decisiones'!F27</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G27" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G27,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H27">
+      <c r="H27" s="0">
         <f>'Catalogo_Decisiones'!H27</f>
         <v/>
       </c>
-      <c r="I27">
+      <c r="I27" s="0">
         <f>'Catalogo_Decisiones'!I27</f>
         <v/>
       </c>
-      <c r="J27">
+      <c r="J27" s="0">
         <f>'Catalogo_Decisiones'!J27</f>
         <v/>
       </c>
-      <c r="K27">
+      <c r="K27" s="0">
         <f>'Catalogo_Decisiones'!K27</f>
         <v/>
       </c>
-      <c r="L27">
+      <c r="L27" s="0">
         <f>'Catalogo_Decisiones'!L27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
+      <c r="A28" s="0">
         <f>'Catalogo_Decisiones'!A28</f>
         <v/>
       </c>
-      <c r="B28">
+      <c r="B28" s="0">
         <f>'Catalogo_Decisiones'!B28</f>
         <v/>
       </c>
-      <c r="C28">
+      <c r="C28" s="0">
         <f>'Catalogo_Decisiones'!C28</f>
         <v/>
       </c>
-      <c r="D28">
+      <c r="D28" s="0">
         <f>'Catalogo_Decisiones'!D28</f>
         <v/>
       </c>
-      <c r="E28">
+      <c r="E28" s="0">
         <f>'Catalogo_Decisiones'!E28</f>
         <v/>
       </c>
-      <c r="F28">
+      <c r="F28" s="0">
         <f>'Catalogo_Decisiones'!F28</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G28" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G28,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H28">
+      <c r="H28" s="0">
         <f>'Catalogo_Decisiones'!H28</f>
         <v/>
       </c>
-      <c r="I28">
+      <c r="I28" s="0">
         <f>'Catalogo_Decisiones'!I28</f>
         <v/>
       </c>
-      <c r="J28">
+      <c r="J28" s="0">
         <f>'Catalogo_Decisiones'!J28</f>
         <v/>
       </c>
-      <c r="K28">
+      <c r="K28" s="0">
         <f>'Catalogo_Decisiones'!K28</f>
         <v/>
       </c>
-      <c r="L28">
+      <c r="L28" s="0">
         <f>'Catalogo_Decisiones'!L28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
+      <c r="A29" s="0">
         <f>'Catalogo_Decisiones'!A29</f>
         <v/>
       </c>
-      <c r="B29">
+      <c r="B29" s="0">
         <f>'Catalogo_Decisiones'!B29</f>
         <v/>
       </c>
-      <c r="C29">
+      <c r="C29" s="0">
         <f>'Catalogo_Decisiones'!C29</f>
         <v/>
       </c>
-      <c r="D29">
+      <c r="D29" s="0">
         <f>'Catalogo_Decisiones'!D29</f>
         <v/>
       </c>
-      <c r="E29">
+      <c r="E29" s="0">
         <f>'Catalogo_Decisiones'!E29</f>
         <v/>
       </c>
-      <c r="F29">
+      <c r="F29" s="0">
         <f>'Catalogo_Decisiones'!F29</f>
         <v/>
       </c>
-      <c r="G29">
+      <c r="G29" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G29,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H29">
+      <c r="H29" s="0">
         <f>'Catalogo_Decisiones'!H29</f>
         <v/>
       </c>
-      <c r="I29">
+      <c r="I29" s="0">
         <f>'Catalogo_Decisiones'!I29</f>
         <v/>
       </c>
-      <c r="J29">
+      <c r="J29" s="0">
         <f>'Catalogo_Decisiones'!J29</f>
         <v/>
       </c>
-      <c r="K29">
+      <c r="K29" s="0">
         <f>'Catalogo_Decisiones'!K29</f>
         <v/>
       </c>
-      <c r="L29">
+      <c r="L29" s="0">
         <f>'Catalogo_Decisiones'!L29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" s="0">
         <f>'Catalogo_Decisiones'!A30</f>
         <v/>
       </c>
-      <c r="B30">
+      <c r="B30" s="0">
         <f>'Catalogo_Decisiones'!B30</f>
         <v/>
       </c>
-      <c r="C30">
+      <c r="C30" s="0">
         <f>'Catalogo_Decisiones'!C30</f>
         <v/>
       </c>
-      <c r="D30">
+      <c r="D30" s="0">
         <f>'Catalogo_Decisiones'!D30</f>
         <v/>
       </c>
-      <c r="E30">
+      <c r="E30" s="0">
         <f>'Catalogo_Decisiones'!E30</f>
         <v/>
       </c>
-      <c r="F30">
+      <c r="F30" s="0">
         <f>'Catalogo_Decisiones'!F30</f>
         <v/>
       </c>
-      <c r="G30">
+      <c r="G30" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G30,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H30">
+      <c r="H30" s="0">
         <f>'Catalogo_Decisiones'!H30</f>
         <v/>
       </c>
-      <c r="I30">
+      <c r="I30" s="0">
         <f>'Catalogo_Decisiones'!I30</f>
         <v/>
       </c>
-      <c r="J30">
+      <c r="J30" s="0">
         <f>'Catalogo_Decisiones'!J30</f>
         <v/>
       </c>
-      <c r="K30">
+      <c r="K30" s="0">
         <f>'Catalogo_Decisiones'!K30</f>
         <v/>
       </c>
-      <c r="L30">
+      <c r="L30" s="0">
         <f>'Catalogo_Decisiones'!L30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" s="0">
         <f>'Catalogo_Decisiones'!A31</f>
         <v/>
       </c>
-      <c r="B31">
+      <c r="B31" s="0">
         <f>'Catalogo_Decisiones'!B31</f>
         <v/>
       </c>
-      <c r="C31">
+      <c r="C31" s="0">
         <f>'Catalogo_Decisiones'!C31</f>
         <v/>
       </c>
-      <c r="D31">
+      <c r="D31" s="0">
         <f>'Catalogo_Decisiones'!D31</f>
         <v/>
       </c>
-      <c r="E31">
+      <c r="E31" s="0">
         <f>'Catalogo_Decisiones'!E31</f>
         <v/>
       </c>
-      <c r="F31">
+      <c r="F31" s="0">
         <f>'Catalogo_Decisiones'!F31</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G31" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G31,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H31">
+      <c r="H31" s="0">
         <f>'Catalogo_Decisiones'!H31</f>
         <v/>
       </c>
-      <c r="I31">
+      <c r="I31" s="0">
         <f>'Catalogo_Decisiones'!I31</f>
         <v/>
       </c>
-      <c r="J31">
+      <c r="J31" s="0">
         <f>'Catalogo_Decisiones'!J31</f>
         <v/>
       </c>
-      <c r="K31">
+      <c r="K31" s="0">
         <f>'Catalogo_Decisiones'!K31</f>
         <v/>
       </c>
-      <c r="L31">
+      <c r="L31" s="0">
         <f>'Catalogo_Decisiones'!L31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" s="0">
         <f>'Catalogo_Decisiones'!A32</f>
         <v/>
       </c>
-      <c r="B32">
+      <c r="B32" s="0">
         <f>'Catalogo_Decisiones'!B32</f>
         <v/>
       </c>
-      <c r="C32">
+      <c r="C32" s="0">
         <f>'Catalogo_Decisiones'!C32</f>
         <v/>
       </c>
-      <c r="D32">
+      <c r="D32" s="0">
         <f>'Catalogo_Decisiones'!D32</f>
         <v/>
       </c>
-      <c r="E32">
+      <c r="E32" s="0">
         <f>'Catalogo_Decisiones'!E32</f>
         <v/>
       </c>
-      <c r="F32">
+      <c r="F32" s="0">
         <f>'Catalogo_Decisiones'!F32</f>
         <v/>
       </c>
-      <c r="G32">
+      <c r="G32" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G32,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H32">
+      <c r="H32" s="0">
         <f>'Catalogo_Decisiones'!H32</f>
         <v/>
       </c>
-      <c r="I32">
+      <c r="I32" s="0">
         <f>'Catalogo_Decisiones'!I32</f>
         <v/>
       </c>
-      <c r="J32">
+      <c r="J32" s="0">
         <f>'Catalogo_Decisiones'!J32</f>
         <v/>
       </c>
-      <c r="K32">
+      <c r="K32" s="0">
         <f>'Catalogo_Decisiones'!K32</f>
         <v/>
       </c>
-      <c r="L32">
+      <c r="L32" s="0">
         <f>'Catalogo_Decisiones'!L32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" s="0">
         <f>'Catalogo_Decisiones'!A33</f>
         <v/>
       </c>
-      <c r="B33">
+      <c r="B33" s="0">
         <f>'Catalogo_Decisiones'!B33</f>
         <v/>
       </c>
-      <c r="C33">
+      <c r="C33" s="0">
         <f>'Catalogo_Decisiones'!C33</f>
         <v/>
       </c>
-      <c r="D33">
+      <c r="D33" s="0">
         <f>'Catalogo_Decisiones'!D33</f>
         <v/>
       </c>
-      <c r="E33">
+      <c r="E33" s="0">
         <f>'Catalogo_Decisiones'!E33</f>
         <v/>
       </c>
-      <c r="F33">
+      <c r="F33" s="0">
         <f>'Catalogo_Decisiones'!F33</f>
         <v/>
       </c>
-      <c r="G33">
+      <c r="G33" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G33,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H33">
+      <c r="H33" s="0">
         <f>'Catalogo_Decisiones'!H33</f>
         <v/>
       </c>
-      <c r="I33">
+      <c r="I33" s="0">
         <f>'Catalogo_Decisiones'!I33</f>
         <v/>
       </c>
-      <c r="J33">
+      <c r="J33" s="0">
         <f>'Catalogo_Decisiones'!J33</f>
         <v/>
       </c>
-      <c r="K33">
+      <c r="K33" s="0">
         <f>'Catalogo_Decisiones'!K33</f>
         <v/>
       </c>
-      <c r="L33">
+      <c r="L33" s="0">
         <f>'Catalogo_Decisiones'!L33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" s="0">
         <f>'Catalogo_Decisiones'!A34</f>
         <v/>
       </c>
-      <c r="B34">
+      <c r="B34" s="0">
         <f>'Catalogo_Decisiones'!B34</f>
         <v/>
       </c>
-      <c r="C34">
+      <c r="C34" s="0">
         <f>'Catalogo_Decisiones'!C34</f>
         <v/>
       </c>
-      <c r="D34">
+      <c r="D34" s="0">
         <f>'Catalogo_Decisiones'!D34</f>
         <v/>
       </c>
-      <c r="E34">
+      <c r="E34" s="0">
         <f>'Catalogo_Decisiones'!E34</f>
         <v/>
       </c>
-      <c r="F34">
+      <c r="F34" s="0">
         <f>'Catalogo_Decisiones'!F34</f>
         <v/>
       </c>
-      <c r="G34">
+      <c r="G34" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G34,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H34">
+      <c r="H34" s="0">
         <f>'Catalogo_Decisiones'!H34</f>
         <v/>
       </c>
-      <c r="I34">
+      <c r="I34" s="0">
         <f>'Catalogo_Decisiones'!I34</f>
         <v/>
       </c>
-      <c r="J34">
+      <c r="J34" s="0">
         <f>'Catalogo_Decisiones'!J34</f>
         <v/>
       </c>
-      <c r="K34">
+      <c r="K34" s="0">
         <f>'Catalogo_Decisiones'!K34</f>
         <v/>
       </c>
-      <c r="L34">
+      <c r="L34" s="0">
         <f>'Catalogo_Decisiones'!L34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" s="0">
         <f>'Catalogo_Decisiones'!A35</f>
         <v/>
       </c>
-      <c r="B35">
+      <c r="B35" s="0">
         <f>'Catalogo_Decisiones'!B35</f>
         <v/>
       </c>
-      <c r="C35">
+      <c r="C35" s="0">
         <f>'Catalogo_Decisiones'!C35</f>
         <v/>
       </c>
-      <c r="D35">
+      <c r="D35" s="0">
         <f>'Catalogo_Decisiones'!D35</f>
         <v/>
       </c>
-      <c r="E35">
+      <c r="E35" s="0">
         <f>'Catalogo_Decisiones'!E35</f>
         <v/>
       </c>
-      <c r="F35">
+      <c r="F35" s="0">
         <f>'Catalogo_Decisiones'!F35</f>
         <v/>
       </c>
-      <c r="G35">
+      <c r="G35" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G35,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H35">
+      <c r="H35" s="0">
         <f>'Catalogo_Decisiones'!H35</f>
         <v/>
       </c>
-      <c r="I35">
+      <c r="I35" s="0">
         <f>'Catalogo_Decisiones'!I35</f>
         <v/>
       </c>
-      <c r="J35">
+      <c r="J35" s="0">
         <f>'Catalogo_Decisiones'!J35</f>
         <v/>
       </c>
-      <c r="K35">
+      <c r="K35" s="0">
         <f>'Catalogo_Decisiones'!K35</f>
         <v/>
       </c>
-      <c r="L35">
+      <c r="L35" s="0">
         <f>'Catalogo_Decisiones'!L35</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" s="0">
         <f>'Catalogo_Decisiones'!A36</f>
         <v/>
       </c>
-      <c r="B36">
+      <c r="B36" s="0">
         <f>'Catalogo_Decisiones'!B36</f>
         <v/>
       </c>
-      <c r="C36">
+      <c r="C36" s="0">
         <f>'Catalogo_Decisiones'!C36</f>
         <v/>
       </c>
-      <c r="D36">
+      <c r="D36" s="0">
         <f>'Catalogo_Decisiones'!D36</f>
         <v/>
       </c>
-      <c r="E36">
+      <c r="E36" s="0">
         <f>'Catalogo_Decisiones'!E36</f>
         <v/>
       </c>
-      <c r="F36">
+      <c r="F36" s="0">
         <f>'Catalogo_Decisiones'!F36</f>
         <v/>
       </c>
-      <c r="G36">
+      <c r="G36" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G36,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H36">
+      <c r="H36" s="0">
         <f>'Catalogo_Decisiones'!H36</f>
         <v/>
       </c>
-      <c r="I36">
+      <c r="I36" s="0">
         <f>'Catalogo_Decisiones'!I36</f>
         <v/>
       </c>
-      <c r="J36">
+      <c r="J36" s="0">
         <f>'Catalogo_Decisiones'!J36</f>
         <v/>
       </c>
-      <c r="K36">
+      <c r="K36" s="0">
         <f>'Catalogo_Decisiones'!K36</f>
         <v/>
       </c>
-      <c r="L36">
+      <c r="L36" s="0">
         <f>'Catalogo_Decisiones'!L36</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" s="0">
         <f>'Catalogo_Decisiones'!A37</f>
         <v/>
       </c>
-      <c r="B37">
+      <c r="B37" s="0">
         <f>'Catalogo_Decisiones'!B37</f>
         <v/>
       </c>
-      <c r="C37">
+      <c r="C37" s="0">
         <f>'Catalogo_Decisiones'!C37</f>
         <v/>
       </c>
-      <c r="D37">
+      <c r="D37" s="0">
         <f>'Catalogo_Decisiones'!D37</f>
         <v/>
       </c>
-      <c r="E37">
+      <c r="E37" s="0">
         <f>'Catalogo_Decisiones'!E37</f>
         <v/>
       </c>
-      <c r="F37">
+      <c r="F37" s="0">
         <f>'Catalogo_Decisiones'!F37</f>
         <v/>
       </c>
-      <c r="G37">
+      <c r="G37" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G37,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H37">
+      <c r="H37" s="0">
         <f>'Catalogo_Decisiones'!H37</f>
         <v/>
       </c>
-      <c r="I37">
+      <c r="I37" s="0">
         <f>'Catalogo_Decisiones'!I37</f>
         <v/>
       </c>
-      <c r="J37">
+      <c r="J37" s="0">
         <f>'Catalogo_Decisiones'!J37</f>
         <v/>
       </c>
-      <c r="K37">
+      <c r="K37" s="0">
         <f>'Catalogo_Decisiones'!K37</f>
         <v/>
       </c>
-      <c r="L37">
+      <c r="L37" s="0">
         <f>'Catalogo_Decisiones'!L37</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" s="0">
         <f>'Catalogo_Decisiones'!A38</f>
         <v/>
       </c>
-      <c r="B38">
+      <c r="B38" s="0">
         <f>'Catalogo_Decisiones'!B38</f>
         <v/>
       </c>
-      <c r="C38">
+      <c r="C38" s="0">
         <f>'Catalogo_Decisiones'!C38</f>
         <v/>
       </c>
-      <c r="D38">
+      <c r="D38" s="0">
         <f>'Catalogo_Decisiones'!D38</f>
         <v/>
       </c>
-      <c r="E38">
+      <c r="E38" s="0">
         <f>'Catalogo_Decisiones'!E38</f>
         <v/>
       </c>
-      <c r="F38">
+      <c r="F38" s="0">
         <f>'Catalogo_Decisiones'!F38</f>
         <v/>
       </c>
-      <c r="G38">
+      <c r="G38" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G38,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H38">
+      <c r="H38" s="0">
         <f>'Catalogo_Decisiones'!H38</f>
         <v/>
       </c>
-      <c r="I38">
+      <c r="I38" s="0">
         <f>'Catalogo_Decisiones'!I38</f>
         <v/>
       </c>
-      <c r="J38">
+      <c r="J38" s="0">
         <f>'Catalogo_Decisiones'!J38</f>
         <v/>
       </c>
-      <c r="K38">
+      <c r="K38" s="0">
         <f>'Catalogo_Decisiones'!K38</f>
         <v/>
       </c>
-      <c r="L38">
+      <c r="L38" s="0">
         <f>'Catalogo_Decisiones'!L38</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" s="0">
         <f>'Catalogo_Decisiones'!A39</f>
         <v/>
       </c>
-      <c r="B39">
+      <c r="B39" s="0">
         <f>'Catalogo_Decisiones'!B39</f>
         <v/>
       </c>
-      <c r="C39">
+      <c r="C39" s="0">
         <f>'Catalogo_Decisiones'!C39</f>
         <v/>
       </c>
-      <c r="D39">
+      <c r="D39" s="0">
         <f>'Catalogo_Decisiones'!D39</f>
         <v/>
       </c>
-      <c r="E39">
+      <c r="E39" s="0">
         <f>'Catalogo_Decisiones'!E39</f>
         <v/>
       </c>
-      <c r="F39">
+      <c r="F39" s="0">
         <f>'Catalogo_Decisiones'!F39</f>
         <v/>
       </c>
-      <c r="G39">
+      <c r="G39" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G39,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H39">
+      <c r="H39" s="0">
         <f>'Catalogo_Decisiones'!H39</f>
         <v/>
       </c>
-      <c r="I39">
+      <c r="I39" s="0">
         <f>'Catalogo_Decisiones'!I39</f>
         <v/>
       </c>
-      <c r="J39">
+      <c r="J39" s="0">
         <f>'Catalogo_Decisiones'!J39</f>
         <v/>
       </c>
-      <c r="K39">
+      <c r="K39" s="0">
         <f>'Catalogo_Decisiones'!K39</f>
         <v/>
       </c>
-      <c r="L39">
+      <c r="L39" s="0">
         <f>'Catalogo_Decisiones'!L39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" s="0">
         <f>'Catalogo_Decisiones'!A40</f>
         <v/>
       </c>
-      <c r="B40">
+      <c r="B40" s="0">
         <f>'Catalogo_Decisiones'!B40</f>
         <v/>
       </c>
-      <c r="C40">
+      <c r="C40" s="0">
         <f>'Catalogo_Decisiones'!C40</f>
         <v/>
       </c>
-      <c r="D40">
+      <c r="D40" s="0">
         <f>'Catalogo_Decisiones'!D40</f>
         <v/>
       </c>
-      <c r="E40">
+      <c r="E40" s="0">
         <f>'Catalogo_Decisiones'!E40</f>
         <v/>
       </c>
-      <c r="F40">
+      <c r="F40" s="0">
         <f>'Catalogo_Decisiones'!F40</f>
         <v/>
       </c>
-      <c r="G40">
+      <c r="G40" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G40,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H40">
+      <c r="H40" s="0">
         <f>'Catalogo_Decisiones'!H40</f>
         <v/>
       </c>
-      <c r="I40">
+      <c r="I40" s="0">
         <f>'Catalogo_Decisiones'!I40</f>
         <v/>
       </c>
-      <c r="J40">
+      <c r="J40" s="0">
         <f>'Catalogo_Decisiones'!J40</f>
         <v/>
       </c>
-      <c r="K40">
+      <c r="K40" s="0">
         <f>'Catalogo_Decisiones'!K40</f>
         <v/>
       </c>
-      <c r="L40">
+      <c r="L40" s="0">
         <f>'Catalogo_Decisiones'!L40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" s="0">
         <f>'Catalogo_Decisiones'!A41</f>
         <v/>
       </c>
-      <c r="B41">
+      <c r="B41" s="0">
         <f>'Catalogo_Decisiones'!B41</f>
         <v/>
       </c>
-      <c r="C41">
+      <c r="C41" s="0">
         <f>'Catalogo_Decisiones'!C41</f>
         <v/>
       </c>
-      <c r="D41">
+      <c r="D41" s="0">
         <f>'Catalogo_Decisiones'!D41</f>
         <v/>
       </c>
-      <c r="E41">
+      <c r="E41" s="0">
         <f>'Catalogo_Decisiones'!E41</f>
         <v/>
       </c>
-      <c r="F41">
+      <c r="F41" s="0">
         <f>'Catalogo_Decisiones'!F41</f>
         <v/>
       </c>
-      <c r="G41">
+      <c r="G41" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G41,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H41">
+      <c r="H41" s="0">
         <f>'Catalogo_Decisiones'!H41</f>
         <v/>
       </c>
-      <c r="I41">
+      <c r="I41" s="0">
         <f>'Catalogo_Decisiones'!I41</f>
         <v/>
       </c>
-      <c r="J41">
+      <c r="J41" s="0">
         <f>'Catalogo_Decisiones'!J41</f>
         <v/>
       </c>
-      <c r="K41">
+      <c r="K41" s="0">
         <f>'Catalogo_Decisiones'!K41</f>
         <v/>
       </c>
-      <c r="L41">
+      <c r="L41" s="0">
         <f>'Catalogo_Decisiones'!L41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
+      <c r="A42" s="0">
         <f>'Catalogo_Decisiones'!A42</f>
         <v/>
       </c>
-      <c r="B42">
+      <c r="B42" s="0">
         <f>'Catalogo_Decisiones'!B42</f>
         <v/>
       </c>
-      <c r="C42">
+      <c r="C42" s="0">
         <f>'Catalogo_Decisiones'!C42</f>
         <v/>
       </c>
-      <c r="D42">
+      <c r="D42" s="0">
         <f>'Catalogo_Decisiones'!D42</f>
         <v/>
       </c>
-      <c r="E42">
+      <c r="E42" s="0">
         <f>'Catalogo_Decisiones'!E42</f>
         <v/>
       </c>
-      <c r="F42">
+      <c r="F42" s="0">
         <f>'Catalogo_Decisiones'!F42</f>
         <v/>
       </c>
-      <c r="G42">
+      <c r="G42" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G42,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H42">
+      <c r="H42" s="0">
         <f>'Catalogo_Decisiones'!H42</f>
         <v/>
       </c>
-      <c r="I42">
+      <c r="I42" s="0">
         <f>'Catalogo_Decisiones'!I42</f>
         <v/>
       </c>
-      <c r="J42">
+      <c r="J42" s="0">
         <f>'Catalogo_Decisiones'!J42</f>
         <v/>
       </c>
-      <c r="K42">
+      <c r="K42" s="0">
         <f>'Catalogo_Decisiones'!K42</f>
         <v/>
       </c>
-      <c r="L42">
+      <c r="L42" s="0">
         <f>'Catalogo_Decisiones'!L42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
+      <c r="A43" s="0">
         <f>'Catalogo_Decisiones'!A43</f>
         <v/>
       </c>
-      <c r="B43">
+      <c r="B43" s="0">
         <f>'Catalogo_Decisiones'!B43</f>
         <v/>
       </c>
-      <c r="C43">
+      <c r="C43" s="0">
         <f>'Catalogo_Decisiones'!C43</f>
         <v/>
       </c>
-      <c r="D43">
+      <c r="D43" s="0">
         <f>'Catalogo_Decisiones'!D43</f>
         <v/>
       </c>
-      <c r="E43">
+      <c r="E43" s="0">
         <f>'Catalogo_Decisiones'!E43</f>
         <v/>
       </c>
-      <c r="F43">
+      <c r="F43" s="0">
         <f>'Catalogo_Decisiones'!F43</f>
         <v/>
       </c>
-      <c r="G43">
+      <c r="G43" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G43,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H43">
+      <c r="H43" s="0">
         <f>'Catalogo_Decisiones'!H43</f>
         <v/>
       </c>
-      <c r="I43">
+      <c r="I43" s="0">
         <f>'Catalogo_Decisiones'!I43</f>
         <v/>
       </c>
-      <c r="J43">
+      <c r="J43" s="0">
         <f>'Catalogo_Decisiones'!J43</f>
         <v/>
       </c>
-      <c r="K43">
+      <c r="K43" s="0">
         <f>'Catalogo_Decisiones'!K43</f>
         <v/>
       </c>
-      <c r="L43">
+      <c r="L43" s="0">
         <f>'Catalogo_Decisiones'!L43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
+      <c r="A44" s="0">
         <f>'Catalogo_Decisiones'!A44</f>
         <v/>
       </c>
-      <c r="B44">
+      <c r="B44" s="0">
         <f>'Catalogo_Decisiones'!B44</f>
         <v/>
       </c>
-      <c r="C44">
+      <c r="C44" s="0">
         <f>'Catalogo_Decisiones'!C44</f>
         <v/>
       </c>
-      <c r="D44">
+      <c r="D44" s="0">
         <f>'Catalogo_Decisiones'!D44</f>
         <v/>
       </c>
-      <c r="E44">
+      <c r="E44" s="0">
         <f>'Catalogo_Decisiones'!E44</f>
         <v/>
       </c>
-      <c r="F44">
+      <c r="F44" s="0">
         <f>'Catalogo_Decisiones'!F44</f>
         <v/>
       </c>
-      <c r="G44">
+      <c r="G44" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G44,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H44">
+      <c r="H44" s="0">
         <f>'Catalogo_Decisiones'!H44</f>
         <v/>
       </c>
-      <c r="I44">
+      <c r="I44" s="0">
         <f>'Catalogo_Decisiones'!I44</f>
         <v/>
       </c>
-      <c r="J44">
+      <c r="J44" s="0">
         <f>'Catalogo_Decisiones'!J44</f>
         <v/>
       </c>
-      <c r="K44">
+      <c r="K44" s="0">
         <f>'Catalogo_Decisiones'!K44</f>
         <v/>
       </c>
-      <c r="L44">
+      <c r="L44" s="0">
         <f>'Catalogo_Decisiones'!L44</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
+      <c r="A45" s="0">
         <f>'Catalogo_Decisiones'!A45</f>
         <v/>
       </c>
-      <c r="B45">
+      <c r="B45" s="0">
         <f>'Catalogo_Decisiones'!B45</f>
         <v/>
       </c>
-      <c r="C45">
+      <c r="C45" s="0">
         <f>'Catalogo_Decisiones'!C45</f>
         <v/>
       </c>
-      <c r="D45">
+      <c r="D45" s="0">
         <f>'Catalogo_Decisiones'!D45</f>
         <v/>
       </c>
-      <c r="E45">
+      <c r="E45" s="0">
         <f>'Catalogo_Decisiones'!E45</f>
         <v/>
       </c>
-      <c r="F45">
+      <c r="F45" s="0">
         <f>'Catalogo_Decisiones'!F45</f>
         <v/>
       </c>
-      <c r="G45">
+      <c r="G45" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G45,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H45">
+      <c r="H45" s="0">
         <f>'Catalogo_Decisiones'!H45</f>
         <v/>
       </c>
-      <c r="I45">
+      <c r="I45" s="0">
         <f>'Catalogo_Decisiones'!I45</f>
         <v/>
       </c>
-      <c r="J45">
+      <c r="J45" s="0">
         <f>'Catalogo_Decisiones'!J45</f>
         <v/>
       </c>
-      <c r="K45">
+      <c r="K45" s="0">
         <f>'Catalogo_Decisiones'!K45</f>
         <v/>
       </c>
-      <c r="L45">
+      <c r="L45" s="0">
         <f>'Catalogo_Decisiones'!L45</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
+      <c r="A46" s="0">
         <f>'Catalogo_Decisiones'!A46</f>
         <v/>
       </c>
-      <c r="B46">
+      <c r="B46" s="0">
         <f>'Catalogo_Decisiones'!B46</f>
         <v/>
       </c>
-      <c r="C46">
+      <c r="C46" s="0">
         <f>'Catalogo_Decisiones'!C46</f>
         <v/>
       </c>
-      <c r="D46">
+      <c r="D46" s="0">
         <f>'Catalogo_Decisiones'!D46</f>
         <v/>
       </c>
-      <c r="E46">
+      <c r="E46" s="0">
         <f>'Catalogo_Decisiones'!E46</f>
         <v/>
       </c>
-      <c r="F46">
+      <c r="F46" s="0">
         <f>'Catalogo_Decisiones'!F46</f>
         <v/>
       </c>
-      <c r="G46">
+      <c r="G46" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G46,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H46">
+      <c r="H46" s="0">
         <f>'Catalogo_Decisiones'!H46</f>
         <v/>
       </c>
-      <c r="I46">
+      <c r="I46" s="0">
         <f>'Catalogo_Decisiones'!I46</f>
         <v/>
       </c>
-      <c r="J46">
+      <c r="J46" s="0">
         <f>'Catalogo_Decisiones'!J46</f>
         <v/>
       </c>
-      <c r="K46">
+      <c r="K46" s="0">
         <f>'Catalogo_Decisiones'!K46</f>
         <v/>
       </c>
-      <c r="L46">
+      <c r="L46" s="0">
         <f>'Catalogo_Decisiones'!L46</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
+      <c r="A47" s="0">
         <f>'Catalogo_Decisiones'!A47</f>
         <v/>
       </c>
-      <c r="B47">
+      <c r="B47" s="0">
         <f>'Catalogo_Decisiones'!B47</f>
         <v/>
       </c>
-      <c r="C47">
+      <c r="C47" s="0">
         <f>'Catalogo_Decisiones'!C47</f>
         <v/>
       </c>
-      <c r="D47">
+      <c r="D47" s="0">
         <f>'Catalogo_Decisiones'!D47</f>
         <v/>
       </c>
-      <c r="E47">
+      <c r="E47" s="0">
         <f>'Catalogo_Decisiones'!E47</f>
         <v/>
       </c>
-      <c r="F47">
+      <c r="F47" s="0">
         <f>'Catalogo_Decisiones'!F47</f>
         <v/>
       </c>
-      <c r="G47">
+      <c r="G47" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G47,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H47">
+      <c r="H47" s="0">
         <f>'Catalogo_Decisiones'!H47</f>
         <v/>
       </c>
-      <c r="I47">
+      <c r="I47" s="0">
         <f>'Catalogo_Decisiones'!I47</f>
         <v/>
       </c>
-      <c r="J47">
+      <c r="J47" s="0">
         <f>'Catalogo_Decisiones'!J47</f>
         <v/>
       </c>
-      <c r="K47">
+      <c r="K47" s="0">
         <f>'Catalogo_Decisiones'!K47</f>
         <v/>
       </c>
-      <c r="L47">
+      <c r="L47" s="0">
         <f>'Catalogo_Decisiones'!L47</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" s="0">
         <f>'Catalogo_Decisiones'!A48</f>
         <v/>
       </c>
-      <c r="B48">
+      <c r="B48" s="0">
         <f>'Catalogo_Decisiones'!B48</f>
         <v/>
       </c>
-      <c r="C48">
+      <c r="C48" s="0">
         <f>'Catalogo_Decisiones'!C48</f>
         <v/>
       </c>
-      <c r="D48">
+      <c r="D48" s="0">
         <f>'Catalogo_Decisiones'!D48</f>
         <v/>
       </c>
-      <c r="E48">
+      <c r="E48" s="0">
         <f>'Catalogo_Decisiones'!E48</f>
         <v/>
       </c>
-      <c r="F48">
+      <c r="F48" s="0">
         <f>'Catalogo_Decisiones'!F48</f>
         <v/>
       </c>
-      <c r="G48">
+      <c r="G48" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G48,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H48">
+      <c r="H48" s="0">
         <f>'Catalogo_Decisiones'!H48</f>
         <v/>
       </c>
-      <c r="I48">
+      <c r="I48" s="0">
         <f>'Catalogo_Decisiones'!I48</f>
         <v/>
       </c>
-      <c r="J48">
+      <c r="J48" s="0">
         <f>'Catalogo_Decisiones'!J48</f>
         <v/>
       </c>
-      <c r="K48">
+      <c r="K48" s="0">
         <f>'Catalogo_Decisiones'!K48</f>
         <v/>
       </c>
-      <c r="L48">
+      <c r="L48" s="0">
         <f>'Catalogo_Decisiones'!L48</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
+      <c r="A49" s="0">
         <f>'Catalogo_Decisiones'!A49</f>
         <v/>
       </c>
-      <c r="B49">
+      <c r="B49" s="0">
         <f>'Catalogo_Decisiones'!B49</f>
         <v/>
       </c>
-      <c r="C49">
+      <c r="C49" s="0">
         <f>'Catalogo_Decisiones'!C49</f>
         <v/>
       </c>
-      <c r="D49">
+      <c r="D49" s="0">
         <f>'Catalogo_Decisiones'!D49</f>
         <v/>
       </c>
-      <c r="E49">
+      <c r="E49" s="0">
         <f>'Catalogo_Decisiones'!E49</f>
         <v/>
       </c>
-      <c r="F49">
+      <c r="F49" s="0">
         <f>'Catalogo_Decisiones'!F49</f>
         <v/>
       </c>
-      <c r="G49">
+      <c r="G49" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G49,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H49">
+      <c r="H49" s="0">
         <f>'Catalogo_Decisiones'!H49</f>
         <v/>
       </c>
-      <c r="I49">
+      <c r="I49" s="0">
         <f>'Catalogo_Decisiones'!I49</f>
         <v/>
       </c>
-      <c r="J49">
+      <c r="J49" s="0">
         <f>'Catalogo_Decisiones'!J49</f>
         <v/>
       </c>
-      <c r="K49">
+      <c r="K49" s="0">
         <f>'Catalogo_Decisiones'!K49</f>
         <v/>
       </c>
-      <c r="L49">
+      <c r="L49" s="0">
         <f>'Catalogo_Decisiones'!L49</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" s="0">
         <f>'Catalogo_Decisiones'!A50</f>
         <v/>
       </c>
-      <c r="B50">
+      <c r="B50" s="0">
         <f>'Catalogo_Decisiones'!B50</f>
         <v/>
       </c>
-      <c r="C50">
+      <c r="C50" s="0">
         <f>'Catalogo_Decisiones'!C50</f>
         <v/>
       </c>
-      <c r="D50">
+      <c r="D50" s="0">
         <f>'Catalogo_Decisiones'!D50</f>
         <v/>
       </c>
-      <c r="E50">
+      <c r="E50" s="0">
         <f>'Catalogo_Decisiones'!E50</f>
         <v/>
       </c>
-      <c r="F50">
+      <c r="F50" s="0">
         <f>'Catalogo_Decisiones'!F50</f>
         <v/>
       </c>
-      <c r="G50">
+      <c r="G50" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G50,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H50">
+      <c r="H50" s="0">
         <f>'Catalogo_Decisiones'!H50</f>
         <v/>
       </c>
-      <c r="I50">
+      <c r="I50" s="0">
         <f>'Catalogo_Decisiones'!I50</f>
         <v/>
       </c>
-      <c r="J50">
+      <c r="J50" s="0">
         <f>'Catalogo_Decisiones'!J50</f>
         <v/>
       </c>
-      <c r="K50">
+      <c r="K50" s="0">
         <f>'Catalogo_Decisiones'!K50</f>
         <v/>
       </c>
-      <c r="L50">
+      <c r="L50" s="0">
         <f>'Catalogo_Decisiones'!L50</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
+      <c r="A51" s="0">
         <f>'Catalogo_Decisiones'!A51</f>
         <v/>
       </c>
-      <c r="B51">
+      <c r="B51" s="0">
         <f>'Catalogo_Decisiones'!B51</f>
         <v/>
       </c>
-      <c r="C51">
+      <c r="C51" s="0">
         <f>'Catalogo_Decisiones'!C51</f>
         <v/>
       </c>
-      <c r="D51">
+      <c r="D51" s="0">
         <f>'Catalogo_Decisiones'!D51</f>
         <v/>
       </c>
-      <c r="E51">
+      <c r="E51" s="0">
         <f>'Catalogo_Decisiones'!E51</f>
         <v/>
       </c>
-      <c r="F51">
+      <c r="F51" s="0">
         <f>'Catalogo_Decisiones'!F51</f>
         <v/>
       </c>
-      <c r="G51">
+      <c r="G51" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G51,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H51">
+      <c r="H51" s="0">
         <f>'Catalogo_Decisiones'!H51</f>
         <v/>
       </c>
-      <c r="I51">
+      <c r="I51" s="0">
         <f>'Catalogo_Decisiones'!I51</f>
         <v/>
       </c>
-      <c r="J51">
+      <c r="J51" s="0">
         <f>'Catalogo_Decisiones'!J51</f>
         <v/>
       </c>
-      <c r="K51">
+      <c r="K51" s="0">
         <f>'Catalogo_Decisiones'!K51</f>
         <v/>
       </c>
-      <c r="L51">
+      <c r="L51" s="0">
         <f>'Catalogo_Decisiones'!L51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
+      <c r="A52" s="0">
         <f>'Catalogo_Decisiones'!A52</f>
         <v/>
       </c>
-      <c r="B52">
+      <c r="B52" s="0">
         <f>'Catalogo_Decisiones'!B52</f>
         <v/>
       </c>
-      <c r="C52">
+      <c r="C52" s="0">
         <f>'Catalogo_Decisiones'!C52</f>
         <v/>
       </c>
-      <c r="D52">
+      <c r="D52" s="0">
         <f>'Catalogo_Decisiones'!D52</f>
         <v/>
       </c>
-      <c r="E52">
+      <c r="E52" s="0">
         <f>'Catalogo_Decisiones'!E52</f>
         <v/>
       </c>
-      <c r="F52">
+      <c r="F52" s="0">
         <f>'Catalogo_Decisiones'!F52</f>
         <v/>
       </c>
-      <c r="G52">
+      <c r="G52" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G52,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H52">
+      <c r="H52" s="0">
         <f>'Catalogo_Decisiones'!H52</f>
         <v/>
       </c>
-      <c r="I52">
+      <c r="I52" s="0">
         <f>'Catalogo_Decisiones'!I52</f>
         <v/>
       </c>
-      <c r="J52">
+      <c r="J52" s="0">
         <f>'Catalogo_Decisiones'!J52</f>
         <v/>
       </c>
-      <c r="K52">
+      <c r="K52" s="0">
         <f>'Catalogo_Decisiones'!K52</f>
         <v/>
       </c>
-      <c r="L52">
+      <c r="L52" s="0">
         <f>'Catalogo_Decisiones'!L52</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
+      <c r="A53" s="0">
         <f>'Catalogo_Decisiones'!A53</f>
         <v/>
       </c>
-      <c r="B53">
+      <c r="B53" s="0">
         <f>'Catalogo_Decisiones'!B53</f>
         <v/>
       </c>
-      <c r="C53">
+      <c r="C53" s="0">
         <f>'Catalogo_Decisiones'!C53</f>
         <v/>
       </c>
-      <c r="D53">
+      <c r="D53" s="0">
         <f>'Catalogo_Decisiones'!D53</f>
         <v/>
       </c>
-      <c r="E53">
+      <c r="E53" s="0">
         <f>'Catalogo_Decisiones'!E53</f>
         <v/>
       </c>
-      <c r="F53">
+      <c r="F53" s="0">
         <f>'Catalogo_Decisiones'!F53</f>
         <v/>
       </c>
-      <c r="G53">
+      <c r="G53" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G53,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H53">
+      <c r="H53" s="0">
         <f>'Catalogo_Decisiones'!H53</f>
         <v/>
       </c>
-      <c r="I53">
+      <c r="I53" s="0">
         <f>'Catalogo_Decisiones'!I53</f>
         <v/>
       </c>
-      <c r="J53">
+      <c r="J53" s="0">
         <f>'Catalogo_Decisiones'!J53</f>
         <v/>
       </c>
-      <c r="K53">
+      <c r="K53" s="0">
         <f>'Catalogo_Decisiones'!K53</f>
         <v/>
       </c>
-      <c r="L53">
+      <c r="L53" s="0">
         <f>'Catalogo_Decisiones'!L53</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
+      <c r="A54" s="0">
         <f>'Catalogo_Decisiones'!A54</f>
         <v/>
       </c>
-      <c r="B54">
+      <c r="B54" s="0">
         <f>'Catalogo_Decisiones'!B54</f>
         <v/>
       </c>
-      <c r="C54">
+      <c r="C54" s="0">
         <f>'Catalogo_Decisiones'!C54</f>
         <v/>
       </c>
-      <c r="D54">
+      <c r="D54" s="0">
         <f>'Catalogo_Decisiones'!D54</f>
         <v/>
       </c>
-      <c r="E54">
+      <c r="E54" s="0">
         <f>'Catalogo_Decisiones'!E54</f>
         <v/>
       </c>
-      <c r="F54">
+      <c r="F54" s="0">
         <f>'Catalogo_Decisiones'!F54</f>
         <v/>
       </c>
-      <c r="G54">
+      <c r="G54" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G54,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H54">
+      <c r="H54" s="0">
         <f>'Catalogo_Decisiones'!H54</f>
         <v/>
       </c>
-      <c r="I54">
+      <c r="I54" s="0">
         <f>'Catalogo_Decisiones'!I54</f>
         <v/>
       </c>
-      <c r="J54">
+      <c r="J54" s="0">
         <f>'Catalogo_Decisiones'!J54</f>
         <v/>
       </c>
-      <c r="K54">
+      <c r="K54" s="0">
         <f>'Catalogo_Decisiones'!K54</f>
         <v/>
       </c>
-      <c r="L54">
+      <c r="L54" s="0">
         <f>'Catalogo_Decisiones'!L54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55">
+      <c r="A55" s="0">
         <f>'Catalogo_Decisiones'!A55</f>
         <v/>
       </c>
-      <c r="B55">
+      <c r="B55" s="0">
         <f>'Catalogo_Decisiones'!B55</f>
         <v/>
       </c>
-      <c r="C55">
+      <c r="C55" s="0">
         <f>'Catalogo_Decisiones'!C55</f>
         <v/>
       </c>
-      <c r="D55">
+      <c r="D55" s="0">
         <f>'Catalogo_Decisiones'!D55</f>
         <v/>
       </c>
-      <c r="E55">
+      <c r="E55" s="0">
         <f>'Catalogo_Decisiones'!E55</f>
         <v/>
       </c>
-      <c r="F55">
+      <c r="F55" s="0">
         <f>'Catalogo_Decisiones'!F55</f>
         <v/>
       </c>
-      <c r="G55">
+      <c r="G55" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G55,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H55">
+      <c r="H55" s="0">
         <f>'Catalogo_Decisiones'!H55</f>
         <v/>
       </c>
-      <c r="I55">
+      <c r="I55" s="0">
         <f>'Catalogo_Decisiones'!I55</f>
         <v/>
       </c>
-      <c r="J55">
+      <c r="J55" s="0">
         <f>'Catalogo_Decisiones'!J55</f>
         <v/>
       </c>
-      <c r="K55">
+      <c r="K55" s="0">
         <f>'Catalogo_Decisiones'!K55</f>
         <v/>
       </c>
-      <c r="L55">
+      <c r="L55" s="0">
         <f>'Catalogo_Decisiones'!L55</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56">
+      <c r="A56" s="0">
         <f>'Catalogo_Decisiones'!A56</f>
         <v/>
       </c>
-      <c r="B56">
+      <c r="B56" s="0">
         <f>'Catalogo_Decisiones'!B56</f>
         <v/>
       </c>
-      <c r="C56">
+      <c r="C56" s="0">
         <f>'Catalogo_Decisiones'!C56</f>
         <v/>
       </c>
-      <c r="D56">
+      <c r="D56" s="0">
         <f>'Catalogo_Decisiones'!D56</f>
         <v/>
       </c>
-      <c r="E56">
+      <c r="E56" s="0">
         <f>'Catalogo_Decisiones'!E56</f>
         <v/>
       </c>
-      <c r="F56">
+      <c r="F56" s="0">
         <f>'Catalogo_Decisiones'!F56</f>
         <v/>
       </c>
-      <c r="G56">
+      <c r="G56" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G56,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H56">
+      <c r="H56" s="0">
         <f>'Catalogo_Decisiones'!H56</f>
         <v/>
       </c>
-      <c r="I56">
+      <c r="I56" s="0">
         <f>'Catalogo_Decisiones'!I56</f>
         <v/>
       </c>
-      <c r="J56">
+      <c r="J56" s="0">
         <f>'Catalogo_Decisiones'!J56</f>
         <v/>
       </c>
-      <c r="K56">
+      <c r="K56" s="0">
         <f>'Catalogo_Decisiones'!K56</f>
         <v/>
       </c>
-      <c r="L56">
+      <c r="L56" s="0">
         <f>'Catalogo_Decisiones'!L56</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57">
+      <c r="A57" s="0">
         <f>'Catalogo_Decisiones'!A57</f>
         <v/>
       </c>
-      <c r="B57">
+      <c r="B57" s="0">
         <f>'Catalogo_Decisiones'!B57</f>
         <v/>
       </c>
-      <c r="C57">
+      <c r="C57" s="0">
         <f>'Catalogo_Decisiones'!C57</f>
         <v/>
       </c>
-      <c r="D57">
+      <c r="D57" s="0">
         <f>'Catalogo_Decisiones'!D57</f>
         <v/>
       </c>
-      <c r="E57">
+      <c r="E57" s="0">
         <f>'Catalogo_Decisiones'!E57</f>
         <v/>
       </c>
-      <c r="F57">
+      <c r="F57" s="0">
         <f>'Catalogo_Decisiones'!F57</f>
         <v/>
       </c>
-      <c r="G57">
+      <c r="G57" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G57,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H57">
+      <c r="H57" s="0">
         <f>'Catalogo_Decisiones'!H57</f>
         <v/>
       </c>
-      <c r="I57">
+      <c r="I57" s="0">
         <f>'Catalogo_Decisiones'!I57</f>
         <v/>
       </c>
-      <c r="J57">
+      <c r="J57" s="0">
         <f>'Catalogo_Decisiones'!J57</f>
         <v/>
       </c>
-      <c r="K57">
+      <c r="K57" s="0">
         <f>'Catalogo_Decisiones'!K57</f>
         <v/>
       </c>
-      <c r="L57">
+      <c r="L57" s="0">
         <f>'Catalogo_Decisiones'!L57</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
+      <c r="A58" s="0">
         <f>'Catalogo_Decisiones'!A58</f>
         <v/>
       </c>
-      <c r="B58">
+      <c r="B58" s="0">
         <f>'Catalogo_Decisiones'!B58</f>
         <v/>
       </c>
-      <c r="C58">
+      <c r="C58" s="0">
         <f>'Catalogo_Decisiones'!C58</f>
         <v/>
       </c>
-      <c r="D58">
+      <c r="D58" s="0">
         <f>'Catalogo_Decisiones'!D58</f>
         <v/>
       </c>
-      <c r="E58">
+      <c r="E58" s="0">
         <f>'Catalogo_Decisiones'!E58</f>
         <v/>
       </c>
-      <c r="F58">
+      <c r="F58" s="0">
         <f>'Catalogo_Decisiones'!F58</f>
         <v/>
       </c>
-      <c r="G58">
+      <c r="G58" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G58,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H58">
+      <c r="H58" s="0">
         <f>'Catalogo_Decisiones'!H58</f>
         <v/>
       </c>
-      <c r="I58">
+      <c r="I58" s="0">
         <f>'Catalogo_Decisiones'!I58</f>
         <v/>
       </c>
-      <c r="J58">
+      <c r="J58" s="0">
         <f>'Catalogo_Decisiones'!J58</f>
         <v/>
       </c>
-      <c r="K58">
+      <c r="K58" s="0">
         <f>'Catalogo_Decisiones'!K58</f>
         <v/>
       </c>
-      <c r="L58">
+      <c r="L58" s="0">
         <f>'Catalogo_Decisiones'!L58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59">
+      <c r="A59" s="0">
         <f>'Catalogo_Decisiones'!A59</f>
         <v/>
       </c>
-      <c r="B59">
+      <c r="B59" s="0">
         <f>'Catalogo_Decisiones'!B59</f>
         <v/>
       </c>
-      <c r="C59">
+      <c r="C59" s="0">
         <f>'Catalogo_Decisiones'!C59</f>
         <v/>
       </c>
-      <c r="D59">
+      <c r="D59" s="0">
         <f>'Catalogo_Decisiones'!D59</f>
         <v/>
       </c>
-      <c r="E59">
+      <c r="E59" s="0">
         <f>'Catalogo_Decisiones'!E59</f>
         <v/>
       </c>
-      <c r="F59">
+      <c r="F59" s="0">
         <f>'Catalogo_Decisiones'!F59</f>
         <v/>
       </c>
-      <c r="G59">
+      <c r="G59" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G59,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H59">
+      <c r="H59" s="0">
         <f>'Catalogo_Decisiones'!H59</f>
         <v/>
       </c>
-      <c r="I59">
+      <c r="I59" s="0">
         <f>'Catalogo_Decisiones'!I59</f>
         <v/>
       </c>
-      <c r="J59">
+      <c r="J59" s="0">
         <f>'Catalogo_Decisiones'!J59</f>
         <v/>
       </c>
-      <c r="K59">
+      <c r="K59" s="0">
         <f>'Catalogo_Decisiones'!K59</f>
         <v/>
       </c>
-      <c r="L59">
+      <c r="L59" s="0">
         <f>'Catalogo_Decisiones'!L59</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60">
+      <c r="A60" s="0">
         <f>'Catalogo_Decisiones'!A60</f>
         <v/>
       </c>
-      <c r="B60">
+      <c r="B60" s="0">
         <f>'Catalogo_Decisiones'!B60</f>
         <v/>
       </c>
-      <c r="C60">
+      <c r="C60" s="0">
         <f>'Catalogo_Decisiones'!C60</f>
         <v/>
       </c>
-      <c r="D60">
+      <c r="D60" s="0">
         <f>'Catalogo_Decisiones'!D60</f>
         <v/>
       </c>
-      <c r="E60">
+      <c r="E60" s="0">
         <f>'Catalogo_Decisiones'!E60</f>
         <v/>
       </c>
-      <c r="F60">
+      <c r="F60" s="0">
         <f>'Catalogo_Decisiones'!F60</f>
         <v/>
       </c>
-      <c r="G60">
+      <c r="G60" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G60,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H60">
+      <c r="H60" s="0">
         <f>'Catalogo_Decisiones'!H60</f>
         <v/>
       </c>
-      <c r="I60">
+      <c r="I60" s="0">
         <f>'Catalogo_Decisiones'!I60</f>
         <v/>
       </c>
-      <c r="J60">
+      <c r="J60" s="0">
         <f>'Catalogo_Decisiones'!J60</f>
         <v/>
       </c>
-      <c r="K60">
+      <c r="K60" s="0">
         <f>'Catalogo_Decisiones'!K60</f>
         <v/>
       </c>
-      <c r="L60">
+      <c r="L60" s="0">
         <f>'Catalogo_Decisiones'!L60</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61">
+      <c r="A61" s="0">
         <f>'Catalogo_Decisiones'!A61</f>
         <v/>
       </c>
-      <c r="B61">
+      <c r="B61" s="0">
         <f>'Catalogo_Decisiones'!B61</f>
         <v/>
       </c>
-      <c r="C61">
+      <c r="C61" s="0">
         <f>'Catalogo_Decisiones'!C61</f>
         <v/>
       </c>
-      <c r="D61">
+      <c r="D61" s="0">
         <f>'Catalogo_Decisiones'!D61</f>
         <v/>
       </c>
-      <c r="E61">
+      <c r="E61" s="0">
         <f>'Catalogo_Decisiones'!E61</f>
         <v/>
       </c>
-      <c r="F61">
+      <c r="F61" s="0">
         <f>'Catalogo_Decisiones'!F61</f>
         <v/>
       </c>
-      <c r="G61">
+      <c r="G61" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G61,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H61">
+      <c r="H61" s="0">
         <f>'Catalogo_Decisiones'!H61</f>
         <v/>
       </c>
-      <c r="I61">
+      <c r="I61" s="0">
         <f>'Catalogo_Decisiones'!I61</f>
         <v/>
       </c>
-      <c r="J61">
+      <c r="J61" s="0">
         <f>'Catalogo_Decisiones'!J61</f>
         <v/>
       </c>
-      <c r="K61">
+      <c r="K61" s="0">
         <f>'Catalogo_Decisiones'!K61</f>
         <v/>
       </c>
-      <c r="L61">
+      <c r="L61" s="0">
         <f>'Catalogo_Decisiones'!L61</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62">
+      <c r="A62" s="0">
         <f>'Catalogo_Decisiones'!A62</f>
         <v/>
       </c>
-      <c r="B62">
+      <c r="B62" s="0">
         <f>'Catalogo_Decisiones'!B62</f>
         <v/>
       </c>
-      <c r="C62">
+      <c r="C62" s="0">
         <f>'Catalogo_Decisiones'!C62</f>
         <v/>
       </c>
-      <c r="D62">
+      <c r="D62" s="0">
         <f>'Catalogo_Decisiones'!D62</f>
         <v/>
       </c>
-      <c r="E62">
+      <c r="E62" s="0">
         <f>'Catalogo_Decisiones'!E62</f>
         <v/>
       </c>
-      <c r="F62">
+      <c r="F62" s="0">
         <f>'Catalogo_Decisiones'!F62</f>
         <v/>
       </c>
-      <c r="G62">
+      <c r="G62" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G62,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H62">
+      <c r="H62" s="0">
         <f>'Catalogo_Decisiones'!H62</f>
         <v/>
       </c>
-      <c r="I62">
+      <c r="I62" s="0">
         <f>'Catalogo_Decisiones'!I62</f>
         <v/>
       </c>
-      <c r="J62">
+      <c r="J62" s="0">
         <f>'Catalogo_Decisiones'!J62</f>
         <v/>
       </c>
-      <c r="K62">
+      <c r="K62" s="0">
         <f>'Catalogo_Decisiones'!K62</f>
         <v/>
       </c>
-      <c r="L62">
+      <c r="L62" s="0">
         <f>'Catalogo_Decisiones'!L62</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63">
+      <c r="A63" s="0">
         <f>'Catalogo_Decisiones'!A63</f>
         <v/>
       </c>
-      <c r="B63">
+      <c r="B63" s="0">
         <f>'Catalogo_Decisiones'!B63</f>
         <v/>
       </c>
-      <c r="C63">
+      <c r="C63" s="0">
         <f>'Catalogo_Decisiones'!C63</f>
         <v/>
       </c>
-      <c r="D63">
+      <c r="D63" s="0">
         <f>'Catalogo_Decisiones'!D63</f>
         <v/>
       </c>
-      <c r="E63">
+      <c r="E63" s="0">
         <f>'Catalogo_Decisiones'!E63</f>
         <v/>
       </c>
-      <c r="F63">
+      <c r="F63" s="0">
         <f>'Catalogo_Decisiones'!F63</f>
         <v/>
       </c>
-      <c r="G63">
+      <c r="G63" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G63,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H63">
+      <c r="H63" s="0">
         <f>'Catalogo_Decisiones'!H63</f>
         <v/>
       </c>
-      <c r="I63">
+      <c r="I63" s="0">
         <f>'Catalogo_Decisiones'!I63</f>
         <v/>
       </c>
-      <c r="J63">
+      <c r="J63" s="0">
         <f>'Catalogo_Decisiones'!J63</f>
         <v/>
       </c>
-      <c r="K63">
+      <c r="K63" s="0">
         <f>'Catalogo_Decisiones'!K63</f>
         <v/>
       </c>
-      <c r="L63">
+      <c r="L63" s="0">
         <f>'Catalogo_Decisiones'!L63</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64">
+      <c r="A64" s="0">
         <f>'Catalogo_Decisiones'!A64</f>
         <v/>
       </c>
-      <c r="B64">
+      <c r="B64" s="0">
         <f>'Catalogo_Decisiones'!B64</f>
         <v/>
       </c>
-      <c r="C64">
+      <c r="C64" s="0">
         <f>'Catalogo_Decisiones'!C64</f>
         <v/>
       </c>
-      <c r="D64">
+      <c r="D64" s="0">
         <f>'Catalogo_Decisiones'!D64</f>
         <v/>
       </c>
-      <c r="E64">
+      <c r="E64" s="0">
         <f>'Catalogo_Decisiones'!E64</f>
         <v/>
       </c>
-      <c r="F64">
+      <c r="F64" s="0">
         <f>'Catalogo_Decisiones'!F64</f>
         <v/>
       </c>
-      <c r="G64">
+      <c r="G64" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G64,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H64">
+      <c r="H64" s="0">
         <f>'Catalogo_Decisiones'!H64</f>
         <v/>
       </c>
-      <c r="I64">
+      <c r="I64" s="0">
         <f>'Catalogo_Decisiones'!I64</f>
         <v/>
       </c>
-      <c r="J64">
+      <c r="J64" s="0">
         <f>'Catalogo_Decisiones'!J64</f>
         <v/>
       </c>
-      <c r="K64">
+      <c r="K64" s="0">
         <f>'Catalogo_Decisiones'!K64</f>
         <v/>
       </c>
-      <c r="L64">
+      <c r="L64" s="0">
         <f>'Catalogo_Decisiones'!L64</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65">
+      <c r="A65" s="0">
         <f>'Catalogo_Decisiones'!A65</f>
         <v/>
       </c>
-      <c r="B65">
+      <c r="B65" s="0">
         <f>'Catalogo_Decisiones'!B65</f>
         <v/>
       </c>
-      <c r="C65">
+      <c r="C65" s="0">
         <f>'Catalogo_Decisiones'!C65</f>
         <v/>
       </c>
-      <c r="D65">
+      <c r="D65" s="0">
         <f>'Catalogo_Decisiones'!D65</f>
         <v/>
       </c>
-      <c r="E65">
+      <c r="E65" s="0">
         <f>'Catalogo_Decisiones'!E65</f>
         <v/>
       </c>
-      <c r="F65">
+      <c r="F65" s="0">
         <f>'Catalogo_Decisiones'!F65</f>
         <v/>
       </c>
-      <c r="G65">
+      <c r="G65" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G65,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H65">
+      <c r="H65" s="0">
         <f>'Catalogo_Decisiones'!H65</f>
         <v/>
       </c>
-      <c r="I65">
+      <c r="I65" s="0">
         <f>'Catalogo_Decisiones'!I65</f>
         <v/>
       </c>
-      <c r="J65">
+      <c r="J65" s="0">
         <f>'Catalogo_Decisiones'!J65</f>
         <v/>
       </c>
-      <c r="K65">
+      <c r="K65" s="0">
         <f>'Catalogo_Decisiones'!K65</f>
         <v/>
       </c>
-      <c r="L65">
+      <c r="L65" s="0">
         <f>'Catalogo_Decisiones'!L65</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66">
+      <c r="A66" s="0">
         <f>'Catalogo_Decisiones'!A66</f>
         <v/>
       </c>
-      <c r="B66">
+      <c r="B66" s="0">
         <f>'Catalogo_Decisiones'!B66</f>
         <v/>
       </c>
-      <c r="C66">
+      <c r="C66" s="0">
         <f>'Catalogo_Decisiones'!C66</f>
         <v/>
       </c>
-      <c r="D66">
+      <c r="D66" s="0">
         <f>'Catalogo_Decisiones'!D66</f>
         <v/>
       </c>
-      <c r="E66">
+      <c r="E66" s="0">
         <f>'Catalogo_Decisiones'!E66</f>
         <v/>
       </c>
-      <c r="F66">
+      <c r="F66" s="0">
         <f>'Catalogo_Decisiones'!F66</f>
         <v/>
       </c>
-      <c r="G66">
+      <c r="G66" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G66,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H66">
+      <c r="H66" s="0">
         <f>'Catalogo_Decisiones'!H66</f>
         <v/>
       </c>
-      <c r="I66">
+      <c r="I66" s="0">
         <f>'Catalogo_Decisiones'!I66</f>
         <v/>
       </c>
-      <c r="J66">
+      <c r="J66" s="0">
         <f>'Catalogo_Decisiones'!J66</f>
         <v/>
       </c>
-      <c r="K66">
+      <c r="K66" s="0">
         <f>'Catalogo_Decisiones'!K66</f>
         <v/>
       </c>
-      <c r="L66">
+      <c r="L66" s="0">
         <f>'Catalogo_Decisiones'!L66</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67">
+      <c r="A67" s="0">
         <f>'Catalogo_Decisiones'!A67</f>
         <v/>
       </c>
-      <c r="B67">
+      <c r="B67" s="0">
         <f>'Catalogo_Decisiones'!B67</f>
         <v/>
       </c>
-      <c r="C67">
+      <c r="C67" s="0">
         <f>'Catalogo_Decisiones'!C67</f>
         <v/>
       </c>
-      <c r="D67">
+      <c r="D67" s="0">
         <f>'Catalogo_Decisiones'!D67</f>
         <v/>
       </c>
-      <c r="E67">
+      <c r="E67" s="0">
         <f>'Catalogo_Decisiones'!E67</f>
         <v/>
       </c>
-      <c r="F67">
+      <c r="F67" s="0">
         <f>'Catalogo_Decisiones'!F67</f>
         <v/>
       </c>
-      <c r="G67">
+      <c r="G67" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G67,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H67">
+      <c r="H67" s="0">
         <f>'Catalogo_Decisiones'!H67</f>
         <v/>
       </c>
-      <c r="I67">
+      <c r="I67" s="0">
         <f>'Catalogo_Decisiones'!I67</f>
         <v/>
       </c>
-      <c r="J67">
+      <c r="J67" s="0">
         <f>'Catalogo_Decisiones'!J67</f>
         <v/>
       </c>
-      <c r="K67">
+      <c r="K67" s="0">
         <f>'Catalogo_Decisiones'!K67</f>
         <v/>
       </c>
-      <c r="L67">
+      <c r="L67" s="0">
         <f>'Catalogo_Decisiones'!L67</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68">
+      <c r="A68" s="0">
         <f>'Catalogo_Decisiones'!A68</f>
         <v/>
       </c>
-      <c r="B68">
+      <c r="B68" s="0">
         <f>'Catalogo_Decisiones'!B68</f>
         <v/>
       </c>
-      <c r="C68">
+      <c r="C68" s="0">
         <f>'Catalogo_Decisiones'!C68</f>
         <v/>
       </c>
-      <c r="D68">
+      <c r="D68" s="0">
         <f>'Catalogo_Decisiones'!D68</f>
         <v/>
       </c>
-      <c r="E68">
+      <c r="E68" s="0">
         <f>'Catalogo_Decisiones'!E68</f>
         <v/>
       </c>
-      <c r="F68">
+      <c r="F68" s="0">
         <f>'Catalogo_Decisiones'!F68</f>
         <v/>
       </c>
-      <c r="G68">
+      <c r="G68" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G68,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H68">
+      <c r="H68" s="0">
         <f>'Catalogo_Decisiones'!H68</f>
         <v/>
       </c>
-      <c r="I68">
+      <c r="I68" s="0">
         <f>'Catalogo_Decisiones'!I68</f>
         <v/>
       </c>
-      <c r="J68">
+      <c r="J68" s="0">
         <f>'Catalogo_Decisiones'!J68</f>
         <v/>
       </c>
-      <c r="K68">
+      <c r="K68" s="0">
         <f>'Catalogo_Decisiones'!K68</f>
         <v/>
       </c>
-      <c r="L68">
+      <c r="L68" s="0">
         <f>'Catalogo_Decisiones'!L68</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69">
+      <c r="A69" s="0">
         <f>'Catalogo_Decisiones'!A69</f>
         <v/>
       </c>
-      <c r="B69">
+      <c r="B69" s="0">
         <f>'Catalogo_Decisiones'!B69</f>
         <v/>
       </c>
-      <c r="C69">
+      <c r="C69" s="0">
         <f>'Catalogo_Decisiones'!C69</f>
         <v/>
       </c>
-      <c r="D69">
+      <c r="D69" s="0">
         <f>'Catalogo_Decisiones'!D69</f>
         <v/>
       </c>
-      <c r="E69">
+      <c r="E69" s="0">
         <f>'Catalogo_Decisiones'!E69</f>
         <v/>
       </c>
-      <c r="F69">
+      <c r="F69" s="0">
         <f>'Catalogo_Decisiones'!F69</f>
         <v/>
       </c>
-      <c r="G69">
+      <c r="G69" s="0">
         <f>IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(Catalogo_Decisiones!G69,"S/",""),",","")),0)</f>
         <v/>
       </c>
-      <c r="H69">
+      <c r="H69" s="0">
         <f>'Catalogo_Decisiones'!H69</f>
         <v/>
       </c>
-      <c r="I69">
+      <c r="I69" s="0">
         <f>'Catalogo_Decisiones'!I69</f>
         <v/>
       </c>
-      <c r="J69">
+      <c r="J69" s="0">
         <f>'Catalogo_Decisiones'!J69</f>
         <v/>
       </c>
-      <c r="K69">
+      <c r="K69" s="0">
         <f>'Catalogo_Decisiones'!K69</f>
         <v/>
       </c>
-      <c r="L69">
+      <c r="L69" s="0">
         <f>'Catalogo_Decisiones'!L69</f>
         <v/>
       </c>

--- a/tests/oracle/ORACULO_banca.xlsx
+++ b/tests/oracle/ORACULO_banca.xlsx
@@ -5384,242 +5384,242 @@
           <t>CONS-08</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>capitalInicial</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="0" t="inlineStr">
         <is>
           <t>compraActivos</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="0" t="inlineStr">
         <is>
           <t>adquisicionNeta</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="0" t="inlineStr">
         <is>
           <t>valorCompradoNeto</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="0" t="inlineStr">
         <is>
           <t>valorInventarioNeto</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="0" t="inlineStr">
         <is>
           <t>cajaInicial</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="0" t="inlineStr">
         <is>
           <t>tasaNuevoPrestamo</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="0" t="inlineStr">
         <is>
           <t>interesMensual</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="0" t="inlineStr">
         <is>
           <t>tasaMensual</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="0" t="inlineStr">
         <is>
           <t>intereses</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="0" t="inlineStr">
         <is>
           <t>pagosOperacion</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="0" t="inlineStr">
         <is>
           <t>cajaFinal</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="0" t="inlineStr">
         <is>
           <t>depreciacionAcumulada</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="0" t="inlineStr">
         <is>
           <t>activosCosto</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="0" t="inlineStr">
         <is>
           <t>activosFijos</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ingresos</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ventasNetas</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costos</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.utilidad</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.depreciacion</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.intereses</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="0" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costosProduccion</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.entradas</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.salidas</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cobrosVentas</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.pagosOperacion</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.compraActivos</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.financiamiento</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.operacion</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.inversion</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.flujoNeto</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="0" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.efectivo</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activosFijos</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.inventarioMP</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activos</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.deuda</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.patrimonio</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="0" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.pasivoPatrimonio</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.montoPrestamo</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaTEA</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.deudaPrincipal</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaAdicionalProximoPrestamo</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaMensual</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="0" t="inlineStr">
         <is>
           <t>financial.financiamiento.intereses</t>
         </is>
@@ -6172,194 +6172,194 @@
         <f>AND(K2=0,AF2&lt;5)</f>
         <v/>
       </c>
-      <c r="FA2" t="n">
+      <c r="FA2" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB2">
+      <c r="FB2" s="0">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC2">
+      <c r="FC2" s="0">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD2">
+      <c r="FD2" s="0">
         <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FE2">
+      <c r="FE2" s="0">
         <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.8924</f>
         <v/>
       </c>
-      <c r="FF2">
+      <c r="FF2" s="0">
         <f>FA2</f>
         <v/>
       </c>
-      <c r="FG2">
+      <c r="FG2" s="0">
         <f>(1+AR2/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH2">
+      <c r="FH2" s="0">
         <f>0*0+AP2*FG2</f>
         <v/>
       </c>
-      <c r="FI2">
+      <c r="FI2" s="0">
         <f>IFERROR(FH2/(0+AP2),0)</f>
         <v/>
       </c>
-      <c r="FJ2">
+      <c r="FJ2" s="0">
         <f>FH2*1</f>
         <v/>
       </c>
-      <c r="FK2">
+      <c r="FK2" s="0">
         <f>EQ2-DW2-DU2+FD2+FJ2</f>
         <v/>
       </c>
-      <c r="FL2">
+      <c r="FL2" s="0">
         <f>FF2+EK2+AP2-FK2-FB2</f>
         <v/>
       </c>
-      <c r="FM2">
+      <c r="FM2" s="0">
         <f>0+DW2</f>
         <v/>
       </c>
-      <c r="FN2">
+      <c r="FN2" s="0">
         <f>0+FC2</f>
         <v/>
       </c>
-      <c r="FO2">
+      <c r="FO2" s="0">
         <f>FN2-FM2</f>
         <v/>
       </c>
-      <c r="FP2">
+      <c r="FP2" s="0">
         <f>EK2</f>
         <v/>
       </c>
-      <c r="FQ2">
+      <c r="FQ2" s="0">
         <f>EK2</f>
         <v/>
       </c>
-      <c r="FR2">
+      <c r="FR2" s="0">
         <f>EQ2+FJ2</f>
         <v/>
       </c>
-      <c r="FS2">
+      <c r="FS2" s="0">
         <f>ER2-FJ2</f>
         <v/>
       </c>
-      <c r="FT2">
+      <c r="FT2" s="0">
         <f>DW2</f>
         <v/>
       </c>
-      <c r="FU2">
+      <c r="FU2" s="0">
         <f>FJ2</f>
         <v/>
       </c>
-      <c r="FV2">
+      <c r="FV2" s="0">
         <f>EQ2</f>
         <v/>
       </c>
-      <c r="FW2">
+      <c r="FW2" s="0">
         <f>FF2</f>
         <v/>
       </c>
-      <c r="FX2">
+      <c r="FX2" s="0">
         <f>EK2+AP2</f>
         <v/>
       </c>
-      <c r="FY2">
+      <c r="FY2" s="0">
         <f>FK2+FB2</f>
         <v/>
       </c>
-      <c r="FZ2">
+      <c r="FZ2" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="GA2">
+      <c r="GA2" s="0">
         <f>FF2</f>
         <v/>
       </c>
-      <c r="GB2">
+      <c r="GB2" s="0">
         <f>EK2</f>
         <v/>
       </c>
-      <c r="GC2">
+      <c r="GC2" s="0">
         <f>FK2</f>
         <v/>
       </c>
-      <c r="GD2">
+      <c r="GD2" s="0">
         <f>FB2</f>
         <v/>
       </c>
-      <c r="GE2">
+      <c r="GE2" s="0">
         <f>AP2</f>
         <v/>
       </c>
-      <c r="GF2">
+      <c r="GF2" s="0">
         <f>EK2-FK2</f>
         <v/>
       </c>
-      <c r="GG2">
+      <c r="GG2" s="0">
         <f>-FB2</f>
         <v/>
       </c>
-      <c r="GH2">
+      <c r="GH2" s="0">
         <f>FL2-FF2</f>
         <v/>
       </c>
-      <c r="GI2">
+      <c r="GI2" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="GJ2">
+      <c r="GJ2" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="GK2">
+      <c r="GK2" s="0">
         <f>FO2</f>
         <v/>
       </c>
-      <c r="GL2">
+      <c r="GL2" s="0">
         <f>FE2</f>
         <v/>
       </c>
-      <c r="GM2">
+      <c r="GM2" s="0">
         <f>FL2+FO2+FE2</f>
         <v/>
       </c>
-      <c r="GN2">
+      <c r="GN2" s="0">
         <f>AS2</f>
         <v/>
       </c>
-      <c r="GO2">
+      <c r="GO2" s="0">
         <f>FL2+FO2+FE2-AS2</f>
         <v/>
       </c>
-      <c r="GP2">
+      <c r="GP2" s="0">
         <f>FL2+FO2+FE2</f>
         <v/>
       </c>
-      <c r="GQ2">
+      <c r="GQ2" s="0">
         <f>AP2</f>
         <v/>
       </c>
-      <c r="GR2">
+      <c r="GR2" s="0">
         <f>AR2</f>
         <v/>
       </c>
-      <c r="GS2">
+      <c r="GS2" s="0">
         <f>AS2</f>
         <v/>
       </c>
-      <c r="GT2">
+      <c r="GT2" s="0">
         <f>AT2</f>
         <v/>
       </c>
-      <c r="GU2">
+      <c r="GU2" s="0">
         <f>FI2</f>
         <v/>
       </c>
-      <c r="GV2">
+      <c r="GV2" s="0">
         <f>FJ2</f>
         <v/>
       </c>
@@ -6939,194 +6939,194 @@
         <f>AND(K3=0,AF3&lt;5)</f>
         <v/>
       </c>
-      <c r="FA3" t="n">
+      <c r="FA3" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB3">
+      <c r="FB3" s="0">
         <f>0*2500*(1+0.03+0.02)+0*3500*(1+0.03+0.02)+0*1200*(1+0.03+0.02)+0*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC3">
+      <c r="FC3" s="0">
         <f>0*2500+0*3500+0*1200+0*300</f>
         <v/>
       </c>
-      <c r="FD3">
+      <c r="FD3" s="0">
         <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.9016000000000001</f>
         <v/>
       </c>
-      <c r="FE3">
+      <c r="FE3" s="0">
         <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.9016000000000001</f>
         <v/>
       </c>
-      <c r="FF3">
+      <c r="FF3" s="0">
         <f>FL2</f>
         <v/>
       </c>
-      <c r="FG3">
+      <c r="FG3" s="0">
         <f>(1+AR3/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH3">
+      <c r="FH3" s="0">
         <f>AS2*FI2+AP3*FG3</f>
         <v/>
       </c>
-      <c r="FI3">
+      <c r="FI3" s="0">
         <f>IFERROR(FH3/(AS2+AP3),0)</f>
         <v/>
       </c>
-      <c r="FJ3">
+      <c r="FJ3" s="0">
         <f>FH3*1</f>
         <v/>
       </c>
-      <c r="FK3">
+      <c r="FK3" s="0">
         <f>EQ3-DW3-DU3+FD3+FJ3</f>
         <v/>
       </c>
-      <c r="FL3">
+      <c r="FL3" s="0">
         <f>FF3+EK3+AP3-FK3-FB3</f>
         <v/>
       </c>
-      <c r="FM3">
+      <c r="FM3" s="0">
         <f>FM2+DW3</f>
         <v/>
       </c>
-      <c r="FN3">
+      <c r="FN3" s="0">
         <f>FN2+FC3</f>
         <v/>
       </c>
-      <c r="FO3">
+      <c r="FO3" s="0">
         <f>FN3-FM3</f>
         <v/>
       </c>
-      <c r="FP3">
+      <c r="FP3" s="0">
         <f>EK3</f>
         <v/>
       </c>
-      <c r="FQ3">
+      <c r="FQ3" s="0">
         <f>EK3</f>
         <v/>
       </c>
-      <c r="FR3">
+      <c r="FR3" s="0">
         <f>EQ3+FJ3</f>
         <v/>
       </c>
-      <c r="FS3">
+      <c r="FS3" s="0">
         <f>ER3-FJ3</f>
         <v/>
       </c>
-      <c r="FT3">
+      <c r="FT3" s="0">
         <f>DW3</f>
         <v/>
       </c>
-      <c r="FU3">
+      <c r="FU3" s="0">
         <f>FJ3</f>
         <v/>
       </c>
-      <c r="FV3">
+      <c r="FV3" s="0">
         <f>EQ3</f>
         <v/>
       </c>
-      <c r="FW3">
+      <c r="FW3" s="0">
         <f>FF3</f>
         <v/>
       </c>
-      <c r="FX3">
+      <c r="FX3" s="0">
         <f>EK3+AP3</f>
         <v/>
       </c>
-      <c r="FY3">
+      <c r="FY3" s="0">
         <f>FK3+FB3</f>
         <v/>
       </c>
-      <c r="FZ3">
+      <c r="FZ3" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="GA3">
+      <c r="GA3" s="0">
         <f>FF3</f>
         <v/>
       </c>
-      <c r="GB3">
+      <c r="GB3" s="0">
         <f>EK3</f>
         <v/>
       </c>
-      <c r="GC3">
+      <c r="GC3" s="0">
         <f>FK3</f>
         <v/>
       </c>
-      <c r="GD3">
+      <c r="GD3" s="0">
         <f>FB3</f>
         <v/>
       </c>
-      <c r="GE3">
+      <c r="GE3" s="0">
         <f>AP3</f>
         <v/>
       </c>
-      <c r="GF3">
+      <c r="GF3" s="0">
         <f>EK3-FK3</f>
         <v/>
       </c>
-      <c r="GG3">
+      <c r="GG3" s="0">
         <f>-FB3</f>
         <v/>
       </c>
-      <c r="GH3">
+      <c r="GH3" s="0">
         <f>FL3-FF3</f>
         <v/>
       </c>
-      <c r="GI3">
+      <c r="GI3" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="GJ3">
+      <c r="GJ3" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="GK3">
+      <c r="GK3" s="0">
         <f>FO3</f>
         <v/>
       </c>
-      <c r="GL3">
+      <c r="GL3" s="0">
         <f>FE3</f>
         <v/>
       </c>
-      <c r="GM3">
+      <c r="GM3" s="0">
         <f>FL3+FO3+FE3</f>
         <v/>
       </c>
-      <c r="GN3">
+      <c r="GN3" s="0">
         <f>AS3</f>
         <v/>
       </c>
-      <c r="GO3">
+      <c r="GO3" s="0">
         <f>FL3+FO3+FE3-AS3</f>
         <v/>
       </c>
-      <c r="GP3">
+      <c r="GP3" s="0">
         <f>FL3+FO3+FE3</f>
         <v/>
       </c>
-      <c r="GQ3">
+      <c r="GQ3" s="0">
         <f>AP3</f>
         <v/>
       </c>
-      <c r="GR3">
+      <c r="GR3" s="0">
         <f>AR3</f>
         <v/>
       </c>
-      <c r="GS3">
+      <c r="GS3" s="0">
         <f>AS3</f>
         <v/>
       </c>
-      <c r="GT3">
+      <c r="GT3" s="0">
         <f>AT3</f>
         <v/>
       </c>
-      <c r="GU3">
+      <c r="GU3" s="0">
         <f>FI3</f>
         <v/>
       </c>
-      <c r="GV3">
+      <c r="GV3" s="0">
         <f>FJ3</f>
         <v/>
       </c>
@@ -7706,194 +7706,194 @@
         <f>AND(K4=0,AF4&lt;5)</f>
         <v/>
       </c>
-      <c r="FA4" t="n">
+      <c r="FA4" s="0" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB4">
+      <c r="FB4" s="0">
         <f>0*2500*(1+0.03+0.02)+0*3500*(1+0.03+0.02)+0*1200*(1+0.03+0.02)+0*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC4">
+      <c r="FC4" s="0">
         <f>0*2500+0*3500+0*1200+0*300</f>
         <v/>
       </c>
-      <c r="FD4">
+      <c r="FD4" s="0">
         <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.9016000000000001</f>
         <v/>
       </c>
-      <c r="FE4">
+      <c r="FE4" s="0">
         <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.9016000000000001</f>
         <v/>
       </c>
-      <c r="FF4">
+      <c r="FF4" s="0">
         <f>FL3</f>
         <v/>
       </c>
-      <c r="FG4">
+      <c r="FG4" s="0">
         <f>(1+AR4/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH4">
+      <c r="FH4" s="0">
         <f>AS3*FI3+AP4*FG4</f>
         <v/>
       </c>
-      <c r="FI4">
+      <c r="FI4" s="0">
         <f>IFERROR(FH4/(AS3+AP4),0)</f>
         <v/>
       </c>
-      <c r="FJ4">
+      <c r="FJ4" s="0">
         <f>FH4*1</f>
         <v/>
       </c>
-      <c r="FK4">
+      <c r="FK4" s="0">
         <f>EQ4-DW4-DU4+FD4+FJ4</f>
         <v/>
       </c>
-      <c r="FL4">
+      <c r="FL4" s="0">
         <f>FF4+EK4+AP4-FK4-FB4</f>
         <v/>
       </c>
-      <c r="FM4">
+      <c r="FM4" s="0">
         <f>FM3+DW4</f>
         <v/>
       </c>
-      <c r="FN4">
+      <c r="FN4" s="0">
         <f>FN3+FC4</f>
         <v/>
       </c>
-      <c r="FO4">
+      <c r="FO4" s="0">
         <f>FN4-FM4</f>
         <v/>
       </c>
-      <c r="FP4">
+      <c r="FP4" s="0">
         <f>EK4</f>
         <v/>
       </c>
-      <c r="FQ4">
+      <c r="FQ4" s="0">
         <f>EK4</f>
         <v/>
       </c>
-      <c r="FR4">
+      <c r="FR4" s="0">
         <f>EQ4+FJ4</f>
         <v/>
       </c>
-      <c r="FS4">
+      <c r="FS4" s="0">
         <f>ER4-FJ4</f>
         <v/>
       </c>
-      <c r="FT4">
+      <c r="FT4" s="0">
         <f>DW4</f>
         <v/>
       </c>
-      <c r="FU4">
+      <c r="FU4" s="0">
         <f>FJ4</f>
         <v/>
       </c>
-      <c r="FV4">
+      <c r="FV4" s="0">
         <f>EQ4</f>
         <v/>
       </c>
-      <c r="FW4">
+      <c r="FW4" s="0">
         <f>FF4</f>
         <v/>
       </c>
-      <c r="FX4">
+      <c r="FX4" s="0">
         <f>EK4+AP4</f>
         <v/>
       </c>
-      <c r="FY4">
+      <c r="FY4" s="0">
         <f>FK4+FB4</f>
         <v/>
       </c>
-      <c r="FZ4">
+      <c r="FZ4" s="0">
         <f>FL4</f>
         <v/>
       </c>
-      <c r="GA4">
+      <c r="GA4" s="0">
         <f>FF4</f>
         <v/>
       </c>
-      <c r="GB4">
+      <c r="GB4" s="0">
         <f>EK4</f>
         <v/>
       </c>
-      <c r="GC4">
+      <c r="GC4" s="0">
         <f>FK4</f>
         <v/>
       </c>
-      <c r="GD4">
+      <c r="GD4" s="0">
         <f>FB4</f>
         <v/>
       </c>
-      <c r="GE4">
+      <c r="GE4" s="0">
         <f>AP4</f>
         <v/>
       </c>
-      <c r="GF4">
+      <c r="GF4" s="0">
         <f>EK4-FK4</f>
         <v/>
       </c>
-      <c r="GG4">
+      <c r="GG4" s="0">
         <f>-FB4</f>
         <v/>
       </c>
-      <c r="GH4">
+      <c r="GH4" s="0">
         <f>FL4-FF4</f>
         <v/>
       </c>
-      <c r="GI4">
+      <c r="GI4" s="0">
         <f>FL4</f>
         <v/>
       </c>
-      <c r="GJ4">
+      <c r="GJ4" s="0">
         <f>FL4</f>
         <v/>
       </c>
-      <c r="GK4">
+      <c r="GK4" s="0">
         <f>FO4</f>
         <v/>
       </c>
-      <c r="GL4">
+      <c r="GL4" s="0">
         <f>FE4</f>
         <v/>
       </c>
-      <c r="GM4">
+      <c r="GM4" s="0">
         <f>FL4+FO4+FE4</f>
         <v/>
       </c>
-      <c r="GN4">
+      <c r="GN4" s="0">
         <f>AS4</f>
         <v/>
       </c>
-      <c r="GO4">
+      <c r="GO4" s="0">
         <f>FL4+FO4+FE4-AS4</f>
         <v/>
       </c>
-      <c r="GP4">
+      <c r="GP4" s="0">
         <f>FL4+FO4+FE4</f>
         <v/>
       </c>
-      <c r="GQ4">
+      <c r="GQ4" s="0">
         <f>AP4</f>
         <v/>
       </c>
-      <c r="GR4">
+      <c r="GR4" s="0">
         <f>AR4</f>
         <v/>
       </c>
-      <c r="GS4">
+      <c r="GS4" s="0">
         <f>AS4</f>
         <v/>
       </c>
-      <c r="GT4">
+      <c r="GT4" s="0">
         <f>AT4</f>
         <v/>
       </c>
-      <c r="GU4">
+      <c r="GU4" s="0">
         <f>FI4</f>
         <v/>
       </c>
-      <c r="GV4">
+      <c r="GV4" s="0">
         <f>FJ4</f>
         <v/>
       </c>

--- a/tests/oracle/ORACULO_banca.xlsx
+++ b/tests/oracle/ORACULO_banca.xlsx
@@ -4442,7 +4442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GV4"/>
+  <dimension ref="A1:GW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="184" min="1" max="1"/>
@@ -4601,6 +4601,7 @@
     <col width="20" customWidth="1" style="184" min="154" max="154"/>
     <col width="20" customWidth="1" style="184" min="155" max="155"/>
     <col width="20" customWidth="1" style="184" min="156" max="156"/>
+    <col width="20" customWidth="1" style="184" min="157" max="157"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5336,290 +5337,295 @@
       </c>
       <c r="EQ1" s="0" t="inlineStr">
         <is>
+          <t>costoAnalista</t>
+        </is>
+      </c>
+      <c r="ER1" s="0" t="inlineStr">
+        <is>
           <t>costosTotales</t>
         </is>
       </c>
-      <c r="ER1" s="0" t="inlineStr">
+      <c r="ES1" s="0" t="inlineStr">
         <is>
           <t>utilidad</t>
         </is>
       </c>
-      <c r="ES1" s="0" t="inlineStr">
+      <c r="ET1" s="0" t="inlineStr">
         <is>
           <t>CONS-01</t>
         </is>
       </c>
-      <c r="ET1" s="0" t="inlineStr">
+      <c r="EU1" s="0" t="inlineStr">
         <is>
           <t>CONS-02</t>
         </is>
       </c>
-      <c r="EU1" s="0" t="inlineStr">
+      <c r="EV1" s="0" t="inlineStr">
         <is>
           <t>CONS-03</t>
         </is>
       </c>
-      <c r="EV1" s="0" t="inlineStr">
+      <c r="EW1" s="0" t="inlineStr">
         <is>
           <t>CONS-04</t>
         </is>
       </c>
-      <c r="EW1" s="0" t="inlineStr">
+      <c r="EX1" s="0" t="inlineStr">
         <is>
           <t>CONS-05</t>
         </is>
       </c>
-      <c r="EX1" s="0" t="inlineStr">
+      <c r="EY1" s="0" t="inlineStr">
         <is>
           <t>CONS-06</t>
         </is>
       </c>
-      <c r="EY1" s="0" t="inlineStr">
+      <c r="EZ1" s="0" t="inlineStr">
         <is>
           <t>CONS-07</t>
         </is>
       </c>
-      <c r="EZ1" s="0" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>CONS-08</t>
         </is>
       </c>
-      <c r="FA1" s="0" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>capitalInicial</t>
         </is>
       </c>
-      <c r="FB1" s="0" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>compraActivos</t>
         </is>
       </c>
-      <c r="FC1" s="0" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>adquisicionNeta</t>
         </is>
       </c>
-      <c r="FD1" s="0" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>valorCompradoNeto</t>
         </is>
       </c>
-      <c r="FE1" s="0" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>valorInventarioNeto</t>
         </is>
       </c>
-      <c r="FF1" s="0" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>cajaInicial</t>
         </is>
       </c>
-      <c r="FG1" s="0" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>tasaNuevoPrestamo</t>
         </is>
       </c>
-      <c r="FH1" s="0" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>interesMensual</t>
         </is>
       </c>
-      <c r="FI1" s="0" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>tasaMensual</t>
         </is>
       </c>
-      <c r="FJ1" s="0" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>intereses</t>
         </is>
       </c>
-      <c r="FK1" s="0" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>pagosOperacion</t>
         </is>
       </c>
-      <c r="FL1" s="0" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>cajaFinal</t>
         </is>
       </c>
-      <c r="FM1" s="0" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>depreciacionAcumulada</t>
         </is>
       </c>
-      <c r="FN1" s="0" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>activosCosto</t>
         </is>
       </c>
-      <c r="FO1" s="0" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>activosFijos</t>
         </is>
       </c>
-      <c r="FP1" s="0" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ingresos</t>
         </is>
       </c>
-      <c r="FQ1" s="0" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.ventasNetas</t>
         </is>
       </c>
-      <c r="FR1" s="0" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costos</t>
         </is>
       </c>
-      <c r="FS1" s="0" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.utilidad</t>
         </is>
       </c>
-      <c r="FT1" s="0" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.depreciacion</t>
         </is>
       </c>
-      <c r="FU1" s="0" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.intereses</t>
         </is>
       </c>
-      <c r="FV1" s="0" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>financial.estadoResultados.costosProduccion</t>
         </is>
       </c>
-      <c r="FW1" s="0" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="FX1" s="0" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.entradas</t>
         </is>
       </c>
-      <c r="FY1" s="0" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.salidas</t>
         </is>
       </c>
-      <c r="FZ1" s="0" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>financial.balanceCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GA1" s="0" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaInicial</t>
         </is>
       </c>
-      <c r="GB1" s="0" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cobrosVentas</t>
         </is>
       </c>
-      <c r="GC1" s="0" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.pagosOperacion</t>
         </is>
       </c>
-      <c r="GD1" s="0" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.compraActivos</t>
         </is>
       </c>
-      <c r="GE1" s="0" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.financiamiento</t>
         </is>
       </c>
-      <c r="GF1" s="0" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.operacion</t>
         </is>
       </c>
-      <c r="GG1" s="0" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.inversion</t>
         </is>
       </c>
-      <c r="GH1" s="0" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.flujoNeto</t>
         </is>
       </c>
-      <c r="GI1" s="0" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>financial.flujoCaja.cajaFinal</t>
         </is>
       </c>
-      <c r="GJ1" s="0" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.efectivo</t>
         </is>
       </c>
-      <c r="GK1" s="0" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activosFijos</t>
         </is>
       </c>
-      <c r="GL1" s="0" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.inventarioMP</t>
         </is>
       </c>
-      <c r="GM1" s="0" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.activos</t>
         </is>
       </c>
-      <c r="GN1" s="0" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.deuda</t>
         </is>
       </c>
-      <c r="GO1" s="0" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.patrimonio</t>
         </is>
       </c>
-      <c r="GP1" s="0" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>financial.balanceGeneral.pasivoPatrimonio</t>
         </is>
       </c>
-      <c r="GQ1" s="0" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>financial.financiamiento.montoPrestamo</t>
         </is>
       </c>
-      <c r="GR1" s="0" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaTEA</t>
         </is>
       </c>
-      <c r="GS1" s="0" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>financial.financiamiento.deudaPrincipal</t>
         </is>
       </c>
-      <c r="GT1" s="0" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaAdicionalProximoPrestamo</t>
         </is>
       </c>
-      <c r="GU1" s="0" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>financial.financiamiento.tasaMensual</t>
         </is>
       </c>
-      <c r="GV1" s="0" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>financial.financiamiento.intereses</t>
         </is>
@@ -5674,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="0" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
@@ -5688,7 +5694,7 @@
       </c>
       <c r="O2" s="0" t="inlineStr">
         <is>
-          <t>INS-10A</t>
+          <t>COM-06B</t>
         </is>
       </c>
       <c r="P2" s="0" t="inlineStr">
@@ -6047,7 +6053,7 @@
         <v/>
       </c>
       <c r="DU2" s="0">
-        <f>(DB2*25+DD2*45+DF2*80+DI2*4+DK2*9+DN2*2+DP2*4+DR2*7)*0.8924</f>
+        <f>(DB2*25+DD2*45+DF2*80+DI2*4+DK2*9+DN2*2+DP2*4+DR2*7)*0.92</f>
         <v/>
       </c>
       <c r="DV2" s="0">
@@ -6121,246 +6127,249 @@
         <v/>
       </c>
       <c r="EN2" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)*EJ2</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO2" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("INV-02A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
+        <f>(0)*1</f>
         <v/>
       </c>
       <c r="EP2" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ2" s="0">
-        <f>DT2+DU2+DV2+DW2+L2+EL2+EM2+EN2+EO2+EP2</f>
-        <v/>
+      <c r="EQ2" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER2" s="0">
-        <f>EK2-EQ2</f>
+        <f>DT2+DU2+DV2+DW2+L2+EL2+EM2+EN2+EO2+EP2+EQ2</f>
         <v/>
       </c>
       <c r="ES2" s="0">
+        <f>EK2-ER2</f>
+        <v/>
+      </c>
+      <c r="ET2" s="0">
         <f>AND(D2="SEG-03",AI2&lt;4,I2&gt;0)</f>
         <v/>
       </c>
-      <c r="ET2" s="0">
+      <c r="EU2" s="0">
         <f>AND(D2="SEG-03",AI2&gt;=7,I2&gt;0)</f>
         <v/>
       </c>
-      <c r="EU2" s="0">
+      <c r="EV2" s="0">
         <f>AF2&lt;4</f>
         <v/>
       </c>
-      <c r="EV2" s="0">
+      <c r="EW2" s="0">
         <f>AM2&gt;=2</f>
         <v/>
       </c>
-      <c r="EW2" s="0">
+      <c r="EX2" s="0">
         <f>AH2&lt;3</f>
         <v/>
       </c>
-      <c r="EX2" s="0">
+      <c r="EY2" s="0">
         <f>I2&gt;CE2</f>
         <v/>
       </c>
-      <c r="EY2" s="0">
+      <c r="EZ2" s="0">
         <f>CZ2&gt;EJ2</f>
         <v/>
       </c>
-      <c r="EZ2" s="0">
+      <c r="FA2" s="0">
         <f>AND(K2=0,AF2&lt;5)</f>
         <v/>
       </c>
-      <c r="FA2" s="0" t="n">
+      <c r="FB2" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB2" s="0">
+      <c r="FC2">
         <f>1*2500*(1+0.03+0.02)+1*3500*(1+0.03+0.02)+1*1200*(1+0.03+0.02)+1*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC2" s="0">
+      <c r="FD2">
         <f>1*2500+1*3500+1*1200+1*300</f>
         <v/>
       </c>
-      <c r="FD2" s="0">
-        <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FE2" s="0">
-        <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.8924</f>
-        <v/>
-      </c>
-      <c r="FF2" s="0">
-        <f>FA2</f>
-        <v/>
-      </c>
-      <c r="FG2" s="0">
+      <c r="FE2">
+        <f>(CF2*25+CH2*45+CJ2*80+CL2*4+CN2*9+CP2*2+CR2*4+CT2*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF2">
+        <f>(DC2*25+DE2*45+DG2*80+DJ2*4+DL2*9+DO2*2+DQ2*4+DS2*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG2">
+        <f>FB2</f>
+        <v/>
+      </c>
+      <c r="FH2">
         <f>(1+AR2/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH2" s="0">
-        <f>0*0+AP2*FG2</f>
-        <v/>
-      </c>
-      <c r="FI2" s="0">
-        <f>IFERROR(FH2/(0+AP2),0)</f>
-        <v/>
-      </c>
-      <c r="FJ2" s="0">
-        <f>FH2*1</f>
-        <v/>
-      </c>
-      <c r="FK2" s="0">
-        <f>EQ2-DW2-DU2+FD2+FJ2</f>
-        <v/>
-      </c>
-      <c r="FL2" s="0">
-        <f>FF2+EK2+AP2-FK2-FB2</f>
-        <v/>
-      </c>
-      <c r="FM2" s="0">
+      <c r="FI2">
+        <f>0*0+AP2*FH2</f>
+        <v/>
+      </c>
+      <c r="FJ2">
+        <f>IFERROR(FI2/(0+AP2),0)</f>
+        <v/>
+      </c>
+      <c r="FK2">
+        <f>FI2*1</f>
+        <v/>
+      </c>
+      <c r="FL2">
+        <f>ER2-DW2-DU2+FE2+FK2</f>
+        <v/>
+      </c>
+      <c r="FM2">
+        <f>FG2+EK2+AP2-FL2-FC2</f>
+        <v/>
+      </c>
+      <c r="FN2">
         <f>0+DW2</f>
         <v/>
       </c>
-      <c r="FN2" s="0">
-        <f>0+FC2</f>
-        <v/>
-      </c>
-      <c r="FO2" s="0">
-        <f>FN2-FM2</f>
-        <v/>
-      </c>
-      <c r="FP2" s="0">
+      <c r="FO2">
+        <f>0+FD2</f>
+        <v/>
+      </c>
+      <c r="FP2">
+        <f>FO2-FN2</f>
+        <v/>
+      </c>
+      <c r="FQ2">
         <f>EK2</f>
         <v/>
       </c>
-      <c r="FQ2" s="0">
+      <c r="FR2">
         <f>EK2</f>
         <v/>
       </c>
-      <c r="FR2" s="0">
-        <f>EQ2+FJ2</f>
-        <v/>
-      </c>
-      <c r="FS2" s="0">
-        <f>ER2-FJ2</f>
-        <v/>
-      </c>
-      <c r="FT2" s="0">
+      <c r="FS2">
+        <f>ER2+FK2</f>
+        <v/>
+      </c>
+      <c r="FT2">
+        <f>ES2-FK2</f>
+        <v/>
+      </c>
+      <c r="FU2">
         <f>DW2</f>
         <v/>
       </c>
-      <c r="FU2" s="0">
+      <c r="FV2">
+        <f>FK2</f>
+        <v/>
+      </c>
+      <c r="FW2">
+        <f>ER2</f>
+        <v/>
+      </c>
+      <c r="FX2">
+        <f>FG2</f>
+        <v/>
+      </c>
+      <c r="FY2">
+        <f>EK2+AP2</f>
+        <v/>
+      </c>
+      <c r="FZ2">
+        <f>FL2+FC2</f>
+        <v/>
+      </c>
+      <c r="GA2">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="GB2">
+        <f>FG2</f>
+        <v/>
+      </c>
+      <c r="GC2">
+        <f>EK2</f>
+        <v/>
+      </c>
+      <c r="GD2">
+        <f>FL2</f>
+        <v/>
+      </c>
+      <c r="GE2">
+        <f>FC2</f>
+        <v/>
+      </c>
+      <c r="GF2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GG2">
+        <f>EK2-FL2</f>
+        <v/>
+      </c>
+      <c r="GH2">
+        <f>-FC2</f>
+        <v/>
+      </c>
+      <c r="GI2">
+        <f>FM2-FG2</f>
+        <v/>
+      </c>
+      <c r="GJ2">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="GK2">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="GL2">
+        <f>FP2</f>
+        <v/>
+      </c>
+      <c r="GM2">
+        <f>FF2</f>
+        <v/>
+      </c>
+      <c r="GN2">
+        <f>FM2+FP2+FF2</f>
+        <v/>
+      </c>
+      <c r="GO2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GP2">
+        <f>FM2+FP2+FF2-AS2</f>
+        <v/>
+      </c>
+      <c r="GQ2">
+        <f>FM2+FP2+FF2</f>
+        <v/>
+      </c>
+      <c r="GR2">
+        <f>AP2</f>
+        <v/>
+      </c>
+      <c r="GS2">
+        <f>AR2</f>
+        <v/>
+      </c>
+      <c r="GT2">
+        <f>AS2</f>
+        <v/>
+      </c>
+      <c r="GU2">
+        <f>AT2</f>
+        <v/>
+      </c>
+      <c r="GV2">
         <f>FJ2</f>
         <v/>
       </c>
-      <c r="FV2" s="0">
-        <f>EQ2</f>
-        <v/>
-      </c>
-      <c r="FW2" s="0">
-        <f>FF2</f>
-        <v/>
-      </c>
-      <c r="FX2" s="0">
-        <f>EK2+AP2</f>
-        <v/>
-      </c>
-      <c r="FY2" s="0">
-        <f>FK2+FB2</f>
-        <v/>
-      </c>
-      <c r="FZ2" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="GA2" s="0">
-        <f>FF2</f>
-        <v/>
-      </c>
-      <c r="GB2" s="0">
-        <f>EK2</f>
-        <v/>
-      </c>
-      <c r="GC2" s="0">
+      <c r="GW2">
         <f>FK2</f>
-        <v/>
-      </c>
-      <c r="GD2" s="0">
-        <f>FB2</f>
-        <v/>
-      </c>
-      <c r="GE2" s="0">
-        <f>AP2</f>
-        <v/>
-      </c>
-      <c r="GF2" s="0">
-        <f>EK2-FK2</f>
-        <v/>
-      </c>
-      <c r="GG2" s="0">
-        <f>-FB2</f>
-        <v/>
-      </c>
-      <c r="GH2" s="0">
-        <f>FL2-FF2</f>
-        <v/>
-      </c>
-      <c r="GI2" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="GJ2" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="GK2" s="0">
-        <f>FO2</f>
-        <v/>
-      </c>
-      <c r="GL2" s="0">
-        <f>FE2</f>
-        <v/>
-      </c>
-      <c r="GM2" s="0">
-        <f>FL2+FO2+FE2</f>
-        <v/>
-      </c>
-      <c r="GN2" s="0">
-        <f>AS2</f>
-        <v/>
-      </c>
-      <c r="GO2" s="0">
-        <f>FL2+FO2+FE2-AS2</f>
-        <v/>
-      </c>
-      <c r="GP2" s="0">
-        <f>FL2+FO2+FE2</f>
-        <v/>
-      </c>
-      <c r="GQ2" s="0">
-        <f>AP2</f>
-        <v/>
-      </c>
-      <c r="GR2" s="0">
-        <f>AR2</f>
-        <v/>
-      </c>
-      <c r="GS2" s="0">
-        <f>AS2</f>
-        <v/>
-      </c>
-      <c r="GT2" s="0">
-        <f>AT2</f>
-        <v/>
-      </c>
-      <c r="GU2" s="0">
-        <f>FI2</f>
-        <v/>
-      </c>
-      <c r="GV2" s="0">
-        <f>FJ2</f>
         <v/>
       </c>
     </row>
@@ -6432,44 +6441,20 @@
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
-          <t>INS-09A</t>
+          <t>RH-10B</t>
         </is>
       </c>
       <c r="Q3" s="0" t="inlineStr">
         <is>
-          <t>INS-10B</t>
-        </is>
-      </c>
-      <c r="R3" s="0" t="inlineStr">
-        <is>
-          <t>INS-11C</t>
-        </is>
-      </c>
-      <c r="S3" s="0" t="inlineStr">
-        <is>
-          <t>RH-10B</t>
-        </is>
-      </c>
-      <c r="T3" s="0" t="inlineStr">
-        <is>
-          <t>FIN-02B</t>
-        </is>
-      </c>
-      <c r="U3" s="0" t="inlineStr">
-        <is>
-          <t>COM-06A</t>
-        </is>
-      </c>
-      <c r="V3" s="0" t="inlineStr">
-        <is>
-          <t>INF-11A</t>
-        </is>
-      </c>
-      <c r="W3" s="0" t="inlineStr">
-        <is>
-          <t>INS-12A</t>
-        </is>
-      </c>
+          <t>COM-06B</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr"/>
+      <c r="S3" s="0" t="inlineStr"/>
+      <c r="T3" s="0" t="inlineStr"/>
+      <c r="U3" s="0" t="inlineStr"/>
+      <c r="V3" s="0" t="inlineStr"/>
+      <c r="W3" s="0" t="inlineStr"/>
       <c r="X3" s="0" t="inlineStr"/>
       <c r="Y3" s="0" t="inlineStr"/>
       <c r="Z3" s="0" t="inlineStr"/>
@@ -6479,15 +6464,15 @@
       <c r="AD3" s="0" t="inlineStr"/>
       <c r="AE3" s="0" t="inlineStr"/>
       <c r="AF3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(R3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(S3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(T3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(U3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(W3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AG3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(R3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(S3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(T3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(U3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(W3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AH3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(R3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(S3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(T3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(U3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(W3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(Q3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AI3" s="0">
@@ -6814,15 +6799,15 @@
         <v/>
       </c>
       <c r="DU3" s="0">
-        <f>(DB3*25+DD3*45+DF3*80+DI3*4+DK3*9+DN3*2+DP3*4+DR3*7)*0.9016000000000001</f>
+        <f>(DB3*25+DD3*45+DF3*80+DI3*4+DK3*9+DN3*2+DP3*4+DR3*7)*0.92</f>
         <v/>
       </c>
       <c r="DV3" s="0">
-        <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH(V3,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1</f>
         <v/>
       </c>
       <c r="DW3" s="0">
-        <f>1*(2375.0*CZ3/100000)+1*(3325.0*CZ3/100000)+1*(1140.0*CZ3/100000)+1*(285.0*CZ3/100000)</f>
+        <f>1*(2375.0/10/12*1)+1*(3325.0/10/12*1)+1*(1140.0/8/12*1)+1*(285.0/5/12*1)</f>
         <v/>
       </c>
       <c r="DX3" s="0">
@@ -6888,246 +6873,249 @@
         <v/>
       </c>
       <c r="EN3" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-06A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)*EJ3</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO3" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-01A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("INS-12A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
+        <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-01A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
       <c r="EP3" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ3" s="0">
-        <f>DT3+DU3+DV3+DW3+L3+EL3+EM3+EN3+EO3+EP3</f>
-        <v/>
+      <c r="EQ3" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER3" s="0">
-        <f>EK3-EQ3</f>
+        <f>DT3+DU3+DV3+DW3+L3+EL3+EM3+EN3+EO3+EP3+EQ3</f>
         <v/>
       </c>
       <c r="ES3" s="0">
+        <f>EK3-ER3</f>
+        <v/>
+      </c>
+      <c r="ET3" s="0">
         <f>AND(D3="SEG-03",AI3&lt;4,I3&gt;0)</f>
         <v/>
       </c>
-      <c r="ET3" s="0">
+      <c r="EU3" s="0">
         <f>AND(D3="SEG-03",AI3&gt;=7,I3&gt;0)</f>
         <v/>
       </c>
-      <c r="EU3" s="0">
+      <c r="EV3" s="0">
         <f>AF3&lt;4</f>
         <v/>
       </c>
-      <c r="EV3" s="0">
+      <c r="EW3" s="0">
         <f>AM3&gt;=2</f>
         <v/>
       </c>
-      <c r="EW3" s="0">
+      <c r="EX3" s="0">
         <f>AH3&lt;3</f>
         <v/>
       </c>
-      <c r="EX3" s="0">
+      <c r="EY3" s="0">
         <f>I3&gt;CE3</f>
         <v/>
       </c>
-      <c r="EY3" s="0">
+      <c r="EZ3" s="0">
         <f>CZ3&gt;EJ3</f>
         <v/>
       </c>
-      <c r="EZ3" s="0">
+      <c r="FA3" s="0">
         <f>AND(K3=0,AF3&lt;5)</f>
         <v/>
       </c>
-      <c r="FA3" s="0" t="n">
+      <c r="FB3" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB3" s="0">
+      <c r="FC3">
         <f>0*2500*(1+0.03+0.02)+0*3500*(1+0.03+0.02)+0*1200*(1+0.03+0.02)+0*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC3" s="0">
+      <c r="FD3">
         <f>0*2500+0*3500+0*1200+0*300</f>
         <v/>
       </c>
-      <c r="FD3" s="0">
-        <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.9016000000000001</f>
-        <v/>
-      </c>
-      <c r="FE3" s="0">
-        <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.9016000000000001</f>
-        <v/>
-      </c>
-      <c r="FF3" s="0">
-        <f>FL2</f>
-        <v/>
-      </c>
-      <c r="FG3" s="0">
+      <c r="FE3">
+        <f>(CF3*25+CH3*45+CJ3*80+CL3*4+CN3*9+CP3*2+CR3*4+CT3*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF3">
+        <f>(DC3*25+DE3*45+DG3*80+DJ3*4+DL3*9+DO3*2+DQ3*4+DS3*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG3">
+        <f>FM2</f>
+        <v/>
+      </c>
+      <c r="FH3">
         <f>(1+AR3/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH3" s="0">
-        <f>AS2*FI2+AP3*FG3</f>
-        <v/>
-      </c>
-      <c r="FI3" s="0">
-        <f>IFERROR(FH3/(AS2+AP3),0)</f>
-        <v/>
-      </c>
-      <c r="FJ3" s="0">
-        <f>FH3*1</f>
-        <v/>
-      </c>
-      <c r="FK3" s="0">
-        <f>EQ3-DW3-DU3+FD3+FJ3</f>
-        <v/>
-      </c>
-      <c r="FL3" s="0">
-        <f>FF3+EK3+AP3-FK3-FB3</f>
-        <v/>
-      </c>
-      <c r="FM3" s="0">
-        <f>FM2+DW3</f>
-        <v/>
-      </c>
-      <c r="FN3" s="0">
-        <f>FN2+FC3</f>
-        <v/>
-      </c>
-      <c r="FO3" s="0">
-        <f>FN3-FM3</f>
-        <v/>
-      </c>
-      <c r="FP3" s="0">
+      <c r="FI3">
+        <f>AS2*FJ2+AP3*FH3</f>
+        <v/>
+      </c>
+      <c r="FJ3">
+        <f>IFERROR(FI3/(AS2+AP3),0)</f>
+        <v/>
+      </c>
+      <c r="FK3">
+        <f>FI3*1</f>
+        <v/>
+      </c>
+      <c r="FL3">
+        <f>ER3-DW3-DU3+FE3+FK3</f>
+        <v/>
+      </c>
+      <c r="FM3">
+        <f>FG3+EK3+AP3-FL3-FC3</f>
+        <v/>
+      </c>
+      <c r="FN3">
+        <f>FN2+DW3</f>
+        <v/>
+      </c>
+      <c r="FO3">
+        <f>FO2+FD3</f>
+        <v/>
+      </c>
+      <c r="FP3">
+        <f>FO3-FN3</f>
+        <v/>
+      </c>
+      <c r="FQ3">
         <f>EK3</f>
         <v/>
       </c>
-      <c r="FQ3" s="0">
+      <c r="FR3">
         <f>EK3</f>
         <v/>
       </c>
-      <c r="FR3" s="0">
-        <f>EQ3+FJ3</f>
-        <v/>
-      </c>
-      <c r="FS3" s="0">
-        <f>ER3-FJ3</f>
-        <v/>
-      </c>
-      <c r="FT3" s="0">
+      <c r="FS3">
+        <f>ER3+FK3</f>
+        <v/>
+      </c>
+      <c r="FT3">
+        <f>ES3-FK3</f>
+        <v/>
+      </c>
+      <c r="FU3">
         <f>DW3</f>
         <v/>
       </c>
-      <c r="FU3" s="0">
+      <c r="FV3">
+        <f>FK3</f>
+        <v/>
+      </c>
+      <c r="FW3">
+        <f>ER3</f>
+        <v/>
+      </c>
+      <c r="FX3">
+        <f>FG3</f>
+        <v/>
+      </c>
+      <c r="FY3">
+        <f>EK3+AP3</f>
+        <v/>
+      </c>
+      <c r="FZ3">
+        <f>FL3+FC3</f>
+        <v/>
+      </c>
+      <c r="GA3">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="GB3">
+        <f>FG3</f>
+        <v/>
+      </c>
+      <c r="GC3">
+        <f>EK3</f>
+        <v/>
+      </c>
+      <c r="GD3">
+        <f>FL3</f>
+        <v/>
+      </c>
+      <c r="GE3">
+        <f>FC3</f>
+        <v/>
+      </c>
+      <c r="GF3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GG3">
+        <f>EK3-FL3</f>
+        <v/>
+      </c>
+      <c r="GH3">
+        <f>-FC3</f>
+        <v/>
+      </c>
+      <c r="GI3">
+        <f>FM3-FG3</f>
+        <v/>
+      </c>
+      <c r="GJ3">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="GK3">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="GL3">
+        <f>FP3</f>
+        <v/>
+      </c>
+      <c r="GM3">
+        <f>FF3</f>
+        <v/>
+      </c>
+      <c r="GN3">
+        <f>FM3+FP3+FF3</f>
+        <v/>
+      </c>
+      <c r="GO3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GP3">
+        <f>FM3+FP3+FF3-AS3</f>
+        <v/>
+      </c>
+      <c r="GQ3">
+        <f>FM3+FP3+FF3</f>
+        <v/>
+      </c>
+      <c r="GR3">
+        <f>AP3</f>
+        <v/>
+      </c>
+      <c r="GS3">
+        <f>AR3</f>
+        <v/>
+      </c>
+      <c r="GT3">
+        <f>AS3</f>
+        <v/>
+      </c>
+      <c r="GU3">
+        <f>AT3</f>
+        <v/>
+      </c>
+      <c r="GV3">
         <f>FJ3</f>
         <v/>
       </c>
-      <c r="FV3" s="0">
-        <f>EQ3</f>
-        <v/>
-      </c>
-      <c r="FW3" s="0">
-        <f>FF3</f>
-        <v/>
-      </c>
-      <c r="FX3" s="0">
-        <f>EK3+AP3</f>
-        <v/>
-      </c>
-      <c r="FY3" s="0">
-        <f>FK3+FB3</f>
-        <v/>
-      </c>
-      <c r="FZ3" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="GA3" s="0">
-        <f>FF3</f>
-        <v/>
-      </c>
-      <c r="GB3" s="0">
-        <f>EK3</f>
-        <v/>
-      </c>
-      <c r="GC3" s="0">
+      <c r="GW3">
         <f>FK3</f>
-        <v/>
-      </c>
-      <c r="GD3" s="0">
-        <f>FB3</f>
-        <v/>
-      </c>
-      <c r="GE3" s="0">
-        <f>AP3</f>
-        <v/>
-      </c>
-      <c r="GF3" s="0">
-        <f>EK3-FK3</f>
-        <v/>
-      </c>
-      <c r="GG3" s="0">
-        <f>-FB3</f>
-        <v/>
-      </c>
-      <c r="GH3" s="0">
-        <f>FL3-FF3</f>
-        <v/>
-      </c>
-      <c r="GI3" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="GJ3" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="GK3" s="0">
-        <f>FO3</f>
-        <v/>
-      </c>
-      <c r="GL3" s="0">
-        <f>FE3</f>
-        <v/>
-      </c>
-      <c r="GM3" s="0">
-        <f>FL3+FO3+FE3</f>
-        <v/>
-      </c>
-      <c r="GN3" s="0">
-        <f>AS3</f>
-        <v/>
-      </c>
-      <c r="GO3" s="0">
-        <f>FL3+FO3+FE3-AS3</f>
-        <v/>
-      </c>
-      <c r="GP3" s="0">
-        <f>FL3+FO3+FE3</f>
-        <v/>
-      </c>
-      <c r="GQ3" s="0">
-        <f>AP3</f>
-        <v/>
-      </c>
-      <c r="GR3" s="0">
-        <f>AR3</f>
-        <v/>
-      </c>
-      <c r="GS3" s="0">
-        <f>AS3</f>
-        <v/>
-      </c>
-      <c r="GT3" s="0">
-        <f>AT3</f>
-        <v/>
-      </c>
-      <c r="GU3" s="0">
-        <f>FI3</f>
-        <v/>
-      </c>
-      <c r="GV3" s="0">
-        <f>FJ3</f>
         <v/>
       </c>
     </row>
@@ -7194,49 +7182,25 @@
       </c>
       <c r="O4" s="0" t="inlineStr">
         <is>
-          <t>INS-09A</t>
+          <t>RH-10B</t>
         </is>
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
-          <t>INS-10B</t>
+          <t>COM-06B</t>
         </is>
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>INS-11C</t>
-        </is>
-      </c>
-      <c r="R4" s="0" t="inlineStr">
-        <is>
-          <t>RH-10B</t>
-        </is>
-      </c>
-      <c r="S4" s="0" t="inlineStr">
-        <is>
-          <t>FIN-02B</t>
-        </is>
-      </c>
-      <c r="T4" s="0" t="inlineStr">
-        <is>
-          <t>COM-06A</t>
-        </is>
-      </c>
-      <c r="U4" s="0" t="inlineStr">
-        <is>
-          <t>INF-11A</t>
-        </is>
-      </c>
-      <c r="V4" s="0" t="inlineStr">
-        <is>
-          <t>INS-12A</t>
-        </is>
-      </c>
-      <c r="W4" s="0" t="inlineStr">
-        <is>
           <t>FIN-01A</t>
         </is>
       </c>
+      <c r="R4" s="0" t="inlineStr"/>
+      <c r="S4" s="0" t="inlineStr"/>
+      <c r="T4" s="0" t="inlineStr"/>
+      <c r="U4" s="0" t="inlineStr"/>
+      <c r="V4" s="0" t="inlineStr"/>
+      <c r="W4" s="0" t="inlineStr"/>
       <c r="X4" s="0" t="inlineStr"/>
       <c r="Y4" s="0" t="inlineStr"/>
       <c r="Z4" s="0" t="inlineStr"/>
@@ -7246,15 +7210,15 @@
       <c r="AD4" s="0" t="inlineStr"/>
       <c r="AE4" s="0" t="inlineStr"/>
       <c r="AF4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(R4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(S4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(T4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(V4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(W4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$I$2:$I$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AG4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(R4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(S4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(T4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(V4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(W4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$J$2:$J$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AH4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(R4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(S4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(T4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(V4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(W4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(N4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(O4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(P4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$K$2:$K$69,MATCH(Q4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
         <v/>
       </c>
       <c r="AI4" s="0">
@@ -7581,15 +7545,15 @@
         <v/>
       </c>
       <c r="DU4" s="0">
-        <f>(DB4*25+DD4*45+DF4*80+DI4*4+DK4*9+DN4*2+DP4*4+DR4*7)*0.9016000000000001</f>
+        <f>(DB4*25+DD4*45+DF4*80+DI4*4+DK4*9+DN4*2+DP4*4+DR4*7)*0.92</f>
         <v/>
       </c>
       <c r="DV4" s="0">
-        <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH(U4,'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)</f>
+        <f>1*2500*0.05/12*1+1*3500*0.05/12*1+1*1200*0.05/12*1+1*300*0.05/12*1</f>
         <v/>
       </c>
       <c r="DW4" s="0">
-        <f>1*(2375.0*CZ4/100000)+1*(3325.0*CZ4/100000)+1*(1140.0*CZ4/100000)+1*(285.0*CZ4/100000)</f>
+        <f>1*(2375.0/10/12*1)+1*(3325.0/10/12*1)+1*(1140.0/8/12*1)+1*(285.0/5/12*1)</f>
         <v/>
       </c>
       <c r="DX4" s="0">
@@ -7655,246 +7619,249 @@
         <v/>
       </c>
       <c r="EN4" s="0">
-        <f>IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-06A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)*EJ4</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="EO4" s="0">
-        <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-01A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0)+IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("INS-12A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
+        <f>(IFERROR(INDEX('Catalogo_Numerico_banca'!$G$2:$G$69,MATCH("COM-01A",'Catalogo_Numerico_banca'!$A$2:$A$69,0)),0))*1</f>
         <v/>
       </c>
       <c r="EP4" s="0">
         <f>0</f>
         <v/>
       </c>
-      <c r="EQ4" s="0">
-        <f>DT4+DU4+DV4+DW4+L4+EL4+EM4+EN4+EO4+EP4</f>
-        <v/>
+      <c r="EQ4" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="ER4" s="0">
-        <f>EK4-EQ4</f>
+        <f>DT4+DU4+DV4+DW4+L4+EL4+EM4+EN4+EO4+EP4+EQ4</f>
         <v/>
       </c>
       <c r="ES4" s="0">
+        <f>EK4-ER4</f>
+        <v/>
+      </c>
+      <c r="ET4" s="0">
         <f>AND(D4="SEG-03",AI4&lt;4,I4&gt;0)</f>
         <v/>
       </c>
-      <c r="ET4" s="0">
+      <c r="EU4" s="0">
         <f>AND(D4="SEG-03",AI4&gt;=7,I4&gt;0)</f>
         <v/>
       </c>
-      <c r="EU4" s="0">
+      <c r="EV4" s="0">
         <f>AF4&lt;4</f>
         <v/>
       </c>
-      <c r="EV4" s="0">
+      <c r="EW4" s="0">
         <f>AM4&gt;=2</f>
         <v/>
       </c>
-      <c r="EW4" s="0">
+      <c r="EX4" s="0">
         <f>AH4&lt;3</f>
         <v/>
       </c>
-      <c r="EX4" s="0">
+      <c r="EY4" s="0">
         <f>I4&gt;CE4</f>
         <v/>
       </c>
-      <c r="EY4" s="0">
+      <c r="EZ4" s="0">
         <f>CZ4&gt;EJ4</f>
         <v/>
       </c>
-      <c r="EZ4" s="0">
+      <c r="FA4" s="0">
         <f>AND(K4=0,AF4&lt;5)</f>
         <v/>
       </c>
-      <c r="FA4" s="0" t="n">
+      <c r="FB4" t="n">
         <v>1000000</v>
       </c>
-      <c r="FB4" s="0">
+      <c r="FC4">
         <f>0*2500*(1+0.03+0.02)+0*3500*(1+0.03+0.02)+0*1200*(1+0.03+0.02)+0*300*(1+0+0.01)</f>
         <v/>
       </c>
-      <c r="FC4" s="0">
+      <c r="FD4">
         <f>0*2500+0*3500+0*1200+0*300</f>
         <v/>
       </c>
-      <c r="FD4" s="0">
-        <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.9016000000000001</f>
-        <v/>
-      </c>
-      <c r="FE4" s="0">
-        <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.9016000000000001</f>
-        <v/>
-      </c>
-      <c r="FF4" s="0">
-        <f>FL3</f>
-        <v/>
-      </c>
-      <c r="FG4" s="0">
+      <c r="FE4">
+        <f>(CF4*25+CH4*45+CJ4*80+CL4*4+CN4*9+CP4*2+CR4*4+CT4*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FF4">
+        <f>(DC4*25+DE4*45+DG4*80+DJ4*4+DL4*9+DO4*2+DQ4*4+DS4*7)*0.92</f>
+        <v/>
+      </c>
+      <c r="FG4">
+        <f>FM3</f>
+        <v/>
+      </c>
+      <c r="FH4">
         <f>(1+AR4/100)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="FH4" s="0">
-        <f>AS3*FI3+AP4*FG4</f>
-        <v/>
-      </c>
-      <c r="FI4" s="0">
-        <f>IFERROR(FH4/(AS3+AP4),0)</f>
-        <v/>
-      </c>
-      <c r="FJ4" s="0">
-        <f>FH4*1</f>
-        <v/>
-      </c>
-      <c r="FK4" s="0">
-        <f>EQ4-DW4-DU4+FD4+FJ4</f>
-        <v/>
-      </c>
-      <c r="FL4" s="0">
-        <f>FF4+EK4+AP4-FK4-FB4</f>
-        <v/>
-      </c>
-      <c r="FM4" s="0">
-        <f>FM3+DW4</f>
-        <v/>
-      </c>
-      <c r="FN4" s="0">
-        <f>FN3+FC4</f>
-        <v/>
-      </c>
-      <c r="FO4" s="0">
-        <f>FN4-FM4</f>
-        <v/>
-      </c>
-      <c r="FP4" s="0">
+      <c r="FI4">
+        <f>AS3*FJ3+AP4*FH4</f>
+        <v/>
+      </c>
+      <c r="FJ4">
+        <f>IFERROR(FI4/(AS3+AP4),0)</f>
+        <v/>
+      </c>
+      <c r="FK4">
+        <f>FI4*1</f>
+        <v/>
+      </c>
+      <c r="FL4">
+        <f>ER4-DW4-DU4+FE4+FK4</f>
+        <v/>
+      </c>
+      <c r="FM4">
+        <f>FG4+EK4+AP4-FL4-FC4</f>
+        <v/>
+      </c>
+      <c r="FN4">
+        <f>FN3+DW4</f>
+        <v/>
+      </c>
+      <c r="FO4">
+        <f>FO3+FD4</f>
+        <v/>
+      </c>
+      <c r="FP4">
+        <f>FO4-FN4</f>
+        <v/>
+      </c>
+      <c r="FQ4">
         <f>EK4</f>
         <v/>
       </c>
-      <c r="FQ4" s="0">
+      <c r="FR4">
         <f>EK4</f>
         <v/>
       </c>
-      <c r="FR4" s="0">
-        <f>EQ4+FJ4</f>
-        <v/>
-      </c>
-      <c r="FS4" s="0">
-        <f>ER4-FJ4</f>
-        <v/>
-      </c>
-      <c r="FT4" s="0">
+      <c r="FS4">
+        <f>ER4+FK4</f>
+        <v/>
+      </c>
+      <c r="FT4">
+        <f>ES4-FK4</f>
+        <v/>
+      </c>
+      <c r="FU4">
         <f>DW4</f>
         <v/>
       </c>
-      <c r="FU4" s="0">
+      <c r="FV4">
+        <f>FK4</f>
+        <v/>
+      </c>
+      <c r="FW4">
+        <f>ER4</f>
+        <v/>
+      </c>
+      <c r="FX4">
+        <f>FG4</f>
+        <v/>
+      </c>
+      <c r="FY4">
+        <f>EK4+AP4</f>
+        <v/>
+      </c>
+      <c r="FZ4">
+        <f>FL4+FC4</f>
+        <v/>
+      </c>
+      <c r="GA4">
+        <f>FM4</f>
+        <v/>
+      </c>
+      <c r="GB4">
+        <f>FG4</f>
+        <v/>
+      </c>
+      <c r="GC4">
+        <f>EK4</f>
+        <v/>
+      </c>
+      <c r="GD4">
+        <f>FL4</f>
+        <v/>
+      </c>
+      <c r="GE4">
+        <f>FC4</f>
+        <v/>
+      </c>
+      <c r="GF4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GG4">
+        <f>EK4-FL4</f>
+        <v/>
+      </c>
+      <c r="GH4">
+        <f>-FC4</f>
+        <v/>
+      </c>
+      <c r="GI4">
+        <f>FM4-FG4</f>
+        <v/>
+      </c>
+      <c r="GJ4">
+        <f>FM4</f>
+        <v/>
+      </c>
+      <c r="GK4">
+        <f>FM4</f>
+        <v/>
+      </c>
+      <c r="GL4">
+        <f>FP4</f>
+        <v/>
+      </c>
+      <c r="GM4">
+        <f>FF4</f>
+        <v/>
+      </c>
+      <c r="GN4">
+        <f>FM4+FP4+FF4</f>
+        <v/>
+      </c>
+      <c r="GO4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GP4">
+        <f>FM4+FP4+FF4-AS4</f>
+        <v/>
+      </c>
+      <c r="GQ4">
+        <f>FM4+FP4+FF4</f>
+        <v/>
+      </c>
+      <c r="GR4">
+        <f>AP4</f>
+        <v/>
+      </c>
+      <c r="GS4">
+        <f>AR4</f>
+        <v/>
+      </c>
+      <c r="GT4">
+        <f>AS4</f>
+        <v/>
+      </c>
+      <c r="GU4">
+        <f>AT4</f>
+        <v/>
+      </c>
+      <c r="GV4">
         <f>FJ4</f>
         <v/>
       </c>
-      <c r="FV4" s="0">
-        <f>EQ4</f>
-        <v/>
-      </c>
-      <c r="FW4" s="0">
-        <f>FF4</f>
-        <v/>
-      </c>
-      <c r="FX4" s="0">
-        <f>EK4+AP4</f>
-        <v/>
-      </c>
-      <c r="FY4" s="0">
-        <f>FK4+FB4</f>
-        <v/>
-      </c>
-      <c r="FZ4" s="0">
-        <f>FL4</f>
-        <v/>
-      </c>
-      <c r="GA4" s="0">
-        <f>FF4</f>
-        <v/>
-      </c>
-      <c r="GB4" s="0">
-        <f>EK4</f>
-        <v/>
-      </c>
-      <c r="GC4" s="0">
+      <c r="GW4">
         <f>FK4</f>
-        <v/>
-      </c>
-      <c r="GD4" s="0">
-        <f>FB4</f>
-        <v/>
-      </c>
-      <c r="GE4" s="0">
-        <f>AP4</f>
-        <v/>
-      </c>
-      <c r="GF4" s="0">
-        <f>EK4-FK4</f>
-        <v/>
-      </c>
-      <c r="GG4" s="0">
-        <f>-FB4</f>
-        <v/>
-      </c>
-      <c r="GH4" s="0">
-        <f>FL4-FF4</f>
-        <v/>
-      </c>
-      <c r="GI4" s="0">
-        <f>FL4</f>
-        <v/>
-      </c>
-      <c r="GJ4" s="0">
-        <f>FL4</f>
-        <v/>
-      </c>
-      <c r="GK4" s="0">
-        <f>FO4</f>
-        <v/>
-      </c>
-      <c r="GL4" s="0">
-        <f>FE4</f>
-        <v/>
-      </c>
-      <c r="GM4" s="0">
-        <f>FL4+FO4+FE4</f>
-        <v/>
-      </c>
-      <c r="GN4" s="0">
-        <f>AS4</f>
-        <v/>
-      </c>
-      <c r="GO4" s="0">
-        <f>FL4+FO4+FE4-AS4</f>
-        <v/>
-      </c>
-      <c r="GP4" s="0">
-        <f>FL4+FO4+FE4</f>
-        <v/>
-      </c>
-      <c r="GQ4" s="0">
-        <f>AP4</f>
-        <v/>
-      </c>
-      <c r="GR4" s="0">
-        <f>AR4</f>
-        <v/>
-      </c>
-      <c r="GS4" s="0">
-        <f>AS4</f>
-        <v/>
-      </c>
-      <c r="GT4" s="0">
-        <f>AT4</f>
-        <v/>
-      </c>
-      <c r="GU4" s="0">
-        <f>FI4</f>
-        <v/>
-      </c>
-      <c r="GV4" s="0">
-        <f>FJ4</f>
         <v/>
       </c>
     </row>

--- a/tests/oracle/ORACULO_banca.xlsx
+++ b/tests/oracle/ORACULO_banca.xlsx
@@ -3721,11 +3721,11 @@
         </is>
       </c>
       <c r="D7" s="186">
-        <f>B9&gt;B10</f>
+        <f>B11&gt;B10</f>
         <v/>
       </c>
       <c r="E7" s="186">
-        <f>IF(D7,0.25*B13*MIN(1,IFERROR((B9-B10)/B10,0)),0)</f>
+        <f>IF(D7,0.25*B13*MIN(1,IFERROR((B11-B10)/B10,0)),0)</f>
         <v/>
       </c>
       <c r="F7" s="186">
@@ -6091,7 +6091,7 @@
         <v/>
       </c>
       <c r="EE2" s="0">
-        <f>ROUND(MIN(100,AI2*10),0)</f>
+        <f>IFERROR(ROUND(DY2/SUMIF($C$2:$C$4,"1|SEG-01",$DY$2:$DY$4)*100,0),0)</f>
         <v/>
       </c>
       <c r="EF2" s="0">
@@ -6123,7 +6123,7 @@
         <v/>
       </c>
       <c r="EM2" s="0">
-        <f>IF(I2&gt;CE2,0.25*DT2*IFERROR(MIN(1,(I2-CE2)/CE2),1),0)</f>
+        <f>IF(CZ2&gt;CE2,0.25*DT2*IFERROR(MIN(1,(CZ2-CE2)/CE2),1),0)</f>
         <v/>
       </c>
       <c r="EN2" s="0">
@@ -6170,7 +6170,7 @@
         <v/>
       </c>
       <c r="EY2" s="0">
-        <f>I2&gt;CE2</f>
+        <f>CZ2&gt;CE2</f>
         <v/>
       </c>
       <c r="EZ2" s="0">
@@ -6837,7 +6837,7 @@
         <v/>
       </c>
       <c r="EE3" s="0">
-        <f>ROUND(MIN(100,AI3*10),0)</f>
+        <f>IFERROR(ROUND(DY3/SUMIF($C$2:$C$4,"2|SEG-01",$DY$2:$DY$4)*100,0),0)</f>
         <v/>
       </c>
       <c r="EF3" s="0">
@@ -6869,7 +6869,7 @@
         <v/>
       </c>
       <c r="EM3" s="0">
-        <f>IF(I3&gt;CE3,0.25*DT3*IFERROR(MIN(1,(I3-CE3)/CE3),1),0)</f>
+        <f>IF(CZ3&gt;CE3,0.25*DT3*IFERROR(MIN(1,(CZ3-CE3)/CE3),1),0)</f>
         <v/>
       </c>
       <c r="EN3" s="0">
@@ -6916,7 +6916,7 @@
         <v/>
       </c>
       <c r="EY3" s="0">
-        <f>I3&gt;CE3</f>
+        <f>CZ3&gt;CE3</f>
         <v/>
       </c>
       <c r="EZ3" s="0">
@@ -7583,7 +7583,7 @@
         <v/>
       </c>
       <c r="EE4" s="0">
-        <f>ROUND(MIN(100,AI4*10),0)</f>
+        <f>IFERROR(ROUND(DY4/SUMIF($C$2:$C$4,"3|SEG-01",$DY$2:$DY$4)*100,0),0)</f>
         <v/>
       </c>
       <c r="EF4" s="0">
@@ -7615,7 +7615,7 @@
         <v/>
       </c>
       <c r="EM4" s="0">
-        <f>IF(I4&gt;CE4,0.25*DT4*IFERROR(MIN(1,(I4-CE4)/CE4),1),0)</f>
+        <f>IF(CZ4&gt;CE4,0.25*DT4*IFERROR(MIN(1,(CZ4-CE4)/CE4),1),0)</f>
         <v/>
       </c>
       <c r="EN4" s="0">
@@ -7662,7 +7662,7 @@
         <v/>
       </c>
       <c r="EY4" s="0">
-        <f>I4&gt;CE4</f>
+        <f>CZ4&gt;CE4</f>
         <v/>
       </c>
       <c r="EZ4" s="0">
